--- a/output/screener_output_20260908.xlsx
+++ b/output/screener_output_20260908.xlsx
@@ -2552,18 +2552,18 @@
       </c>
       <c r="F7" s="15" t="inlineStr">
         <is>
-          <t>70.2</t>
+          <t>69.6</t>
         </is>
       </c>
       <c r="H7" s="12" t="n"/>
       <c r="I7" s="15" t="inlineStr">
         <is>
-          <t>20.8%</t>
+          <t>25.9%</t>
         </is>
       </c>
       <c r="K7" s="15" t="inlineStr">
         <is>
-          <t>37.8%</t>
+          <t>38.2%</t>
         </is>
       </c>
       <c r="M7" s="15" t="inlineStr">
@@ -2779,7 +2779,7 @@
         <v>588.2</v>
       </c>
       <c r="J12" s="22" t="n">
-        <v>79.2</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="K12" s="24" t="inlineStr">
         <is>
@@ -2800,7 +2800,7 @@
         <v>2219.5</v>
       </c>
       <c r="O12" s="22" t="n">
-        <v>77.2</v>
+        <v>77.5</v>
       </c>
       <c r="P12" s="24" t="inlineStr">
         <is>
@@ -2844,7 +2844,7 @@
         <v>685.2</v>
       </c>
       <c r="J13" s="22" t="n">
-        <v>78.7</v>
+        <v>78.5</v>
       </c>
       <c r="K13" s="24" t="inlineStr">
         <is>
@@ -2888,7 +2888,7 @@
         <v>257.5</v>
       </c>
       <c r="E14" s="22" t="n">
-        <v>70</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="F14" s="23" t="inlineStr">
         <is>
@@ -2930,7 +2930,7 @@
         <v>10618.6</v>
       </c>
       <c r="O14" s="22" t="n">
-        <v>73</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="P14" s="23" t="inlineStr">
         <is>
@@ -2953,7 +2953,7 @@
         <v>117.2</v>
       </c>
       <c r="E15" s="22" t="n">
-        <v>67.40000000000001</v>
+        <v>67.09999999999999</v>
       </c>
       <c r="F15" s="23" t="inlineStr">
         <is>
@@ -2962,19 +2962,19 @@
       </c>
       <c r="G15" s="25" t="inlineStr">
         <is>
-          <t>LXFR</t>
+          <t>EVLV</t>
         </is>
       </c>
       <c r="H15" s="26" t="inlineStr">
         <is>
-          <t>Luxfer Holdings PLC</t>
+          <t>Evolv Technologies Holdings, Inc.</t>
         </is>
       </c>
       <c r="I15" s="27" t="n">
-        <v>463.9</v>
+        <v>912.8</v>
       </c>
       <c r="J15" s="22" t="n">
-        <v>74</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="K15" s="23" t="inlineStr">
         <is>
@@ -2995,7 +2995,7 @@
         <v>13629.7</v>
       </c>
       <c r="O15" s="22" t="n">
-        <v>71.5</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="P15" s="23" t="inlineStr">
         <is>
@@ -3027,19 +3027,19 @@
       </c>
       <c r="G16" s="19" t="inlineStr">
         <is>
-          <t>CLFD</t>
+          <t>GHM</t>
         </is>
       </c>
       <c r="H16" s="20" t="inlineStr">
         <is>
-          <t>Clearfield, Inc.</t>
+          <t>Graham Corporation</t>
         </is>
       </c>
       <c r="I16" s="21" t="n">
-        <v>394.6</v>
+        <v>1046.6</v>
       </c>
       <c r="J16" s="22" t="n">
-        <v>73.90000000000001</v>
+        <v>70.8</v>
       </c>
       <c r="K16" s="23" t="inlineStr">
         <is>
@@ -3048,19 +3048,19 @@
       </c>
       <c r="L16" s="19" t="inlineStr">
         <is>
-          <t>BRC</t>
+          <t>MRCY</t>
         </is>
       </c>
       <c r="M16" s="20" t="inlineStr">
         <is>
-          <t>Brady Corporation</t>
+          <t>Mercury Systems, Inc.</t>
         </is>
       </c>
       <c r="N16" s="21" t="n">
-        <v>4139.7</v>
+        <v>5093.4</v>
       </c>
       <c r="O16" s="22" t="n">
-        <v>69.90000000000001</v>
+        <v>69.8</v>
       </c>
       <c r="P16" s="23" t="inlineStr">
         <is>
@@ -3113,7 +3113,7 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>79.2</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -3128,7 +3128,7 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>78.7</v>
+        <v>78.5</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -3143,7 +3143,7 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>77.2</v>
+        <v>77.5</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -3169,56 +3169,56 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>LXFR</t>
+          <t>ADEA</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>74</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Small Cap</t>
+          <t>Breakout</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>CLFD</t>
+          <t>DCI</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>73.90000000000001</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Small Cap</t>
+          <t>Breakout</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>ADEA</t>
+          <t>EVLV</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>73.40000000000001</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Breakout</t>
+          <t>Small Cap</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>DCI</t>
+          <t>CACI</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>73</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -3229,26 +3229,26 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>ARRY</t>
+          <t>SODI</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>72.59999999999999</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Small Cap</t>
+          <t>Nano Cap</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>EVLV</t>
+          <t>GHM</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>72.09999999999999</v>
+        <v>70.8</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -3674,17 +3674,17 @@
     <row r="18" ht="16" customHeight="1">
       <c r="B18" s="19" t="inlineStr">
         <is>
-          <t>LXFR</t>
+          <t>ADEA</t>
         </is>
       </c>
       <c r="C18" s="20" t="inlineStr">
         <is>
-          <t>Luxfer Holdings PLC</t>
+          <t>Adeia Inc.</t>
         </is>
       </c>
       <c r="D18" s="48" t="inlineStr">
         <is>
-          <t>Small Cap</t>
+          <t>Breakout</t>
         </is>
       </c>
       <c r="E18" s="23" t="inlineStr">
@@ -3696,13 +3696,13 @@
         <v>0.03</v>
       </c>
       <c r="G18" s="71" t="n">
-        <v>0.03</v>
+        <v>0.036</v>
       </c>
       <c r="H18" s="72" t="n">
-        <v>3000</v>
+        <v>3600</v>
       </c>
       <c r="I18" s="73" t="n">
-        <v>173</v>
+        <v>132</v>
       </c>
       <c r="J18" s="74" t="inlineStr">
         <is>
@@ -3713,17 +3713,17 @@
     <row r="19" ht="16" customHeight="1">
       <c r="B19" s="25" t="inlineStr">
         <is>
-          <t>CLFD</t>
+          <t>DCI</t>
         </is>
       </c>
       <c r="C19" s="26" t="inlineStr">
         <is>
-          <t>Clearfield, Inc.</t>
+          <t>Donaldson Company, Inc.</t>
         </is>
       </c>
       <c r="D19" s="49" t="inlineStr">
         <is>
-          <t>Small Cap</t>
+          <t>Breakout</t>
         </is>
       </c>
       <c r="E19" s="23" t="inlineStr">
@@ -3735,34 +3735,34 @@
         <v>0.03</v>
       </c>
       <c r="G19" s="75" t="n">
-        <v>0.03</v>
+        <v>0.036</v>
       </c>
       <c r="H19" s="76" t="n">
-        <v>3000</v>
+        <v>3600</v>
       </c>
       <c r="I19" s="77" t="n">
-        <v>103</v>
+        <v>39</v>
       </c>
       <c r="J19" s="78" t="inlineStr">
         <is>
-          <t>Medium-High risk</t>
+          <t>Medium-Low risk</t>
         </is>
       </c>
     </row>
     <row r="20" ht="16" customHeight="1">
       <c r="B20" s="19" t="inlineStr">
         <is>
-          <t>ADEA</t>
+          <t>EVLV</t>
         </is>
       </c>
       <c r="C20" s="20" t="inlineStr">
         <is>
-          <t>Adeia Inc.</t>
+          <t>Evolv Technologies Holdings, Inc.</t>
         </is>
       </c>
       <c r="D20" s="48" t="inlineStr">
         <is>
-          <t>Breakout</t>
+          <t>Small Cap</t>
         </is>
       </c>
       <c r="E20" s="23" t="inlineStr">
@@ -3774,13 +3774,13 @@
         <v>0.03</v>
       </c>
       <c r="G20" s="71" t="n">
-        <v>0.036</v>
+        <v>0.03</v>
       </c>
       <c r="H20" s="72" t="n">
-        <v>3600</v>
+        <v>3000</v>
       </c>
       <c r="I20" s="73" t="n">
-        <v>132</v>
+        <v>589</v>
       </c>
       <c r="J20" s="74" t="inlineStr">
         <is>
@@ -3791,12 +3791,12 @@
     <row r="21" ht="16" customHeight="1">
       <c r="B21" s="25" t="inlineStr">
         <is>
-          <t>DCI</t>
+          <t>CACI</t>
         </is>
       </c>
       <c r="C21" s="26" t="inlineStr">
         <is>
-          <t>Donaldson Company, Inc.</t>
+          <t>CACI International Inc</t>
         </is>
       </c>
       <c r="D21" s="49" t="inlineStr">
@@ -3819,28 +3819,28 @@
         <v>3600</v>
       </c>
       <c r="I21" s="77" t="n">
-        <v>39</v>
+        <v>5</v>
       </c>
       <c r="J21" s="78" t="inlineStr">
         <is>
-          <t>Medium-Low risk</t>
+          <t>Medium-High risk</t>
         </is>
       </c>
     </row>
     <row r="22" ht="16" customHeight="1">
       <c r="B22" s="19" t="inlineStr">
         <is>
-          <t>ARRY</t>
+          <t>SODI</t>
         </is>
       </c>
       <c r="C22" s="20" t="inlineStr">
         <is>
-          <t>Array Technologies, Inc.</t>
+          <t>Solitron Devices, Inc.</t>
         </is>
       </c>
       <c r="D22" s="48" t="inlineStr">
         <is>
-          <t>Small Cap</t>
+          <t>Nano Cap</t>
         </is>
       </c>
       <c r="E22" s="23" t="inlineStr">
@@ -3852,29 +3852,29 @@
         <v>0.03</v>
       </c>
       <c r="G22" s="71" t="n">
-        <v>0.03</v>
+        <v>0.018</v>
       </c>
       <c r="H22" s="72" t="n">
-        <v>3000</v>
+        <v>1800</v>
       </c>
       <c r="I22" s="73" t="n">
-        <v>621</v>
+        <v>55</v>
       </c>
       <c r="J22" s="74" t="inlineStr">
         <is>
-          <t>Medium-High risk</t>
+          <t>High risk</t>
         </is>
       </c>
     </row>
     <row r="23" ht="16" customHeight="1">
       <c r="B23" s="25" t="inlineStr">
         <is>
-          <t>EVLV</t>
+          <t>GHM</t>
         </is>
       </c>
       <c r="C23" s="26" t="inlineStr">
         <is>
-          <t>Evolv Technologies Holdings, Inc.</t>
+          <t>Graham Corporation</t>
         </is>
       </c>
       <c r="D23" s="49" t="inlineStr">
@@ -3897,7 +3897,7 @@
         <v>3000</v>
       </c>
       <c r="I23" s="77" t="n">
-        <v>589</v>
+        <v>33</v>
       </c>
       <c r="J23" s="78" t="inlineStr">
         <is>
@@ -3908,17 +3908,17 @@
     <row r="24" ht="16" customHeight="1">
       <c r="B24" s="19" t="inlineStr">
         <is>
-          <t>CACI</t>
+          <t>ADTN</t>
         </is>
       </c>
       <c r="C24" s="20" t="inlineStr">
         <is>
-          <t>CACI International Inc</t>
+          <t>ADTRAN Holdings Inc.</t>
         </is>
       </c>
       <c r="D24" s="48" t="inlineStr">
         <is>
-          <t>Breakout</t>
+          <t>Small Cap</t>
         </is>
       </c>
       <c r="E24" s="23" t="inlineStr">
@@ -3930,29 +3930,25 @@
         <v>0.03</v>
       </c>
       <c r="G24" s="71" t="n">
-        <v>0.036</v>
+        <v>0.03</v>
       </c>
       <c r="H24" s="72" t="n">
-        <v>3600</v>
+        <v>3000</v>
       </c>
       <c r="I24" s="73" t="n">
-        <v>5</v>
-      </c>
-      <c r="J24" s="74" t="inlineStr">
-        <is>
-          <t>Medium-High risk</t>
-        </is>
-      </c>
+        <v>398</v>
+      </c>
+      <c r="J24" s="74" t="inlineStr"/>
     </row>
     <row r="25" ht="16" customHeight="1">
       <c r="B25" s="25" t="inlineStr">
         <is>
-          <t>SODI</t>
+          <t>INTT</t>
         </is>
       </c>
       <c r="C25" s="26" t="inlineStr">
         <is>
-          <t>Solitron Devices, Inc.</t>
+          <t>inTEST Corporation</t>
         </is>
       </c>
       <c r="D25" s="49" t="inlineStr">
@@ -3975,28 +3971,28 @@
         <v>1800</v>
       </c>
       <c r="I25" s="77" t="n">
-        <v>55</v>
+        <v>155</v>
       </c>
       <c r="J25" s="78" t="inlineStr">
         <is>
-          <t>High risk</t>
+          <t>Medium-High risk</t>
         </is>
       </c>
     </row>
     <row r="26" ht="16" customHeight="1">
       <c r="B26" s="19" t="inlineStr">
         <is>
-          <t>GHM</t>
+          <t>MRCY</t>
         </is>
       </c>
       <c r="C26" s="20" t="inlineStr">
         <is>
-          <t>Graham Corporation</t>
+          <t>Mercury Systems, Inc.</t>
         </is>
       </c>
       <c r="D26" s="48" t="inlineStr">
         <is>
-          <t>Small Cap</t>
+          <t>Breakout</t>
         </is>
       </c>
       <c r="E26" s="23" t="inlineStr">
@@ -4008,13 +4004,13 @@
         <v>0.03</v>
       </c>
       <c r="G26" s="71" t="n">
-        <v>0.03</v>
+        <v>0.036</v>
       </c>
       <c r="H26" s="72" t="n">
-        <v>3000</v>
+        <v>3600</v>
       </c>
       <c r="I26" s="73" t="n">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="J26" s="74" t="inlineStr">
         <is>
@@ -4025,17 +4021,17 @@
     <row r="27" ht="16" customHeight="1">
       <c r="B27" s="25" t="inlineStr">
         <is>
-          <t>NNDM</t>
+          <t>BRC</t>
         </is>
       </c>
       <c r="C27" s="26" t="inlineStr">
         <is>
-          <t>Nano Dimension Ltd.</t>
+          <t>Brady Corporation</t>
         </is>
       </c>
       <c r="D27" s="49" t="inlineStr">
         <is>
-          <t>Small Cap</t>
+          <t>Breakout</t>
         </is>
       </c>
       <c r="E27" s="23" t="inlineStr">
@@ -4047,34 +4043,34 @@
         <v>0.03</v>
       </c>
       <c r="G27" s="75" t="n">
-        <v>0.03</v>
+        <v>0.036</v>
       </c>
       <c r="H27" s="76" t="n">
-        <v>3000</v>
+        <v>3600</v>
       </c>
       <c r="I27" s="77" t="n">
-        <v>1935</v>
+        <v>40</v>
       </c>
       <c r="J27" s="78" t="inlineStr">
         <is>
-          <t>Medium-High risk</t>
+          <t>Medium-Low risk</t>
         </is>
       </c>
     </row>
     <row r="28" ht="16" customHeight="1">
       <c r="B28" s="19" t="inlineStr">
         <is>
-          <t>ADTN</t>
+          <t>RELL</t>
         </is>
       </c>
       <c r="C28" s="20" t="inlineStr">
         <is>
-          <t>ADTRAN Holdings Inc.</t>
+          <t>Richardson Electronics, Ltd.</t>
         </is>
       </c>
       <c r="D28" s="48" t="inlineStr">
         <is>
-          <t>Small Cap</t>
+          <t>Nano Cap</t>
         </is>
       </c>
       <c r="E28" s="23" t="inlineStr">
@@ -4086,30 +4082,34 @@
         <v>0.03</v>
       </c>
       <c r="G28" s="71" t="n">
-        <v>0.03</v>
+        <v>0.018</v>
       </c>
       <c r="H28" s="72" t="n">
-        <v>3000</v>
+        <v>1800</v>
       </c>
       <c r="I28" s="73" t="n">
-        <v>398</v>
-      </c>
-      <c r="J28" s="74" t="inlineStr"/>
+        <v>102</v>
+      </c>
+      <c r="J28" s="74" t="inlineStr">
+        <is>
+          <t>Medium-High risk</t>
+        </is>
+      </c>
     </row>
     <row r="29" ht="16" customHeight="1">
       <c r="B29" s="25" t="inlineStr">
         <is>
-          <t>INTT</t>
+          <t>ARLO</t>
         </is>
       </c>
       <c r="C29" s="26" t="inlineStr">
         <is>
-          <t>inTEST Corporation</t>
+          <t>Arlo Technologies, Inc.</t>
         </is>
       </c>
       <c r="D29" s="49" t="inlineStr">
         <is>
-          <t>Nano Cap</t>
+          <t>Small Cap</t>
         </is>
       </c>
       <c r="E29" s="23" t="inlineStr">
@@ -4121,13 +4121,13 @@
         <v>0.03</v>
       </c>
       <c r="G29" s="75" t="n">
-        <v>0.018</v>
+        <v>0.03</v>
       </c>
       <c r="H29" s="76" t="n">
-        <v>1800</v>
+        <v>3000</v>
       </c>
       <c r="I29" s="77" t="n">
-        <v>155</v>
+        <v>215</v>
       </c>
       <c r="J29" s="78" t="inlineStr">
         <is>
@@ -4138,17 +4138,17 @@
     <row r="30" ht="16" customHeight="1">
       <c r="B30" s="19" t="inlineStr">
         <is>
-          <t>RELL</t>
+          <t>CE</t>
         </is>
       </c>
       <c r="C30" s="20" t="inlineStr">
         <is>
-          <t>Richardson Electronics, Ltd.</t>
+          <t>Celanese Corporation</t>
         </is>
       </c>
       <c r="D30" s="48" t="inlineStr">
         <is>
-          <t>Nano Cap</t>
+          <t>Breakout</t>
         </is>
       </c>
       <c r="E30" s="23" t="inlineStr">
@@ -4160,34 +4160,34 @@
         <v>0.03</v>
       </c>
       <c r="G30" s="71" t="n">
-        <v>0.018</v>
+        <v>0.036</v>
       </c>
       <c r="H30" s="72" t="n">
-        <v>1800</v>
+        <v>3600</v>
       </c>
       <c r="I30" s="73" t="n">
-        <v>102</v>
+        <v>80</v>
       </c>
       <c r="J30" s="74" t="inlineStr">
         <is>
-          <t>Medium-High risk</t>
+          <t>High risk</t>
         </is>
       </c>
     </row>
     <row r="31" ht="16" customHeight="1">
       <c r="B31" s="25" t="inlineStr">
         <is>
-          <t>BRC</t>
+          <t>TRC</t>
         </is>
       </c>
       <c r="C31" s="26" t="inlineStr">
         <is>
-          <t>Brady Corporation</t>
+          <t>Tejon Ranch Co.</t>
         </is>
       </c>
       <c r="D31" s="49" t="inlineStr">
         <is>
-          <t>Breakout</t>
+          <t>Small Cap</t>
         </is>
       </c>
       <c r="E31" s="23" t="inlineStr">
@@ -4199,29 +4199,29 @@
         <v>0.03</v>
       </c>
       <c r="G31" s="75" t="n">
-        <v>0.036</v>
+        <v>0.03</v>
       </c>
       <c r="H31" s="76" t="n">
-        <v>3600</v>
+        <v>3000</v>
       </c>
       <c r="I31" s="77" t="n">
-        <v>40</v>
+        <v>181</v>
       </c>
       <c r="J31" s="78" t="inlineStr">
         <is>
-          <t>Medium-Low risk</t>
+          <t>High risk</t>
         </is>
       </c>
     </row>
     <row r="32" ht="16" customHeight="1">
       <c r="B32" s="19" t="inlineStr">
         <is>
-          <t>MRCY</t>
+          <t>LYFT</t>
         </is>
       </c>
       <c r="C32" s="20" t="inlineStr">
         <is>
-          <t>Mercury Systems, Inc.</t>
+          <t>Lyft, Inc.</t>
         </is>
       </c>
       <c r="D32" s="48" t="inlineStr">
@@ -4244,23 +4244,23 @@
         <v>3600</v>
       </c>
       <c r="I32" s="73" t="n">
-        <v>42</v>
+        <v>223</v>
       </c>
       <c r="J32" s="74" t="inlineStr">
         <is>
-          <t>Medium-High risk</t>
+          <t>Medium-Low risk</t>
         </is>
       </c>
     </row>
     <row r="33" ht="16" customHeight="1">
       <c r="B33" s="25" t="inlineStr">
         <is>
-          <t>CE</t>
+          <t>RUN</t>
         </is>
       </c>
       <c r="C33" s="26" t="inlineStr">
         <is>
-          <t>Celanese Corporation</t>
+          <t>Sunrun Inc.</t>
         </is>
       </c>
       <c r="D33" s="49" t="inlineStr">
@@ -4283,28 +4283,28 @@
         <v>3600</v>
       </c>
       <c r="I33" s="77" t="n">
-        <v>80</v>
+        <v>392</v>
       </c>
       <c r="J33" s="78" t="inlineStr">
         <is>
-          <t>High risk</t>
+          <t>Medium-Low risk</t>
         </is>
       </c>
     </row>
     <row r="34" ht="16" customHeight="1">
       <c r="B34" s="19" t="inlineStr">
         <is>
-          <t>RUN</t>
+          <t>INOD</t>
         </is>
       </c>
       <c r="C34" s="20" t="inlineStr">
         <is>
-          <t>Sunrun Inc.</t>
+          <t>Innodata Inc.</t>
         </is>
       </c>
       <c r="D34" s="48" t="inlineStr">
         <is>
-          <t>Breakout</t>
+          <t>Small Cap</t>
         </is>
       </c>
       <c r="E34" s="23" t="inlineStr">
@@ -4316,29 +4316,29 @@
         <v>0.03</v>
       </c>
       <c r="G34" s="71" t="n">
-        <v>0.036</v>
+        <v>0.03</v>
       </c>
       <c r="H34" s="72" t="n">
-        <v>3600</v>
+        <v>3000</v>
       </c>
       <c r="I34" s="73" t="n">
-        <v>392</v>
+        <v>53</v>
       </c>
       <c r="J34" s="74" t="inlineStr">
         <is>
-          <t>Medium-Low risk</t>
+          <t>Medium-High risk</t>
         </is>
       </c>
     </row>
     <row r="35" ht="16" customHeight="1">
       <c r="B35" s="25" t="inlineStr">
         <is>
-          <t>LYFT</t>
+          <t>ITRI</t>
         </is>
       </c>
       <c r="C35" s="26" t="inlineStr">
         <is>
-          <t>Lyft, Inc.</t>
+          <t>Itron, Inc.</t>
         </is>
       </c>
       <c r="D35" s="49" t="inlineStr">
@@ -4361,7 +4361,7 @@
         <v>3600</v>
       </c>
       <c r="I35" s="77" t="n">
-        <v>223</v>
+        <v>37</v>
       </c>
       <c r="J35" s="78" t="inlineStr">
         <is>
@@ -4372,17 +4372,17 @@
     <row r="36" ht="16" customHeight="1">
       <c r="B36" s="19" t="inlineStr">
         <is>
-          <t>KN</t>
+          <t>RFIL</t>
         </is>
       </c>
       <c r="C36" s="20" t="inlineStr">
         <is>
-          <t>Knowles Corporation</t>
+          <t>RF Industries, Ltd.</t>
         </is>
       </c>
       <c r="D36" s="48" t="inlineStr">
         <is>
-          <t>Breakout</t>
+          <t>Nano Cap</t>
         </is>
       </c>
       <c r="E36" s="23" t="inlineStr">
@@ -4394,34 +4394,34 @@
         <v>0.03</v>
       </c>
       <c r="G36" s="71" t="n">
-        <v>0.036</v>
+        <v>0.018</v>
       </c>
       <c r="H36" s="72" t="n">
-        <v>3600</v>
+        <v>1800</v>
       </c>
       <c r="I36" s="73" t="n">
-        <v>100</v>
+        <v>165</v>
       </c>
       <c r="J36" s="74" t="inlineStr">
         <is>
-          <t>Medium-Low risk</t>
+          <t>Medium-High risk</t>
         </is>
       </c>
     </row>
     <row r="37" ht="16" customHeight="1">
       <c r="B37" s="25" t="inlineStr">
         <is>
-          <t>RFIL</t>
+          <t>CDRE</t>
         </is>
       </c>
       <c r="C37" s="26" t="inlineStr">
         <is>
-          <t>RF Industries, Ltd.</t>
+          <t>Cadre Holdings, Inc.</t>
         </is>
       </c>
       <c r="D37" s="49" t="inlineStr">
         <is>
-          <t>Nano Cap</t>
+          <t>Small Cap</t>
         </is>
       </c>
       <c r="E37" s="23" t="inlineStr">
@@ -4433,13 +4433,13 @@
         <v>0.03</v>
       </c>
       <c r="G37" s="75" t="n">
-        <v>0.018</v>
+        <v>0.03</v>
       </c>
       <c r="H37" s="76" t="n">
-        <v>1800</v>
+        <v>3000</v>
       </c>
       <c r="I37" s="77" t="n">
-        <v>165</v>
+        <v>100</v>
       </c>
       <c r="J37" s="78" t="inlineStr">
         <is>
@@ -4645,12 +4645,12 @@
     <row r="43" ht="16" customHeight="1">
       <c r="B43" s="25" t="inlineStr">
         <is>
-          <t>QUIK</t>
+          <t>KVHI</t>
         </is>
       </c>
       <c r="C43" s="26" t="inlineStr">
         <is>
-          <t>QuickLogic Corporation</t>
+          <t>KVH Industries, Inc.</t>
         </is>
       </c>
       <c r="D43" s="49" t="inlineStr">
@@ -4673,11 +4673,11 @@
         <v>900</v>
       </c>
       <c r="I43" s="77" t="n">
-        <v>80</v>
+        <v>126</v>
       </c>
       <c r="J43" s="78" t="inlineStr">
         <is>
-          <t>High risk</t>
+          <t>Medium-High risk</t>
         </is>
       </c>
     </row>
@@ -4692,7 +4692,7 @@
       <c r="E45" s="80" t="n"/>
       <c r="F45" s="80" t="n"/>
       <c r="G45" s="81" t="n">
-        <v>0.8789999999999999</v>
+        <v>0.879</v>
       </c>
       <c r="H45" s="82" t="n">
         <v>87900</v>
@@ -4709,7 +4709,7 @@
       <c r="E46" s="80" t="n"/>
       <c r="F46" s="80" t="n"/>
       <c r="G46" s="83" t="n">
-        <v>0.1210000000000001</v>
+        <v>0.1209999999999999</v>
       </c>
       <c r="H46" s="84" t="n">
         <v>12100</v>
@@ -4889,79 +4889,79 @@
         </is>
       </c>
       <c r="M54" t="n">
-        <v>12.10000000000001</v>
+        <v>12.09999999999999</v>
       </c>
     </row>
     <row r="55" ht="16" customHeight="1">
       <c r="B55" s="19" t="inlineStr">
         <is>
-          <t>LXFR</t>
+          <t>ADEA</t>
         </is>
       </c>
       <c r="C55" s="21" t="n">
-        <v>1500</v>
+        <v>1800</v>
       </c>
       <c r="D55" s="85" t="n">
-        <v>3000</v>
+        <v>3600</v>
       </c>
       <c r="E55" s="21" t="n">
-        <v>7500</v>
+        <v>9000.000000000002</v>
       </c>
       <c r="F55" s="21" t="n">
-        <v>15000</v>
+        <v>18000</v>
       </c>
       <c r="G55" s="21" t="n">
-        <v>30000</v>
+        <v>36000.00000000001</v>
       </c>
     </row>
     <row r="56" ht="16" customHeight="1">
       <c r="B56" s="25" t="inlineStr">
         <is>
-          <t>CLFD</t>
+          <t>DCI</t>
         </is>
       </c>
       <c r="C56" s="27" t="n">
-        <v>1500</v>
+        <v>1800</v>
       </c>
       <c r="D56" s="85" t="n">
-        <v>3000</v>
+        <v>3600</v>
       </c>
       <c r="E56" s="27" t="n">
-        <v>7500</v>
+        <v>9000.000000000002</v>
       </c>
       <c r="F56" s="27" t="n">
-        <v>15000</v>
+        <v>18000</v>
       </c>
       <c r="G56" s="27" t="n">
-        <v>30000</v>
+        <v>36000.00000000001</v>
       </c>
     </row>
     <row r="57" ht="16" customHeight="1">
       <c r="B57" s="19" t="inlineStr">
         <is>
-          <t>ADEA</t>
+          <t>EVLV</t>
         </is>
       </c>
       <c r="C57" s="21" t="n">
-        <v>1800</v>
+        <v>1500</v>
       </c>
       <c r="D57" s="85" t="n">
-        <v>3600</v>
+        <v>3000</v>
       </c>
       <c r="E57" s="21" t="n">
-        <v>9000.000000000002</v>
+        <v>7500</v>
       </c>
       <c r="F57" s="21" t="n">
-        <v>18000</v>
+        <v>15000</v>
       </c>
       <c r="G57" s="21" t="n">
-        <v>36000.00000000001</v>
+        <v>30000</v>
       </c>
     </row>
     <row r="58" ht="16" customHeight="1">
       <c r="B58" s="25" t="inlineStr">
         <is>
-          <t>DCI</t>
+          <t>CACI</t>
         </is>
       </c>
       <c r="C58" s="27" t="n">
@@ -4983,29 +4983,29 @@
     <row r="59" ht="16" customHeight="1">
       <c r="B59" s="19" t="inlineStr">
         <is>
-          <t>ARRY</t>
+          <t>SODI</t>
         </is>
       </c>
       <c r="C59" s="21" t="n">
-        <v>1500</v>
+        <v>900.0000000000001</v>
       </c>
       <c r="D59" s="85" t="n">
-        <v>3000</v>
+        <v>1800</v>
       </c>
       <c r="E59" s="21" t="n">
-        <v>7500</v>
+        <v>4500.000000000001</v>
       </c>
       <c r="F59" s="21" t="n">
-        <v>15000</v>
+        <v>9000.000000000002</v>
       </c>
       <c r="G59" s="21" t="n">
-        <v>30000</v>
+        <v>18000</v>
       </c>
     </row>
     <row r="60" ht="16" customHeight="1">
       <c r="B60" s="25" t="inlineStr">
         <is>
-          <t>EVLV</t>
+          <t>GHM</t>
         </is>
       </c>
       <c r="C60" s="27" t="n">
@@ -5321,25 +5321,25 @@
         </is>
       </c>
       <c r="E14" s="34" t="n">
-        <v>79.2</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="F14" s="34" t="n">
         <v>85.40000000000001</v>
       </c>
       <c r="G14" s="34" t="n">
-        <v>75.5</v>
+        <v>75.8</v>
       </c>
       <c r="H14" s="34" t="n">
-        <v>71.40000000000001</v>
+        <v>71.7</v>
       </c>
       <c r="I14" s="34" t="n">
         <v>85.40000000000001</v>
       </c>
       <c r="J14" s="34" t="n">
-        <v>71.40000000000001</v>
+        <v>71.7</v>
       </c>
       <c r="K14" s="34" t="n">
-        <v>14</v>
+        <v>13.7</v>
       </c>
       <c r="L14" s="23" t="inlineStr">
         <is>
@@ -5364,25 +5364,25 @@
         </is>
       </c>
       <c r="E15" s="41" t="n">
-        <v>78.7</v>
+        <v>78.5</v>
       </c>
       <c r="F15" s="41" t="n">
         <v>85.40000000000001</v>
       </c>
       <c r="G15" s="41" t="n">
-        <v>74.7</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="H15" s="41" t="n">
-        <v>69.90000000000001</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="I15" s="41" t="n">
         <v>85.40000000000001</v>
       </c>
       <c r="J15" s="41" t="n">
-        <v>69.90000000000001</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="K15" s="41" t="n">
-        <v>15.5</v>
+        <v>15.80000000000001</v>
       </c>
       <c r="L15" s="23" t="inlineStr">
         <is>
@@ -5407,25 +5407,25 @@
         </is>
       </c>
       <c r="E16" s="34" t="n">
-        <v>77.2</v>
+        <v>77.5</v>
       </c>
       <c r="F16" s="34" t="n">
         <v>83.90000000000001</v>
       </c>
       <c r="G16" s="34" t="n">
-        <v>73.2</v>
+        <v>73.7</v>
       </c>
       <c r="H16" s="34" t="n">
-        <v>69.8</v>
+        <v>70.3</v>
       </c>
       <c r="I16" s="34" t="n">
         <v>83.90000000000001</v>
       </c>
       <c r="J16" s="34" t="n">
-        <v>69.8</v>
+        <v>70.3</v>
       </c>
       <c r="K16" s="34" t="n">
-        <v>14.10000000000001</v>
+        <v>13.60000000000001</v>
       </c>
       <c r="L16" s="23" t="inlineStr">
         <is>
@@ -5456,19 +5456,19 @@
         <v>82.59999999999999</v>
       </c>
       <c r="G17" s="41" t="n">
-        <v>70.7</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="H17" s="41" t="n">
-        <v>67</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="I17" s="41" t="n">
         <v>82.59999999999999</v>
       </c>
       <c r="J17" s="41" t="n">
-        <v>67</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="K17" s="41" t="n">
-        <v>15.59999999999999</v>
+        <v>15.69999999999999</v>
       </c>
       <c r="L17" s="23" t="inlineStr">
         <is>
@@ -5479,39 +5479,39 @@
     <row r="18" ht="16" customHeight="1">
       <c r="B18" s="19" t="inlineStr">
         <is>
-          <t>LXFR</t>
+          <t>ADEA</t>
         </is>
       </c>
       <c r="C18" s="20" t="inlineStr">
         <is>
-          <t>Luxfer Holdings PLC</t>
+          <t>Adeia Inc.</t>
         </is>
       </c>
       <c r="D18" s="48" t="inlineStr">
         <is>
-          <t>Small Cap</t>
+          <t>Breakout</t>
         </is>
       </c>
       <c r="E18" s="34" t="n">
-        <v>74</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="F18" s="34" t="n">
-        <v>79</v>
+        <v>75.09999999999999</v>
       </c>
       <c r="G18" s="34" t="n">
-        <v>71</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="H18" s="34" t="n">
-        <v>62.2</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="I18" s="34" t="n">
-        <v>79</v>
+        <v>75.09999999999999</v>
       </c>
       <c r="J18" s="34" t="n">
-        <v>62.2</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="K18" s="34" t="n">
-        <v>16.8</v>
+        <v>10.19999999999999</v>
       </c>
       <c r="L18" s="23" t="inlineStr">
         <is>
@@ -5522,98 +5522,98 @@
     <row r="19" ht="16" customHeight="1">
       <c r="B19" s="25" t="inlineStr">
         <is>
-          <t>CLFD</t>
+          <t>DCI</t>
         </is>
       </c>
       <c r="C19" s="26" t="inlineStr">
         <is>
-          <t>Clearfield, Inc.</t>
+          <t>Donaldson Company, Inc.</t>
         </is>
       </c>
       <c r="D19" s="49" t="inlineStr">
         <is>
-          <t>Small Cap</t>
+          <t>Breakout</t>
         </is>
       </c>
       <c r="E19" s="41" t="n">
-        <v>73.90000000000001</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="F19" s="41" t="n">
-        <v>68.8</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="G19" s="41" t="n">
-        <v>77</v>
+        <v>69.2</v>
       </c>
       <c r="H19" s="41" t="n">
-        <v>76.7</v>
+        <v>59.9</v>
       </c>
       <c r="I19" s="41" t="n">
-        <v>77</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="J19" s="41" t="n">
-        <v>68.8</v>
+        <v>59.9</v>
       </c>
       <c r="K19" s="41" t="n">
-        <v>8.200000000000003</v>
-      </c>
-      <c r="L19" s="90" t="inlineStr">
-        <is>
-          <t>Stable</t>
+        <v>19.50000000000001</v>
+      </c>
+      <c r="L19" s="23" t="inlineStr">
+        <is>
+          <t>Moderate</t>
         </is>
       </c>
     </row>
     <row r="20" ht="16" customHeight="1">
       <c r="B20" s="19" t="inlineStr">
         <is>
-          <t>ADEA</t>
+          <t>EVLV</t>
         </is>
       </c>
       <c r="C20" s="20" t="inlineStr">
         <is>
-          <t>Adeia Inc.</t>
+          <t>Evolv Technologies Holdings, Inc.</t>
         </is>
       </c>
       <c r="D20" s="48" t="inlineStr">
         <is>
-          <t>Breakout</t>
+          <t>Small Cap</t>
         </is>
       </c>
       <c r="E20" s="34" t="n">
-        <v>73.40000000000001</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="F20" s="34" t="n">
-        <v>75.09999999999999</v>
+        <v>74</v>
       </c>
       <c r="G20" s="34" t="n">
-        <v>72.40000000000001</v>
+        <v>71</v>
       </c>
       <c r="H20" s="34" t="n">
-        <v>64.90000000000001</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="I20" s="34" t="n">
-        <v>75.09999999999999</v>
+        <v>74</v>
       </c>
       <c r="J20" s="34" t="n">
-        <v>64.90000000000001</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="K20" s="34" t="n">
-        <v>10.19999999999999</v>
-      </c>
-      <c r="L20" s="23" t="inlineStr">
-        <is>
-          <t>Moderate</t>
+        <v>5.599999999999994</v>
+      </c>
+      <c r="L20" s="90" t="inlineStr">
+        <is>
+          <t>Stable</t>
         </is>
       </c>
     </row>
     <row r="21" ht="16" customHeight="1">
       <c r="B21" s="25" t="inlineStr">
         <is>
-          <t>DCI</t>
+          <t>CACI</t>
         </is>
       </c>
       <c r="C21" s="26" t="inlineStr">
         <is>
-          <t>Donaldson Company, Inc.</t>
+          <t>CACI International Inc</t>
         </is>
       </c>
       <c r="D21" s="49" t="inlineStr">
@@ -5622,25 +5622,25 @@
         </is>
       </c>
       <c r="E21" s="41" t="n">
-        <v>73</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="F21" s="41" t="n">
-        <v>79.40000000000001</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="G21" s="41" t="n">
-        <v>69.2</v>
+        <v>68.5</v>
       </c>
       <c r="H21" s="41" t="n">
-        <v>59.9</v>
+        <v>61.3</v>
       </c>
       <c r="I21" s="41" t="n">
-        <v>79.40000000000001</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="J21" s="41" t="n">
-        <v>59.9</v>
+        <v>61.3</v>
       </c>
       <c r="K21" s="41" t="n">
-        <v>19.50000000000001</v>
+        <v>15.60000000000001</v>
       </c>
       <c r="L21" s="23" t="inlineStr">
         <is>
@@ -5651,39 +5651,39 @@
     <row r="22" ht="16" customHeight="1">
       <c r="B22" s="19" t="inlineStr">
         <is>
-          <t>ARRY</t>
+          <t>SODI</t>
         </is>
       </c>
       <c r="C22" s="20" t="inlineStr">
         <is>
-          <t>Array Technologies, Inc.</t>
+          <t>Solitron Devices, Inc.</t>
         </is>
       </c>
       <c r="D22" s="48" t="inlineStr">
         <is>
-          <t>Small Cap</t>
+          <t>Nano Cap</t>
         </is>
       </c>
       <c r="E22" s="34" t="n">
-        <v>72.59999999999999</v>
+        <v>70.8</v>
       </c>
       <c r="F22" s="34" t="n">
-        <v>78.09999999999999</v>
+        <v>68.09999999999999</v>
       </c>
       <c r="G22" s="34" t="n">
-        <v>69.3</v>
+        <v>72.5</v>
       </c>
       <c r="H22" s="34" t="n">
-        <v>64.09999999999999</v>
+        <v>81.3</v>
       </c>
       <c r="I22" s="34" t="n">
-        <v>78.09999999999999</v>
+        <v>81.3</v>
       </c>
       <c r="J22" s="34" t="n">
-        <v>64.09999999999999</v>
+        <v>68.09999999999999</v>
       </c>
       <c r="K22" s="34" t="n">
-        <v>14</v>
+        <v>13.2</v>
       </c>
       <c r="L22" s="23" t="inlineStr">
         <is>
@@ -5694,12 +5694,12 @@
     <row r="23" ht="16" customHeight="1">
       <c r="B23" s="25" t="inlineStr">
         <is>
-          <t>EVLV</t>
+          <t>GHM</t>
         </is>
       </c>
       <c r="C23" s="26" t="inlineStr">
         <is>
-          <t>Evolv Technologies Holdings, Inc.</t>
+          <t>Graham Corporation</t>
         </is>
       </c>
       <c r="D23" s="49" t="inlineStr">
@@ -5708,68 +5708,68 @@
         </is>
       </c>
       <c r="E23" s="41" t="n">
-        <v>72.09999999999999</v>
+        <v>70.7</v>
       </c>
       <c r="F23" s="41" t="n">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="G23" s="41" t="n">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="H23" s="41" t="n">
-        <v>68.40000000000001</v>
+        <v>61</v>
       </c>
       <c r="I23" s="41" t="n">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="J23" s="41" t="n">
-        <v>68.40000000000001</v>
+        <v>61</v>
       </c>
       <c r="K23" s="41" t="n">
-        <v>5.599999999999994</v>
-      </c>
-      <c r="L23" s="90" t="inlineStr">
-        <is>
-          <t>Stable</t>
+        <v>16</v>
+      </c>
+      <c r="L23" s="23" t="inlineStr">
+        <is>
+          <t>Moderate</t>
         </is>
       </c>
     </row>
     <row r="24" ht="16" customHeight="1">
       <c r="B24" s="19" t="inlineStr">
         <is>
-          <t>CACI</t>
+          <t>ADTN</t>
         </is>
       </c>
       <c r="C24" s="20" t="inlineStr">
         <is>
-          <t>CACI International Inc</t>
+          <t>ADTRAN Holdings Inc.</t>
         </is>
       </c>
       <c r="D24" s="48" t="inlineStr">
         <is>
-          <t>Breakout</t>
+          <t>Small Cap</t>
         </is>
       </c>
       <c r="E24" s="34" t="n">
-        <v>71.59999999999999</v>
+        <v>70.5</v>
       </c>
       <c r="F24" s="34" t="n">
-        <v>76.90000000000001</v>
+        <v>76.7</v>
       </c>
       <c r="G24" s="34" t="n">
-        <v>68.40000000000001</v>
+        <v>66.8</v>
       </c>
       <c r="H24" s="34" t="n">
-        <v>61.2</v>
+        <v>56.8</v>
       </c>
       <c r="I24" s="34" t="n">
-        <v>76.90000000000001</v>
+        <v>76.7</v>
       </c>
       <c r="J24" s="34" t="n">
-        <v>61.2</v>
+        <v>56.8</v>
       </c>
       <c r="K24" s="34" t="n">
-        <v>15.7</v>
+        <v>19.90000000000001</v>
       </c>
       <c r="L24" s="23" t="inlineStr">
         <is>
@@ -5780,12 +5780,12 @@
     <row r="25" ht="16" customHeight="1">
       <c r="B25" s="25" t="inlineStr">
         <is>
-          <t>SODI</t>
+          <t>INTT</t>
         </is>
       </c>
       <c r="C25" s="26" t="inlineStr">
         <is>
-          <t>Solitron Devices, Inc.</t>
+          <t>inTEST Corporation</t>
         </is>
       </c>
       <c r="D25" s="49" t="inlineStr">
@@ -5794,197 +5794,197 @@
         </is>
       </c>
       <c r="E25" s="41" t="n">
-        <v>70.8</v>
+        <v>70.2</v>
       </c>
       <c r="F25" s="41" t="n">
-        <v>68.09999999999999</v>
+        <v>71.2</v>
       </c>
       <c r="G25" s="41" t="n">
-        <v>72.5</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="H25" s="41" t="n">
-        <v>81.3</v>
+        <v>74.5</v>
       </c>
       <c r="I25" s="41" t="n">
-        <v>81.3</v>
+        <v>74.5</v>
       </c>
       <c r="J25" s="41" t="n">
-        <v>68.09999999999999</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="K25" s="41" t="n">
-        <v>13.2</v>
-      </c>
-      <c r="L25" s="23" t="inlineStr">
-        <is>
-          <t>Moderate</t>
+        <v>4.900000000000006</v>
+      </c>
+      <c r="L25" s="90" t="inlineStr">
+        <is>
+          <t>Stable</t>
         </is>
       </c>
     </row>
     <row r="26" ht="16" customHeight="1">
       <c r="B26" s="19" t="inlineStr">
         <is>
-          <t>GHM</t>
+          <t>MRCY</t>
         </is>
       </c>
       <c r="C26" s="20" t="inlineStr">
         <is>
-          <t>Graham Corporation</t>
+          <t>Mercury Systems, Inc.</t>
         </is>
       </c>
       <c r="D26" s="48" t="inlineStr">
         <is>
-          <t>Small Cap</t>
+          <t>Breakout</t>
         </is>
       </c>
       <c r="E26" s="34" t="n">
-        <v>70.7</v>
+        <v>69.8</v>
       </c>
       <c r="F26" s="34" t="n">
-        <v>77</v>
+        <v>71.2</v>
       </c>
       <c r="G26" s="34" t="n">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="H26" s="34" t="n">
-        <v>61</v>
+        <v>63.1</v>
       </c>
       <c r="I26" s="34" t="n">
-        <v>77</v>
+        <v>71.2</v>
       </c>
       <c r="J26" s="34" t="n">
-        <v>61</v>
+        <v>63.1</v>
       </c>
       <c r="K26" s="34" t="n">
-        <v>16</v>
-      </c>
-      <c r="L26" s="23" t="inlineStr">
-        <is>
-          <t>Moderate</t>
+        <v>8.100000000000001</v>
+      </c>
+      <c r="L26" s="90" t="inlineStr">
+        <is>
+          <t>Stable</t>
         </is>
       </c>
     </row>
     <row r="27" ht="16" customHeight="1">
       <c r="B27" s="25" t="inlineStr">
         <is>
-          <t>NNDM</t>
+          <t>BRC</t>
         </is>
       </c>
       <c r="C27" s="26" t="inlineStr">
         <is>
-          <t>Nano Dimension Ltd.</t>
+          <t>Brady Corporation</t>
         </is>
       </c>
       <c r="D27" s="49" t="inlineStr">
         <is>
-          <t>Small Cap</t>
+          <t>Breakout</t>
         </is>
       </c>
       <c r="E27" s="41" t="n">
-        <v>70.5</v>
+        <v>69.7</v>
       </c>
       <c r="F27" s="41" t="n">
-        <v>71</v>
+        <v>75.2</v>
       </c>
       <c r="G27" s="41" t="n">
-        <v>70.3</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="H27" s="41" t="n">
-        <v>63.9</v>
+        <v>63.3</v>
       </c>
       <c r="I27" s="41" t="n">
-        <v>71</v>
+        <v>75.2</v>
       </c>
       <c r="J27" s="41" t="n">
-        <v>63.9</v>
+        <v>63.3</v>
       </c>
       <c r="K27" s="41" t="n">
-        <v>7.100000000000001</v>
-      </c>
-      <c r="L27" s="90" t="inlineStr">
-        <is>
-          <t>Stable</t>
+        <v>11.90000000000001</v>
+      </c>
+      <c r="L27" s="23" t="inlineStr">
+        <is>
+          <t>Moderate</t>
         </is>
       </c>
     </row>
     <row r="28" ht="16" customHeight="1">
       <c r="B28" s="19" t="inlineStr">
         <is>
-          <t>ADTN</t>
+          <t>RELL</t>
         </is>
       </c>
       <c r="C28" s="20" t="inlineStr">
         <is>
-          <t>ADTRAN Holdings Inc.</t>
+          <t>Richardson Electronics, Ltd.</t>
         </is>
       </c>
       <c r="D28" s="48" t="inlineStr">
         <is>
-          <t>Small Cap</t>
+          <t>Nano Cap</t>
         </is>
       </c>
       <c r="E28" s="34" t="n">
-        <v>70.40000000000001</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="F28" s="34" t="n">
-        <v>76.7</v>
+        <v>67.90000000000001</v>
       </c>
       <c r="G28" s="34" t="n">
-        <v>66.59999999999999</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="H28" s="34" t="n">
-        <v>56.7</v>
+        <v>75</v>
       </c>
       <c r="I28" s="34" t="n">
-        <v>76.7</v>
+        <v>75</v>
       </c>
       <c r="J28" s="34" t="n">
-        <v>56.7</v>
+        <v>67.90000000000001</v>
       </c>
       <c r="K28" s="34" t="n">
-        <v>20</v>
-      </c>
-      <c r="L28" s="45" t="inlineStr">
-        <is>
-          <t>Sensitive</t>
+        <v>7.099999999999994</v>
+      </c>
+      <c r="L28" s="90" t="inlineStr">
+        <is>
+          <t>Stable</t>
         </is>
       </c>
     </row>
     <row r="29" ht="16" customHeight="1">
       <c r="B29" s="25" t="inlineStr">
         <is>
-          <t>INTT</t>
+          <t>ARLO</t>
         </is>
       </c>
       <c r="C29" s="26" t="inlineStr">
         <is>
-          <t>inTEST Corporation</t>
+          <t>Arlo Technologies, Inc.</t>
         </is>
       </c>
       <c r="D29" s="49" t="inlineStr">
         <is>
-          <t>Nano Cap</t>
+          <t>Small Cap</t>
         </is>
       </c>
       <c r="E29" s="41" t="n">
-        <v>70.2</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="F29" s="41" t="n">
-        <v>71.2</v>
+        <v>73.2</v>
       </c>
       <c r="G29" s="41" t="n">
-        <v>69.59999999999999</v>
+        <v>67.40000000000001</v>
       </c>
       <c r="H29" s="41" t="n">
-        <v>74.5</v>
+        <v>64.09999999999999</v>
       </c>
       <c r="I29" s="41" t="n">
-        <v>74.5</v>
+        <v>73.2</v>
       </c>
       <c r="J29" s="41" t="n">
-        <v>69.59999999999999</v>
+        <v>64.09999999999999</v>
       </c>
       <c r="K29" s="41" t="n">
-        <v>4.900000000000006</v>
+        <v>9.100000000000009</v>
       </c>
       <c r="L29" s="90" t="inlineStr">
         <is>
@@ -5995,98 +5995,98 @@
     <row r="30" ht="16" customHeight="1">
       <c r="B30" s="19" t="inlineStr">
         <is>
-          <t>RELL</t>
+          <t>CE</t>
         </is>
       </c>
       <c r="C30" s="20" t="inlineStr">
         <is>
-          <t>Richardson Electronics, Ltd.</t>
+          <t>Celanese Corporation</t>
         </is>
       </c>
       <c r="D30" s="48" t="inlineStr">
         <is>
-          <t>Nano Cap</t>
+          <t>Breakout</t>
         </is>
       </c>
       <c r="E30" s="34" t="n">
-        <v>70</v>
+        <v>69.5</v>
       </c>
       <c r="F30" s="34" t="n">
-        <v>67.90000000000001</v>
+        <v>73.5</v>
       </c>
       <c r="G30" s="34" t="n">
-        <v>71.3</v>
+        <v>67.2</v>
       </c>
       <c r="H30" s="34" t="n">
-        <v>75.7</v>
+        <v>62.2</v>
       </c>
       <c r="I30" s="34" t="n">
-        <v>75.7</v>
+        <v>73.5</v>
       </c>
       <c r="J30" s="34" t="n">
-        <v>67.90000000000001</v>
+        <v>62.2</v>
       </c>
       <c r="K30" s="34" t="n">
-        <v>7.799999999999997</v>
-      </c>
-      <c r="L30" s="90" t="inlineStr">
-        <is>
-          <t>Stable</t>
+        <v>11.3</v>
+      </c>
+      <c r="L30" s="23" t="inlineStr">
+        <is>
+          <t>Moderate</t>
         </is>
       </c>
     </row>
     <row r="31" ht="16" customHeight="1">
       <c r="B31" s="25" t="inlineStr">
         <is>
-          <t>BRC</t>
+          <t>TRC</t>
         </is>
       </c>
       <c r="C31" s="26" t="inlineStr">
         <is>
-          <t>Brady Corporation</t>
+          <t>Tejon Ranch Co.</t>
         </is>
       </c>
       <c r="D31" s="49" t="inlineStr">
         <is>
-          <t>Breakout</t>
+          <t>Small Cap</t>
         </is>
       </c>
       <c r="E31" s="41" t="n">
-        <v>69.90000000000001</v>
+        <v>69.3</v>
       </c>
       <c r="F31" s="41" t="n">
-        <v>75.2</v>
+        <v>69.40000000000001</v>
       </c>
       <c r="G31" s="41" t="n">
-        <v>66.7</v>
+        <v>69.2</v>
       </c>
       <c r="H31" s="41" t="n">
-        <v>63.6</v>
+        <v>75.90000000000001</v>
       </c>
       <c r="I31" s="41" t="n">
-        <v>75.2</v>
+        <v>75.90000000000001</v>
       </c>
       <c r="J31" s="41" t="n">
-        <v>63.6</v>
+        <v>69.2</v>
       </c>
       <c r="K31" s="41" t="n">
-        <v>11.6</v>
-      </c>
-      <c r="L31" s="23" t="inlineStr">
-        <is>
-          <t>Moderate</t>
+        <v>6.700000000000003</v>
+      </c>
+      <c r="L31" s="90" t="inlineStr">
+        <is>
+          <t>Stable</t>
         </is>
       </c>
     </row>
     <row r="32" ht="16" customHeight="1">
       <c r="B32" s="19" t="inlineStr">
         <is>
-          <t>MRCY</t>
+          <t>LYFT</t>
         </is>
       </c>
       <c r="C32" s="20" t="inlineStr">
         <is>
-          <t>Mercury Systems, Inc.</t>
+          <t>Lyft, Inc.</t>
         </is>
       </c>
       <c r="D32" s="48" t="inlineStr">
@@ -6095,41 +6095,41 @@
         </is>
       </c>
       <c r="E32" s="34" t="n">
-        <v>69.8</v>
+        <v>69</v>
       </c>
       <c r="F32" s="34" t="n">
-        <v>71.2</v>
+        <v>77.59999999999999</v>
       </c>
       <c r="G32" s="34" t="n">
-        <v>69</v>
+        <v>63.8</v>
       </c>
       <c r="H32" s="34" t="n">
-        <v>63.1</v>
+        <v>62.6</v>
       </c>
       <c r="I32" s="34" t="n">
-        <v>71.2</v>
+        <v>77.59999999999999</v>
       </c>
       <c r="J32" s="34" t="n">
-        <v>63.1</v>
+        <v>62.6</v>
       </c>
       <c r="K32" s="34" t="n">
-        <v>8.100000000000001</v>
-      </c>
-      <c r="L32" s="90" t="inlineStr">
-        <is>
-          <t>Stable</t>
+        <v>14.99999999999999</v>
+      </c>
+      <c r="L32" s="23" t="inlineStr">
+        <is>
+          <t>Moderate</t>
         </is>
       </c>
     </row>
     <row r="33" ht="16" customHeight="1">
       <c r="B33" s="25" t="inlineStr">
         <is>
-          <t>CE</t>
+          <t>RUN</t>
         </is>
       </c>
       <c r="C33" s="26" t="inlineStr">
         <is>
-          <t>Celanese Corporation</t>
+          <t>Sunrun Inc.</t>
         </is>
       </c>
       <c r="D33" s="49" t="inlineStr">
@@ -6138,68 +6138,68 @@
         </is>
       </c>
       <c r="E33" s="41" t="n">
-        <v>69.5</v>
+        <v>68.90000000000001</v>
       </c>
       <c r="F33" s="41" t="n">
-        <v>73.5</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="G33" s="41" t="n">
-        <v>67.2</v>
+        <v>67.7</v>
       </c>
       <c r="H33" s="41" t="n">
-        <v>62.2</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="I33" s="41" t="n">
-        <v>73.5</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="J33" s="41" t="n">
-        <v>62.2</v>
+        <v>67.7</v>
       </c>
       <c r="K33" s="41" t="n">
-        <v>11.3</v>
-      </c>
-      <c r="L33" s="23" t="inlineStr">
-        <is>
-          <t>Moderate</t>
+        <v>4.899999999999991</v>
+      </c>
+      <c r="L33" s="90" t="inlineStr">
+        <is>
+          <t>Stable</t>
         </is>
       </c>
     </row>
     <row r="34" ht="16" customHeight="1">
       <c r="B34" s="19" t="inlineStr">
         <is>
-          <t>RUN</t>
+          <t>INOD</t>
         </is>
       </c>
       <c r="C34" s="20" t="inlineStr">
         <is>
-          <t>Sunrun Inc.</t>
+          <t>Innodata Inc.</t>
         </is>
       </c>
       <c r="D34" s="48" t="inlineStr">
         <is>
-          <t>Breakout</t>
+          <t>Small Cap</t>
         </is>
       </c>
       <c r="E34" s="34" t="n">
-        <v>69.09999999999999</v>
+        <v>68.2</v>
       </c>
       <c r="F34" s="34" t="n">
-        <v>71.09999999999999</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="G34" s="34" t="n">
-        <v>67.90000000000001</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="H34" s="34" t="n">
-        <v>72.8</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="I34" s="34" t="n">
-        <v>72.8</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="J34" s="34" t="n">
-        <v>67.90000000000001</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="K34" s="34" t="n">
-        <v>4.899999999999991</v>
+        <v>4.5</v>
       </c>
       <c r="L34" s="90" t="inlineStr">
         <is>
@@ -6210,12 +6210,12 @@
     <row r="35" ht="16" customHeight="1">
       <c r="B35" s="25" t="inlineStr">
         <is>
-          <t>LYFT</t>
+          <t>ITRI</t>
         </is>
       </c>
       <c r="C35" s="26" t="inlineStr">
         <is>
-          <t>Lyft, Inc.</t>
+          <t>Itron, Inc.</t>
         </is>
       </c>
       <c r="D35" s="49" t="inlineStr">
@@ -6224,25 +6224,25 @@
         </is>
       </c>
       <c r="E35" s="41" t="n">
-        <v>69.09999999999999</v>
+        <v>68.2</v>
       </c>
       <c r="F35" s="41" t="n">
-        <v>77.59999999999999</v>
+        <v>73.7</v>
       </c>
       <c r="G35" s="41" t="n">
-        <v>64</v>
+        <v>64.8</v>
       </c>
       <c r="H35" s="41" t="n">
-        <v>62.8</v>
+        <v>60.9</v>
       </c>
       <c r="I35" s="41" t="n">
-        <v>77.59999999999999</v>
+        <v>73.7</v>
       </c>
       <c r="J35" s="41" t="n">
-        <v>62.8</v>
+        <v>60.9</v>
       </c>
       <c r="K35" s="41" t="n">
-        <v>14.8</v>
+        <v>12.8</v>
       </c>
       <c r="L35" s="23" t="inlineStr">
         <is>
@@ -6253,39 +6253,39 @@
     <row r="36" ht="16" customHeight="1">
       <c r="B36" s="19" t="inlineStr">
         <is>
-          <t>KN</t>
+          <t>RFIL</t>
         </is>
       </c>
       <c r="C36" s="20" t="inlineStr">
         <is>
-          <t>Knowles Corporation</t>
+          <t>RF Industries, Ltd.</t>
         </is>
       </c>
       <c r="D36" s="48" t="inlineStr">
         <is>
-          <t>Breakout</t>
+          <t>Nano Cap</t>
         </is>
       </c>
       <c r="E36" s="34" t="n">
-        <v>68.2</v>
+        <v>67.09999999999999</v>
       </c>
       <c r="F36" s="34" t="n">
-        <v>69</v>
+        <v>65.7</v>
       </c>
       <c r="G36" s="34" t="n">
-        <v>67.7</v>
+        <v>67.90000000000001</v>
       </c>
       <c r="H36" s="34" t="n">
-        <v>64.7</v>
+        <v>66.8</v>
       </c>
       <c r="I36" s="34" t="n">
-        <v>69</v>
+        <v>67.90000000000001</v>
       </c>
       <c r="J36" s="34" t="n">
-        <v>64.7</v>
+        <v>65.7</v>
       </c>
       <c r="K36" s="34" t="n">
-        <v>4.299999999999997</v>
+        <v>2.200000000000003</v>
       </c>
       <c r="L36" s="90" t="inlineStr">
         <is>
@@ -6296,39 +6296,39 @@
     <row r="37" ht="16" customHeight="1">
       <c r="B37" s="25" t="inlineStr">
         <is>
-          <t>RFIL</t>
+          <t>CDRE</t>
         </is>
       </c>
       <c r="C37" s="26" t="inlineStr">
         <is>
-          <t>RF Industries, Ltd.</t>
+          <t>Cadre Holdings, Inc.</t>
         </is>
       </c>
       <c r="D37" s="49" t="inlineStr">
         <is>
-          <t>Nano Cap</t>
+          <t>Small Cap</t>
         </is>
       </c>
       <c r="E37" s="41" t="n">
-        <v>67.40000000000001</v>
+        <v>67</v>
       </c>
       <c r="F37" s="41" t="n">
-        <v>65.7</v>
+        <v>67.3</v>
       </c>
       <c r="G37" s="41" t="n">
-        <v>68.40000000000001</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="H37" s="41" t="n">
-        <v>67.40000000000001</v>
+        <v>72</v>
       </c>
       <c r="I37" s="41" t="n">
-        <v>68.40000000000001</v>
+        <v>72</v>
       </c>
       <c r="J37" s="41" t="n">
-        <v>65.7</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="K37" s="41" t="n">
-        <v>2.700000000000003</v>
+        <v>5.099999999999994</v>
       </c>
       <c r="L37" s="90" t="inlineStr">
         <is>
@@ -6396,25 +6396,25 @@
         </is>
       </c>
       <c r="E39" s="41" t="n">
-        <v>64.90000000000001</v>
+        <v>64.8</v>
       </c>
       <c r="F39" s="41" t="n">
         <v>64.7</v>
       </c>
       <c r="G39" s="41" t="n">
-        <v>65.09999999999999</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="H39" s="41" t="n">
-        <v>74.5</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="I39" s="41" t="n">
-        <v>74.5</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="J39" s="41" t="n">
         <v>64.7</v>
       </c>
       <c r="K39" s="41" t="n">
-        <v>9.799999999999997</v>
+        <v>9.700000000000003</v>
       </c>
       <c r="L39" s="90" t="inlineStr">
         <is>
@@ -6482,25 +6482,25 @@
         </is>
       </c>
       <c r="E41" s="41" t="n">
-        <v>62.4</v>
+        <v>63.1</v>
       </c>
       <c r="F41" s="41" t="n">
         <v>62.1</v>
       </c>
       <c r="G41" s="41" t="n">
-        <v>62.6</v>
+        <v>63.7</v>
       </c>
       <c r="H41" s="41" t="n">
-        <v>64.40000000000001</v>
+        <v>65.5</v>
       </c>
       <c r="I41" s="41" t="n">
-        <v>64.40000000000001</v>
+        <v>65.5</v>
       </c>
       <c r="J41" s="41" t="n">
         <v>62.1</v>
       </c>
       <c r="K41" s="41" t="n">
-        <v>2.300000000000004</v>
+        <v>3.399999999999999</v>
       </c>
       <c r="L41" s="90" t="inlineStr">
         <is>
@@ -6554,12 +6554,12 @@
     <row r="43" ht="16" customHeight="1">
       <c r="B43" s="25" t="inlineStr">
         <is>
-          <t>QUIK</t>
+          <t>KVHI</t>
         </is>
       </c>
       <c r="C43" s="26" t="inlineStr">
         <is>
-          <t>QuickLogic Corporation</t>
+          <t>KVH Industries, Inc.</t>
         </is>
       </c>
       <c r="D43" s="49" t="inlineStr">
@@ -6568,29 +6568,29 @@
         </is>
       </c>
       <c r="E43" s="41" t="n">
-        <v>61.6</v>
+        <v>59.4</v>
       </c>
       <c r="F43" s="41" t="n">
-        <v>57.1</v>
+        <v>58.4</v>
       </c>
       <c r="G43" s="41" t="n">
-        <v>64.2</v>
+        <v>60</v>
       </c>
       <c r="H43" s="41" t="n">
-        <v>70.09999999999999</v>
+        <v>67.90000000000001</v>
       </c>
       <c r="I43" s="41" t="n">
-        <v>70.09999999999999</v>
+        <v>67.90000000000001</v>
       </c>
       <c r="J43" s="41" t="n">
-        <v>57.1</v>
+        <v>58.4</v>
       </c>
       <c r="K43" s="41" t="n">
-        <v>12.99999999999999</v>
-      </c>
-      <c r="L43" s="23" t="inlineStr">
-        <is>
-          <t>Moderate</t>
+        <v>9.500000000000007</v>
+      </c>
+      <c r="L43" s="90" t="inlineStr">
+        <is>
+          <t>Stable</t>
         </is>
       </c>
     </row>
@@ -6646,7 +6646,7 @@
         <v>0</v>
       </c>
       <c r="D49" s="92" t="n">
-        <v>-0.5</v>
+        <v>-0.52</v>
       </c>
     </row>
     <row r="50" ht="16" customHeight="1">
@@ -6656,10 +6656,10 @@
         </is>
       </c>
       <c r="C50" s="93" t="n">
-        <v>-0.6899999999999999</v>
+        <v>-0.67</v>
       </c>
       <c r="D50" s="93" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.55</v>
       </c>
     </row>
     <row r="51" ht="16" customHeight="1">
@@ -6669,10 +6669,10 @@
         </is>
       </c>
       <c r="C51" s="92" t="n">
-        <v>2.06</v>
+        <v>2</v>
       </c>
       <c r="D51" s="92" t="n">
-        <v>-1.68</v>
+        <v>-1.64</v>
       </c>
     </row>
   </sheetData>
@@ -8545,7 +8545,7 @@
     <row r="68" ht="18" customHeight="1">
       <c r="A68" s="94" t="inlineStr">
         <is>
-          <t>QUIK  —  QuickLogic Corporation</t>
+          <t>KVHI  —  KVH Industries, Inc.</t>
         </is>
       </c>
       <c r="C68" s="37" t="inlineStr">
@@ -8555,7 +8555,7 @@
       </c>
       <c r="D68" s="74" t="inlineStr">
         <is>
-          <t>Mkt Cap: $197M</t>
+          <t>Mkt Cap: $139M</t>
         </is>
       </c>
       <c r="E68" s="95" t="n"/>
@@ -8585,7 +8585,7 @@
       </c>
       <c r="E69" s="18" t="inlineStr">
         <is>
-          <t>2024-09-29</t>
+          <t>2024-09-30</t>
         </is>
       </c>
       <c r="F69" s="18" t="inlineStr">
@@ -8595,22 +8595,22 @@
       </c>
       <c r="G69" s="18" t="inlineStr">
         <is>
-          <t>2025-03-30</t>
+          <t>2025-03-31</t>
         </is>
       </c>
       <c r="H69" s="18" t="inlineStr">
         <is>
-          <t>2025-06-29</t>
+          <t>2025-06-30</t>
         </is>
       </c>
       <c r="I69" s="18" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="J69" s="18" t="inlineStr">
         <is>
-          <t>2025-12-28</t>
+          <t>2025-12-31</t>
         </is>
       </c>
     </row>
@@ -8622,28 +8622,28 @@
         </is>
       </c>
       <c r="C70" s="97" t="n">
-        <v>5.669</v>
+        <v>29.267</v>
       </c>
       <c r="D70" s="97" t="n">
-        <v>4.096</v>
+        <v>28.673</v>
       </c>
       <c r="E70" s="97" t="n">
-        <v>4.273</v>
+        <v>28.971</v>
       </c>
       <c r="F70" s="97" t="n">
-        <v>5.705</v>
+        <v>26.917</v>
       </c>
       <c r="G70" s="97" t="n">
-        <v>4.325</v>
+        <v>25.414</v>
       </c>
       <c r="H70" s="97" t="n">
-        <v>3.687</v>
+        <v>26.623</v>
       </c>
       <c r="I70" s="97" t="n">
-        <v>2.029</v>
+        <v>28.453</v>
       </c>
       <c r="J70" s="97" t="n">
-        <v>3.733</v>
+        <v>30.519</v>
       </c>
     </row>
     <row r="71" ht="16" customHeight="1">
@@ -8654,28 +8654,28 @@
         </is>
       </c>
       <c r="C71" s="71" t="n">
-        <v>0.6709999999999999</v>
+        <v>0.339</v>
       </c>
       <c r="D71" s="71" t="n">
-        <v>0.547</v>
+        <v>0.311</v>
       </c>
       <c r="E71" s="71" t="n">
-        <v>0.5579999999999999</v>
+        <v>0.32</v>
       </c>
       <c r="F71" s="71" t="n">
-        <v>0.598</v>
+        <v>0.265</v>
       </c>
       <c r="G71" s="71" t="n">
-        <v>0.434</v>
+        <v>0.293</v>
       </c>
       <c r="H71" s="71" t="n">
-        <v>0.259</v>
+        <v>0.343</v>
       </c>
       <c r="I71" s="71" t="n">
-        <v>-0.233</v>
+        <v>0.067</v>
       </c>
       <c r="J71" s="71" t="n">
-        <v>0.181</v>
+        <v>0.295</v>
       </c>
     </row>
     <row r="72" ht="16" customHeight="1">
@@ -8687,25 +8687,25 @@
       </c>
       <c r="C72" s="49" t="n"/>
       <c r="D72" s="75" t="n">
-        <v>-0.2774739813018169</v>
+        <v>-0.02029589640209109</v>
       </c>
       <c r="E72" s="75" t="n">
-        <v>0.043212890625</v>
+        <v>0.01039305269765982</v>
       </c>
       <c r="F72" s="75" t="n">
-        <v>0.3351275450503159</v>
+        <v>-0.07089848469158815</v>
       </c>
       <c r="G72" s="75" t="n">
-        <v>-0.2418930762489045</v>
+        <v>-0.05583831779173013</v>
       </c>
       <c r="H72" s="75" t="n">
-        <v>-0.147514450867052</v>
+        <v>0.04757220429684426</v>
       </c>
       <c r="I72" s="75" t="n">
-        <v>-0.4496880933007866</v>
+        <v>0.06873755775081697</v>
       </c>
       <c r="J72" s="75" t="n">
-        <v>0.8398225726959093</v>
+        <v>0.07261097248093347</v>
       </c>
     </row>
     <row r="73" ht="16" customHeight="1">
@@ -8720,16 +8720,16 @@
       <c r="E73" s="48" t="n"/>
       <c r="F73" s="48" t="n"/>
       <c r="G73" s="71" t="n">
-        <v>-0.2370788498853413</v>
+        <v>-0.1316499812075033</v>
       </c>
       <c r="H73" s="71" t="n">
-        <v>-0.099853515625</v>
+        <v>-0.07149583231611621</v>
       </c>
       <c r="I73" s="71" t="n">
-        <v>-0.5251579686402995</v>
+        <v>-0.01787994891443167</v>
       </c>
       <c r="J73" s="71" t="n">
-        <v>-0.3456617002629273</v>
+        <v>0.1338187762380652</v>
       </c>
     </row>
     <row r="74" ht="8" customHeight="1"/>
@@ -9326,7 +9326,7 @@
     <row r="97" ht="18" customHeight="1">
       <c r="A97" s="94" t="inlineStr">
         <is>
-          <t>LXFR  —  Luxfer Holdings PLC</t>
+          <t>EVLV  —  Evolv Technologies Holdings, Inc.</t>
         </is>
       </c>
       <c r="C97" s="37" t="inlineStr">
@@ -9336,7 +9336,7 @@
       </c>
       <c r="D97" s="74" t="inlineStr">
         <is>
-          <t>Mkt Cap: $464M</t>
+          <t>Mkt Cap: $913M</t>
         </is>
       </c>
       <c r="E97" s="95" t="n"/>
@@ -9366,7 +9366,7 @@
       </c>
       <c r="E98" s="18" t="inlineStr">
         <is>
-          <t>2024-09-29</t>
+          <t>2024-09-30</t>
         </is>
       </c>
       <c r="F98" s="18" t="inlineStr">
@@ -9376,17 +9376,17 @@
       </c>
       <c r="G98" s="18" t="inlineStr">
         <is>
-          <t>2025-03-30</t>
+          <t>2025-03-31</t>
         </is>
       </c>
       <c r="H98" s="18" t="inlineStr">
         <is>
-          <t>2025-06-29</t>
+          <t>2025-06-30</t>
         </is>
       </c>
       <c r="I98" s="18" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="J98" s="18" t="inlineStr">
@@ -9403,28 +9403,28 @@
         </is>
       </c>
       <c r="C99" s="97" t="n">
-        <v>89.40000000000001</v>
+        <v>22.181</v>
       </c>
       <c r="D99" s="97" t="n">
-        <v>99.7</v>
+        <v>25.54</v>
       </c>
       <c r="E99" s="97" t="n">
-        <v>99.40000000000001</v>
+        <v>27.36</v>
       </c>
       <c r="F99" s="97" t="n">
-        <v>103.4</v>
+        <v>29.1</v>
       </c>
       <c r="G99" s="97" t="n">
-        <v>97</v>
+        <v>32.007</v>
       </c>
       <c r="H99" s="97" t="n">
-        <v>104</v>
+        <v>32.544</v>
       </c>
       <c r="I99" s="97" t="n">
-        <v>92.90000000000001</v>
+        <v>42.85</v>
       </c>
       <c r="J99" s="97" t="n">
-        <v>90.7</v>
+        <v>38.504</v>
       </c>
     </row>
     <row r="100" ht="16" customHeight="1">
@@ -9435,28 +9435,28 @@
         </is>
       </c>
       <c r="C100" s="71" t="n">
-        <v>0.206</v>
+        <v>0.5479999999999999</v>
       </c>
       <c r="D100" s="71" t="n">
-        <v>0.221</v>
+        <v>0.5670000000000001</v>
       </c>
       <c r="E100" s="71" t="n">
-        <v>0.225</v>
+        <v>0.578</v>
       </c>
       <c r="F100" s="71" t="n">
-        <v>0.221</v>
+        <v>0.575</v>
       </c>
       <c r="G100" s="71" t="n">
-        <v>0.221</v>
+        <v>0.598</v>
       </c>
       <c r="H100" s="71" t="n">
-        <v>0.231</v>
+        <v>0.498</v>
       </c>
       <c r="I100" s="71" t="n">
-        <v>0.234</v>
+        <v>0.4970000000000001</v>
       </c>
       <c r="J100" s="71" t="n">
-        <v>0.244</v>
+        <v>0.484</v>
       </c>
     </row>
     <row r="101" ht="16" customHeight="1">
@@ -9468,25 +9468,25 @@
       </c>
       <c r="C101" s="49" t="n"/>
       <c r="D101" s="75" t="n">
-        <v>0.1152125279642058</v>
+        <v>0.1514359136197647</v>
       </c>
       <c r="E101" s="75" t="n">
-        <v>-0.003009027081243731</v>
+        <v>0.07126076742364917</v>
       </c>
       <c r="F101" s="75" t="n">
-        <v>0.04024144869215292</v>
+        <v>0.06359649122807018</v>
       </c>
       <c r="G101" s="75" t="n">
-        <v>-0.06189555125725339</v>
+        <v>0.09989690721649484</v>
       </c>
       <c r="H101" s="75" t="n">
-        <v>0.07216494845360824</v>
+        <v>0.01677757990439591</v>
       </c>
       <c r="I101" s="75" t="n">
-        <v>-0.1067307692307692</v>
+        <v>0.3166789577187807</v>
       </c>
       <c r="J101" s="75" t="n">
-        <v>-0.02368137782561894</v>
+        <v>-0.1014235705950992</v>
       </c>
     </row>
     <row r="102" ht="16" customHeight="1">
@@ -9501,23 +9501,23 @@
       <c r="E102" s="48" t="n"/>
       <c r="F102" s="48" t="n"/>
       <c r="G102" s="71" t="n">
-        <v>0.08501118568232663</v>
+        <v>0.4429917496956855</v>
       </c>
       <c r="H102" s="71" t="n">
-        <v>0.04312938816449348</v>
+        <v>0.2742364917776038</v>
       </c>
       <c r="I102" s="71" t="n">
-        <v>-0.06539235412474849</v>
+        <v>0.5661549707602339</v>
       </c>
       <c r="J102" s="71" t="n">
-        <v>-0.1228239845261122</v>
+        <v>0.3231615120274914</v>
       </c>
     </row>
     <row r="103" ht="8" customHeight="1"/>
     <row r="104" ht="18" customHeight="1">
       <c r="A104" s="94" t="inlineStr">
         <is>
-          <t>CLFD  —  Clearfield, Inc.</t>
+          <t>GHM  —  Graham Corporation</t>
         </is>
       </c>
       <c r="C104" s="37" t="inlineStr">
@@ -9527,7 +9527,7 @@
       </c>
       <c r="D104" s="74" t="inlineStr">
         <is>
-          <t>Mkt Cap: $395M</t>
+          <t>Mkt Cap: $1047M</t>
         </is>
       </c>
       <c r="E104" s="95" t="n"/>
@@ -9594,28 +9594,28 @@
         </is>
       </c>
       <c r="C106" s="97" t="n">
-        <v>36.91</v>
+        <v>49.07</v>
       </c>
       <c r="D106" s="97" t="n">
-        <v>48.793</v>
+        <v>49.951</v>
       </c>
       <c r="E106" s="97" t="n">
-        <v>46.772</v>
+        <v>53.563</v>
       </c>
       <c r="F106" s="97" t="n">
-        <v>29.698</v>
+        <v>47.037</v>
       </c>
       <c r="G106" s="97" t="n">
-        <v>47.168</v>
+        <v>59.345</v>
       </c>
       <c r="H106" s="97" t="n">
-        <v>49.903</v>
+        <v>55.487</v>
       </c>
       <c r="I106" s="97" t="n">
-        <v>17.587</v>
+        <v>66.027</v>
       </c>
       <c r="J106" s="97" t="n">
-        <v>34.341</v>
+        <v>56.701</v>
       </c>
     </row>
     <row r="107" ht="16" customHeight="1">
@@ -9626,28 +9626,28 @@
         </is>
       </c>
       <c r="C107" s="71" t="n">
-        <v>0.077</v>
+        <v>0.259</v>
       </c>
       <c r="D107" s="71" t="n">
-        <v>0.219</v>
+        <v>0.248</v>
       </c>
       <c r="E107" s="71" t="n">
-        <v>0.228</v>
+        <v>0.239</v>
       </c>
       <c r="F107" s="71" t="n">
-        <v>0.292</v>
+        <v>0.248</v>
       </c>
       <c r="G107" s="71" t="n">
-        <v>0.301</v>
+        <v>0.27</v>
       </c>
       <c r="H107" s="71" t="n">
-        <v>0.305</v>
+        <v>0.265</v>
       </c>
       <c r="I107" s="71" t="n">
-        <v>0.735</v>
+        <v>0.217</v>
       </c>
       <c r="J107" s="71" t="n">
-        <v>0.332</v>
+        <v>0.23</v>
       </c>
     </row>
     <row r="108" ht="16" customHeight="1">
@@ -9659,25 +9659,25 @@
       </c>
       <c r="C108" s="49" t="n"/>
       <c r="D108" s="75" t="n">
-        <v>0.3219452722839339</v>
+        <v>0.01795394334624006</v>
       </c>
       <c r="E108" s="75" t="n">
-        <v>-0.04141987580185683</v>
+        <v>0.07231086464735441</v>
       </c>
       <c r="F108" s="75" t="n">
-        <v>-0.3650474642948773</v>
+        <v>-0.1218378358195023</v>
       </c>
       <c r="G108" s="75" t="n">
-        <v>0.5882551013536265</v>
+        <v>0.2616663477687778</v>
       </c>
       <c r="H108" s="75" t="n">
-        <v>0.05798422659430122</v>
+        <v>-0.06500968910607464</v>
       </c>
       <c r="I108" s="75" t="n">
-        <v>-0.6475762980181552</v>
+        <v>0.189954403734208</v>
       </c>
       <c r="J108" s="75" t="n">
-        <v>0.9526354693807926</v>
+        <v>-0.1412452481560574</v>
       </c>
     </row>
     <row r="109" ht="16" customHeight="1">
@@ -9692,23 +9692,23 @@
       <c r="E109" s="48" t="n"/>
       <c r="F109" s="48" t="n"/>
       <c r="G109" s="71" t="n">
-        <v>0.2779192630723381</v>
+        <v>0.2093947422050133</v>
       </c>
       <c r="H109" s="71" t="n">
-        <v>0.02274916483921874</v>
+        <v>0.110828612039799</v>
       </c>
       <c r="I109" s="71" t="n">
-        <v>-0.6239844351321303</v>
+        <v>0.2326979444765976</v>
       </c>
       <c r="J109" s="71" t="n">
-        <v>0.1563404943093811</v>
+        <v>0.2054552798860471</v>
       </c>
     </row>
     <row r="110" ht="8" customHeight="1"/>
     <row r="111" ht="18" customHeight="1">
       <c r="A111" s="94" t="inlineStr">
         <is>
-          <t>ARRY  —  Array Technologies, Inc.</t>
+          <t>ADTN  —  ADTRAN Holdings Inc.</t>
         </is>
       </c>
       <c r="C111" s="37" t="inlineStr">
@@ -9718,7 +9718,7 @@
       </c>
       <c r="D111" s="74" t="inlineStr">
         <is>
-          <t>Mkt Cap: $742M</t>
+          <t>Mkt Cap: $608M</t>
         </is>
       </c>
       <c r="E111" s="95" t="n"/>
@@ -9785,28 +9785,28 @@
         </is>
       </c>
       <c r="C113" s="97" t="n">
-        <v>153.403</v>
+        <v>226.173</v>
       </c>
       <c r="D113" s="97" t="n">
-        <v>255.766</v>
+        <v>225.991</v>
       </c>
       <c r="E113" s="97" t="n">
-        <v>231.406</v>
+        <v>227.704</v>
       </c>
       <c r="F113" s="97" t="n">
-        <v>275.232</v>
+        <v>242.852</v>
       </c>
       <c r="G113" s="97" t="n">
-        <v>302.363</v>
+        <v>247.744</v>
       </c>
       <c r="H113" s="97" t="n">
-        <v>362.243</v>
+        <v>265.068</v>
       </c>
       <c r="I113" s="97" t="n">
-        <v>393.491</v>
+        <v>279.435</v>
       </c>
       <c r="J113" s="97" t="n">
-        <v>226.044</v>
+        <v>291.56</v>
       </c>
     </row>
     <row r="114" ht="16" customHeight="1">
@@ -9817,28 +9817,28 @@
         </is>
       </c>
       <c r="C114" s="71" t="n">
-        <v>0.359</v>
+        <v>0.311</v>
       </c>
       <c r="D114" s="71" t="n">
-        <v>0.336</v>
+        <v>0.361</v>
       </c>
       <c r="E114" s="71" t="n">
-        <v>0.338</v>
+        <v>0.374</v>
       </c>
       <c r="F114" s="71" t="n">
-        <v>0.285</v>
+        <v>0.376</v>
       </c>
       <c r="G114" s="71" t="n">
-        <v>0.253</v>
+        <v>0.384</v>
       </c>
       <c r="H114" s="71" t="n">
-        <v>0.268</v>
+        <v>0.373</v>
       </c>
       <c r="I114" s="71" t="n">
-        <v>0.269</v>
+        <v>0.383</v>
       </c>
       <c r="J114" s="71" t="n">
-        <v>0.08599999999999999</v>
+        <v>0.39</v>
       </c>
     </row>
     <row r="115" ht="16" customHeight="1">
@@ -9850,25 +9850,25 @@
       </c>
       <c r="C115" s="49" t="n"/>
       <c r="D115" s="75" t="n">
-        <v>0.6672816046622295</v>
+        <v>-0.000804693752127796</v>
       </c>
       <c r="E115" s="75" t="n">
-        <v>-0.09524330833652636</v>
+        <v>0.007579947874030382</v>
       </c>
       <c r="F115" s="75" t="n">
-        <v>0.1893900763160851</v>
+        <v>0.06652496223166919</v>
       </c>
       <c r="G115" s="75" t="n">
-        <v>0.09857502034647134</v>
+        <v>0.02014395598965625</v>
       </c>
       <c r="H115" s="75" t="n">
-        <v>0.1980401041132678</v>
+        <v>0.06992702144148799</v>
       </c>
       <c r="I115" s="75" t="n">
-        <v>0.08626253647413476</v>
+        <v>0.05420118611073385</v>
       </c>
       <c r="J115" s="75" t="n">
-        <v>-0.4255421343817267</v>
+        <v>0.04339112852720668</v>
       </c>
     </row>
     <row r="116" ht="16" customHeight="1">
@@ -9883,23 +9883,23 @@
       <c r="E116" s="48" t="n"/>
       <c r="F116" s="48" t="n"/>
       <c r="G116" s="71" t="n">
-        <v>0.9710370722867219</v>
+        <v>0.09537389520411367</v>
       </c>
       <c r="H116" s="71" t="n">
-        <v>0.4163063112376156</v>
+        <v>0.1729139656004</v>
       </c>
       <c r="I116" s="71" t="n">
-        <v>0.7004355980398088</v>
+        <v>0.2271852931876471</v>
       </c>
       <c r="J116" s="71" t="n">
-        <v>-0.1787146843390303</v>
+        <v>0.2005666002338873</v>
       </c>
     </row>
     <row r="117" ht="8" customHeight="1"/>
     <row r="118" ht="18" customHeight="1">
       <c r="A118" s="94" t="inlineStr">
         <is>
-          <t>EVLV  —  Evolv Technologies Holdings, Inc.</t>
+          <t>ARLO  —  Arlo Technologies, Inc.</t>
         </is>
       </c>
       <c r="C118" s="37" t="inlineStr">
@@ -9909,7 +9909,7 @@
       </c>
       <c r="D118" s="74" t="inlineStr">
         <is>
-          <t>Mkt Cap: $913M</t>
+          <t>Mkt Cap: $1513M</t>
         </is>
       </c>
       <c r="E118" s="95" t="n"/>
@@ -9939,7 +9939,7 @@
       </c>
       <c r="E119" s="18" t="inlineStr">
         <is>
-          <t>2024-09-30</t>
+          <t>2024-09-29</t>
         </is>
       </c>
       <c r="F119" s="18" t="inlineStr">
@@ -9949,17 +9949,17 @@
       </c>
       <c r="G119" s="18" t="inlineStr">
         <is>
-          <t>2025-03-31</t>
+          <t>2025-03-30</t>
         </is>
       </c>
       <c r="H119" s="18" t="inlineStr">
         <is>
-          <t>2025-06-30</t>
+          <t>2025-06-29</t>
         </is>
       </c>
       <c r="I119" s="18" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="J119" s="18" t="inlineStr">
@@ -9976,28 +9976,28 @@
         </is>
       </c>
       <c r="C120" s="97" t="n">
-        <v>22.181</v>
+        <v>124.2</v>
       </c>
       <c r="D120" s="97" t="n">
-        <v>25.54</v>
+        <v>127.447</v>
       </c>
       <c r="E120" s="97" t="n">
-        <v>27.36</v>
+        <v>137.667</v>
       </c>
       <c r="F120" s="97" t="n">
-        <v>29.1</v>
+        <v>121.572</v>
       </c>
       <c r="G120" s="97" t="n">
-        <v>32.007</v>
+        <v>119.066</v>
       </c>
       <c r="H120" s="97" t="n">
-        <v>32.544</v>
+        <v>129.405</v>
       </c>
       <c r="I120" s="97" t="n">
-        <v>42.85</v>
+        <v>139.529</v>
       </c>
       <c r="J120" s="97" t="n">
-        <v>38.504</v>
+        <v>141.297</v>
       </c>
     </row>
     <row r="121" ht="16" customHeight="1">
@@ -10008,28 +10008,28 @@
         </is>
       </c>
       <c r="C121" s="71" t="n">
-        <v>0.5479999999999999</v>
+        <v>0.381</v>
       </c>
       <c r="D121" s="71" t="n">
-        <v>0.5670000000000001</v>
+        <v>0.368</v>
       </c>
       <c r="E121" s="71" t="n">
-        <v>0.578</v>
+        <v>0.352</v>
       </c>
       <c r="F121" s="71" t="n">
-        <v>0.575</v>
+        <v>0.369</v>
       </c>
       <c r="G121" s="71" t="n">
-        <v>0.598</v>
+        <v>0.4429999999999999</v>
       </c>
       <c r="H121" s="71" t="n">
-        <v>0.498</v>
+        <v>0.449</v>
       </c>
       <c r="I121" s="71" t="n">
-        <v>0.4970000000000001</v>
+        <v>0.405</v>
       </c>
       <c r="J121" s="71" t="n">
-        <v>0.484</v>
+        <v>0.464</v>
       </c>
     </row>
     <row r="122" ht="16" customHeight="1">
@@ -10041,25 +10041,25 @@
       </c>
       <c r="C122" s="49" t="n"/>
       <c r="D122" s="75" t="n">
-        <v>0.1514359136197647</v>
+        <v>0.02614331723027375</v>
       </c>
       <c r="E122" s="75" t="n">
-        <v>0.07126076742364917</v>
+        <v>0.0801901967092203</v>
       </c>
       <c r="F122" s="75" t="n">
-        <v>0.06359649122807018</v>
+        <v>-0.1169125498485476</v>
       </c>
       <c r="G122" s="75" t="n">
-        <v>0.09989690721649484</v>
+        <v>-0.02061329911492778</v>
       </c>
       <c r="H122" s="75" t="n">
-        <v>0.01677757990439591</v>
+        <v>0.08683419280063158</v>
       </c>
       <c r="I122" s="75" t="n">
-        <v>0.3166789577187807</v>
+        <v>0.07823499864765658</v>
       </c>
       <c r="J122" s="75" t="n">
-        <v>-0.1014235705950992</v>
+        <v>0.01267120096897419</v>
       </c>
     </row>
     <row r="123" ht="16" customHeight="1">
@@ -10074,23 +10074,23 @@
       <c r="E123" s="48" t="n"/>
       <c r="F123" s="48" t="n"/>
       <c r="G123" s="71" t="n">
-        <v>0.4429917496956855</v>
+        <v>-0.0413365539452496</v>
       </c>
       <c r="H123" s="71" t="n">
-        <v>0.2742364917776038</v>
+        <v>0.01536324903685454</v>
       </c>
       <c r="I123" s="71" t="n">
-        <v>0.5661549707602339</v>
+        <v>0.01352539097968286</v>
       </c>
       <c r="J123" s="71" t="n">
-        <v>0.3231615120274914</v>
+        <v>0.1622495311420393</v>
       </c>
     </row>
     <row r="124" ht="8" customHeight="1"/>
     <row r="125" ht="18" customHeight="1">
       <c r="A125" s="94" t="inlineStr">
         <is>
-          <t>GHM  —  Graham Corporation</t>
+          <t>TRC  —  Tejon Ranch Co.</t>
         </is>
       </c>
       <c r="C125" s="37" t="inlineStr">
@@ -10100,7 +10100,7 @@
       </c>
       <c r="D125" s="74" t="inlineStr">
         <is>
-          <t>Mkt Cap: $1047M</t>
+          <t>Mkt Cap: $446M</t>
         </is>
       </c>
       <c r="E125" s="95" t="n"/>
@@ -10167,28 +10167,28 @@
         </is>
       </c>
       <c r="C127" s="97" t="n">
-        <v>49.07</v>
+        <v>7.406</v>
       </c>
       <c r="D127" s="97" t="n">
-        <v>49.951</v>
+        <v>5.689</v>
       </c>
       <c r="E127" s="97" t="n">
-        <v>53.563</v>
+        <v>10.856</v>
       </c>
       <c r="F127" s="97" t="n">
-        <v>47.037</v>
+        <v>17.935</v>
       </c>
       <c r="G127" s="97" t="n">
-        <v>59.345</v>
+        <v>8.209</v>
       </c>
       <c r="H127" s="97" t="n">
-        <v>55.487</v>
+        <v>8.307</v>
       </c>
       <c r="I127" s="97" t="n">
-        <v>66.027</v>
+        <v>11.969</v>
       </c>
       <c r="J127" s="97" t="n">
-        <v>56.701</v>
+        <v>21.106</v>
       </c>
     </row>
     <row r="128" ht="16" customHeight="1">
@@ -10199,28 +10199,28 @@
         </is>
       </c>
       <c r="C128" s="71" t="n">
-        <v>0.259</v>
+        <v>-0.201</v>
       </c>
       <c r="D128" s="71" t="n">
-        <v>0.248</v>
+        <v>-0.034</v>
       </c>
       <c r="E128" s="71" t="n">
-        <v>0.239</v>
+        <v>-0.078</v>
       </c>
       <c r="F128" s="71" t="n">
-        <v>0.248</v>
+        <v>0.247</v>
       </c>
       <c r="G128" s="71" t="n">
-        <v>0.27</v>
+        <v>0.009000000000000001</v>
       </c>
       <c r="H128" s="71" t="n">
-        <v>0.265</v>
+        <v>0.102</v>
       </c>
       <c r="I128" s="71" t="n">
-        <v>0.217</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="J128" s="71" t="n">
-        <v>0.23</v>
+        <v>0.206</v>
       </c>
     </row>
     <row r="129" ht="16" customHeight="1">
@@ -10232,25 +10232,25 @@
       </c>
       <c r="C129" s="49" t="n"/>
       <c r="D129" s="75" t="n">
-        <v>0.01795394334624006</v>
+        <v>-0.2318390494193897</v>
       </c>
       <c r="E129" s="75" t="n">
-        <v>0.07231086464735441</v>
+        <v>0.9082439796097732</v>
       </c>
       <c r="F129" s="75" t="n">
-        <v>-0.1218378358195023</v>
+        <v>0.6520817980840088</v>
       </c>
       <c r="G129" s="75" t="n">
-        <v>0.2616663477687778</v>
+        <v>-0.5422916085865626</v>
       </c>
       <c r="H129" s="75" t="n">
-        <v>-0.06500968910607464</v>
+        <v>0.01193811670118163</v>
       </c>
       <c r="I129" s="75" t="n">
-        <v>0.189954403734208</v>
+        <v>0.4408330323823282</v>
       </c>
       <c r="J129" s="75" t="n">
-        <v>-0.1412452481560574</v>
+        <v>0.7633887542818949</v>
       </c>
     </row>
     <row r="130" ht="16" customHeight="1">
@@ -10265,23 +10265,23 @@
       <c r="E130" s="48" t="n"/>
       <c r="F130" s="48" t="n"/>
       <c r="G130" s="71" t="n">
-        <v>0.2093947422050133</v>
+        <v>0.1084256008641642</v>
       </c>
       <c r="H130" s="71" t="n">
-        <v>0.110828612039799</v>
+        <v>0.4601863244858499</v>
       </c>
       <c r="I130" s="71" t="n">
-        <v>0.2326979444765976</v>
+        <v>0.102523949889462</v>
       </c>
       <c r="J130" s="71" t="n">
-        <v>0.2054552798860471</v>
+        <v>0.1768051296347923</v>
       </c>
     </row>
     <row r="131" ht="8" customHeight="1"/>
     <row r="132" ht="18" customHeight="1">
       <c r="A132" s="94" t="inlineStr">
         <is>
-          <t>NNDM  —  Nano Dimension Ltd.</t>
+          <t>INOD  —  Innodata Inc.</t>
         </is>
       </c>
       <c r="C132" s="37" t="inlineStr">
@@ -10291,7 +10291,7 @@
       </c>
       <c r="D132" s="74" t="inlineStr">
         <is>
-          <t>Mkt Cap: $327M</t>
+          <t>Mkt Cap: $1822M</t>
         </is>
       </c>
       <c r="E132" s="95" t="n"/>
@@ -10358,28 +10358,28 @@
         </is>
       </c>
       <c r="C134" s="97" t="n">
-        <v>13.364</v>
+        <v>26.504</v>
       </c>
       <c r="D134" s="97" t="n">
-        <v>14.986</v>
+        <v>32.553</v>
       </c>
       <c r="E134" s="97" t="n">
-        <v>14.856</v>
+        <v>52.224</v>
       </c>
       <c r="F134" s="97" t="n">
-        <v>14.569</v>
+        <v>59.18</v>
       </c>
       <c r="G134" s="97" t="n">
-        <v>14.401</v>
+        <v>58.344</v>
       </c>
       <c r="H134" s="97" t="n">
-        <v>25.837</v>
+        <v>58.393</v>
       </c>
       <c r="I134" s="97" t="n">
-        <v>26.884</v>
+        <v>62.55</v>
       </c>
       <c r="J134" s="97" t="n">
-        <v>35.315</v>
+        <v>72.376</v>
       </c>
     </row>
     <row r="135" ht="16" customHeight="1">
@@ -10390,28 +10390,28 @@
         </is>
       </c>
       <c r="C135" s="71" t="n">
-        <v>0.462</v>
+        <v>0.361</v>
       </c>
       <c r="D135" s="71" t="n">
-        <v>0.447</v>
+        <v>0.287</v>
       </c>
       <c r="E135" s="71" t="n">
-        <v>0.48</v>
+        <v>0.418</v>
       </c>
       <c r="F135" s="71" t="n">
-        <v>0.333</v>
+        <v>0.452</v>
       </c>
       <c r="G135" s="71" t="n">
-        <v>0.406</v>
+        <v>0.399</v>
       </c>
       <c r="H135" s="71" t="n">
-        <v>0.273</v>
+        <v>0.398</v>
       </c>
       <c r="I135" s="71" t="n">
-        <v>0.303</v>
+        <v>0.414</v>
       </c>
       <c r="J135" s="71" t="n">
-        <v>0.377</v>
+        <v>0.383</v>
       </c>
     </row>
     <row r="136" ht="16" customHeight="1">
@@ -10423,25 +10423,25 @@
       </c>
       <c r="C136" s="49" t="n"/>
       <c r="D136" s="75" t="n">
-        <v>0.1213708470517809</v>
+        <v>0.2282297011771808</v>
       </c>
       <c r="E136" s="75" t="n">
-        <v>-0.008674763112238089</v>
+        <v>0.604276103584923</v>
       </c>
       <c r="F136" s="75" t="n">
-        <v>-0.01931879375336564</v>
+        <v>0.1331954656862745</v>
       </c>
       <c r="G136" s="75" t="n">
-        <v>-0.01153133365364816</v>
+        <v>-0.01412639405204461</v>
       </c>
       <c r="H136" s="75" t="n">
-        <v>0.794111520033331</v>
+        <v>0.0008398464280817222</v>
       </c>
       <c r="I136" s="75" t="n">
-        <v>0.04052328056662925</v>
+        <v>0.07119003990204305</v>
       </c>
       <c r="J136" s="75" t="n">
-        <v>0.3136066061597976</v>
+        <v>0.1570903277378098</v>
       </c>
     </row>
     <row r="137" ht="16" customHeight="1">
@@ -10456,23 +10456,23 @@
       <c r="E137" s="48" t="n"/>
       <c r="F137" s="48" t="n"/>
       <c r="G137" s="71" t="n">
-        <v>0.07759652798563305</v>
+        <v>1.201328101418654</v>
       </c>
       <c r="H137" s="71" t="n">
-        <v>0.7240758040838116</v>
+        <v>0.7937824470862901</v>
       </c>
       <c r="I137" s="71" t="n">
-        <v>0.8096392030156165</v>
+        <v>0.1977251838235294</v>
       </c>
       <c r="J137" s="71" t="n">
-        <v>1.423982428443956</v>
+        <v>0.2229807367353836</v>
       </c>
     </row>
     <row r="138" ht="8" customHeight="1"/>
     <row r="139" ht="18" customHeight="1">
       <c r="A139" s="94" t="inlineStr">
         <is>
-          <t>ADTN  —  ADTRAN Holdings Inc.</t>
+          <t>CDRE  —  Cadre Holdings, Inc.</t>
         </is>
       </c>
       <c r="C139" s="37" t="inlineStr">
@@ -10482,7 +10482,7 @@
       </c>
       <c r="D139" s="74" t="inlineStr">
         <is>
-          <t>Mkt Cap: $608M</t>
+          <t>Mkt Cap: $1279M</t>
         </is>
       </c>
       <c r="E139" s="95" t="n"/>
@@ -10549,28 +10549,28 @@
         </is>
       </c>
       <c r="C141" s="97" t="n">
-        <v>226.173</v>
+        <v>137.86</v>
       </c>
       <c r="D141" s="97" t="n">
-        <v>225.991</v>
+        <v>144.309</v>
       </c>
       <c r="E141" s="97" t="n">
-        <v>227.704</v>
+        <v>109.408</v>
       </c>
       <c r="F141" s="97" t="n">
-        <v>242.852</v>
+        <v>175.984</v>
       </c>
       <c r="G141" s="97" t="n">
-        <v>247.744</v>
+        <v>130.106</v>
       </c>
       <c r="H141" s="97" t="n">
-        <v>265.068</v>
+        <v>157.109</v>
       </c>
       <c r="I141" s="97" t="n">
-        <v>279.435</v>
+        <v>155.869</v>
       </c>
       <c r="J141" s="97" t="n">
-        <v>291.56</v>
+        <v>167.224</v>
       </c>
     </row>
     <row r="142" ht="16" customHeight="1">
@@ -10581,28 +10581,28 @@
         </is>
       </c>
       <c r="C142" s="71" t="n">
-        <v>0.311</v>
+        <v>0.418</v>
       </c>
       <c r="D142" s="71" t="n">
-        <v>0.361</v>
+        <v>0.406</v>
       </c>
       <c r="E142" s="71" t="n">
-        <v>0.374</v>
+        <v>0.366</v>
       </c>
       <c r="F142" s="71" t="n">
-        <v>0.376</v>
+        <v>0.439</v>
       </c>
       <c r="G142" s="71" t="n">
-        <v>0.384</v>
+        <v>0.424</v>
       </c>
       <c r="H142" s="71" t="n">
-        <v>0.373</v>
+        <v>0.401</v>
       </c>
       <c r="I142" s="71" t="n">
-        <v>0.383</v>
+        <v>0.419</v>
       </c>
       <c r="J142" s="71" t="n">
-        <v>0.39</v>
+        <v>0.409</v>
       </c>
     </row>
     <row r="143" ht="16" customHeight="1">
@@ -10614,25 +10614,25 @@
       </c>
       <c r="C143" s="49" t="n"/>
       <c r="D143" s="75" t="n">
-        <v>-0.000804693752127796</v>
+        <v>0.04677934136080081</v>
       </c>
       <c r="E143" s="75" t="n">
-        <v>0.007579947874030382</v>
+        <v>-0.2418490877214865</v>
       </c>
       <c r="F143" s="75" t="n">
-        <v>0.06652496223166919</v>
+        <v>0.6085112606025154</v>
       </c>
       <c r="G143" s="75" t="n">
-        <v>0.02014395598965625</v>
+        <v>-0.2606941540140013</v>
       </c>
       <c r="H143" s="75" t="n">
-        <v>0.06992702144148799</v>
+        <v>0.2075461546738813</v>
       </c>
       <c r="I143" s="75" t="n">
-        <v>0.05420118611073385</v>
+        <v>-0.007892609589520651</v>
       </c>
       <c r="J143" s="75" t="n">
-        <v>0.04339112852720668</v>
+        <v>0.07284963655377272</v>
       </c>
     </row>
     <row r="144" ht="16" customHeight="1">
@@ -10647,16 +10647,16 @@
       <c r="E144" s="48" t="n"/>
       <c r="F144" s="48" t="n"/>
       <c r="G144" s="71" t="n">
-        <v>0.09537389520411367</v>
+        <v>-0.05624546641520383</v>
       </c>
       <c r="H144" s="71" t="n">
-        <v>0.1729139656004</v>
+        <v>0.08869855656958332</v>
       </c>
       <c r="I144" s="71" t="n">
-        <v>0.2271852931876471</v>
+        <v>0.4246581602807838</v>
       </c>
       <c r="J144" s="71" t="n">
-        <v>0.2005666002338873</v>
+        <v>-0.04977725247749795</v>
       </c>
     </row>
     <row r="145" ht="8" customHeight="1"/>
@@ -11444,7 +11444,7 @@
     <row r="175" ht="18" customHeight="1">
       <c r="A175" s="94" t="inlineStr">
         <is>
-          <t>BRC  —  Brady Corporation</t>
+          <t>MRCY  —  Mercury Systems, Inc.</t>
         </is>
       </c>
       <c r="C175" s="37" t="inlineStr">
@@ -11454,7 +11454,7 @@
       </c>
       <c r="D175" s="74" t="inlineStr">
         <is>
-          <t>Mkt Cap: $4140M</t>
+          <t>Mkt Cap: $5093M</t>
         </is>
       </c>
       <c r="E175" s="95" t="n"/>
@@ -11474,42 +11474,42 @@
       </c>
       <c r="C176" s="18" t="inlineStr">
         <is>
-          <t>2024-04-30</t>
+          <t>2024-03-29</t>
         </is>
       </c>
       <c r="D176" s="18" t="inlineStr">
         <is>
-          <t>2024-07-31</t>
+          <t>2024-06-30</t>
         </is>
       </c>
       <c r="E176" s="18" t="inlineStr">
         <is>
-          <t>2024-10-31</t>
+          <t>2024-09-27</t>
         </is>
       </c>
       <c r="F176" s="18" t="inlineStr">
         <is>
-          <t>2025-01-31</t>
+          <t>2024-12-27</t>
         </is>
       </c>
       <c r="G176" s="18" t="inlineStr">
         <is>
-          <t>2025-04-30</t>
+          <t>2025-03-28</t>
         </is>
       </c>
       <c r="H176" s="18" t="inlineStr">
         <is>
-          <t>2025-07-31</t>
+          <t>2025-06-27</t>
         </is>
       </c>
       <c r="I176" s="18" t="inlineStr">
         <is>
-          <t>2025-10-31</t>
+          <t>2025-09-26</t>
         </is>
       </c>
       <c r="J176" s="18" t="inlineStr">
         <is>
-          <t>2026-01-31</t>
+          <t>2025-12-26</t>
         </is>
       </c>
     </row>
@@ -11521,28 +11521,28 @@
         </is>
       </c>
       <c r="C177" s="97" t="n">
-        <v>343.384</v>
+        <v>204.431</v>
       </c>
       <c r="D177" s="97" t="n">
-        <v>343.402</v>
+        <v>248.563</v>
       </c>
       <c r="E177" s="97" t="n">
-        <v>377.065</v>
+        <v>204.431</v>
       </c>
       <c r="F177" s="97" t="n">
-        <v>356.675</v>
+        <v>223.125</v>
       </c>
       <c r="G177" s="97" t="n">
-        <v>382.59</v>
+        <v>211.358</v>
       </c>
       <c r="H177" s="97" t="n">
-        <v>397.275</v>
+        <v>273.106</v>
       </c>
       <c r="I177" s="97" t="n">
-        <v>405.287</v>
+        <v>225.209</v>
       </c>
       <c r="J177" s="97" t="n">
-        <v>384.137</v>
+        <v>232.872</v>
       </c>
     </row>
     <row r="178" ht="16" customHeight="1">
@@ -11553,28 +11553,28 @@
         </is>
       </c>
       <c r="C178" s="71" t="n">
-        <v>0.515</v>
+        <v>0.253</v>
       </c>
       <c r="D178" s="71" t="n">
-        <v>0.516</v>
+        <v>0.295</v>
       </c>
       <c r="E178" s="71" t="n">
-        <v>0.503</v>
+        <v>0.253</v>
       </c>
       <c r="F178" s="71" t="n">
-        <v>0.493</v>
+        <v>0.273</v>
       </c>
       <c r="G178" s="71" t="n">
-        <v>0.51</v>
+        <v>0.27</v>
       </c>
       <c r="H178" s="71" t="n">
-        <v>0.504</v>
+        <v>0.31</v>
       </c>
       <c r="I178" s="71" t="n">
-        <v>0.515</v>
+        <v>0.279</v>
       </c>
       <c r="J178" s="71" t="n">
-        <v>0.506</v>
+        <v>0.26</v>
       </c>
     </row>
     <row r="179" ht="16" customHeight="1">
@@ -11586,25 +11586,25 @@
       </c>
       <c r="C179" s="49" t="n"/>
       <c r="D179" s="75" t="n">
-        <v>5.241944878037416e-05</v>
+        <v>0.2158772397532664</v>
       </c>
       <c r="E179" s="75" t="n">
-        <v>0.09802796722208956</v>
+        <v>-0.1775485490599969</v>
       </c>
       <c r="F179" s="75" t="n">
-        <v>-0.05407555726466259</v>
+        <v>0.09144405691896043</v>
       </c>
       <c r="G179" s="75" t="n">
-        <v>0.07265718090698815</v>
+        <v>-0.05273725490196078</v>
       </c>
       <c r="H179" s="75" t="n">
-        <v>0.03838312553908884</v>
+        <v>0.2921488659052414</v>
       </c>
       <c r="I179" s="75" t="n">
-        <v>0.02016739034673715</v>
+        <v>-0.1753787906527136</v>
       </c>
       <c r="J179" s="75" t="n">
-        <v>-0.05218524156955442</v>
+        <v>0.03402617124537652</v>
       </c>
     </row>
     <row r="180" ht="16" customHeight="1">
@@ -11619,23 +11619,23 @@
       <c r="E180" s="48" t="n"/>
       <c r="F180" s="48" t="n"/>
       <c r="G180" s="71" t="n">
-        <v>0.1141753838268527</v>
+        <v>0.03388429347799502</v>
       </c>
       <c r="H180" s="71" t="n">
-        <v>0.1568802744305508</v>
+        <v>0.09873955496192112</v>
       </c>
       <c r="I180" s="71" t="n">
-        <v>0.07484651187461047</v>
+        <v>0.1016382055559088</v>
       </c>
       <c r="J180" s="71" t="n">
-        <v>0.07699446274619752</v>
+        <v>0.04368403361344537</v>
       </c>
     </row>
     <row r="181" ht="8" customHeight="1"/>
     <row r="182" ht="18" customHeight="1">
       <c r="A182" s="94" t="inlineStr">
         <is>
-          <t>MRCY  —  Mercury Systems, Inc.</t>
+          <t>BRC  —  Brady Corporation</t>
         </is>
       </c>
       <c r="C182" s="37" t="inlineStr">
@@ -11645,7 +11645,7 @@
       </c>
       <c r="D182" s="74" t="inlineStr">
         <is>
-          <t>Mkt Cap: $5093M</t>
+          <t>Mkt Cap: $4140M</t>
         </is>
       </c>
       <c r="E182" s="95" t="n"/>
@@ -11665,42 +11665,42 @@
       </c>
       <c r="C183" s="18" t="inlineStr">
         <is>
-          <t>2024-03-29</t>
+          <t>2024-04-30</t>
         </is>
       </c>
       <c r="D183" s="18" t="inlineStr">
         <is>
-          <t>2024-06-30</t>
+          <t>2024-07-31</t>
         </is>
       </c>
       <c r="E183" s="18" t="inlineStr">
         <is>
-          <t>2024-09-27</t>
+          <t>2024-10-31</t>
         </is>
       </c>
       <c r="F183" s="18" t="inlineStr">
         <is>
-          <t>2024-12-27</t>
+          <t>2025-01-31</t>
         </is>
       </c>
       <c r="G183" s="18" t="inlineStr">
         <is>
-          <t>2025-03-28</t>
+          <t>2025-04-30</t>
         </is>
       </c>
       <c r="H183" s="18" t="inlineStr">
         <is>
-          <t>2025-06-27</t>
+          <t>2025-07-31</t>
         </is>
       </c>
       <c r="I183" s="18" t="inlineStr">
         <is>
-          <t>2025-09-26</t>
+          <t>2025-10-31</t>
         </is>
       </c>
       <c r="J183" s="18" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2026-01-31</t>
         </is>
       </c>
     </row>
@@ -11712,28 +11712,28 @@
         </is>
       </c>
       <c r="C184" s="97" t="n">
-        <v>204.431</v>
+        <v>343.384</v>
       </c>
       <c r="D184" s="97" t="n">
-        <v>248.563</v>
+        <v>343.402</v>
       </c>
       <c r="E184" s="97" t="n">
-        <v>204.431</v>
+        <v>377.065</v>
       </c>
       <c r="F184" s="97" t="n">
-        <v>223.125</v>
+        <v>356.675</v>
       </c>
       <c r="G184" s="97" t="n">
-        <v>211.358</v>
+        <v>382.59</v>
       </c>
       <c r="H184" s="97" t="n">
-        <v>273.106</v>
+        <v>397.275</v>
       </c>
       <c r="I184" s="97" t="n">
-        <v>225.209</v>
+        <v>405.287</v>
       </c>
       <c r="J184" s="97" t="n">
-        <v>232.872</v>
+        <v>384.137</v>
       </c>
     </row>
     <row r="185" ht="16" customHeight="1">
@@ -11744,28 +11744,28 @@
         </is>
       </c>
       <c r="C185" s="71" t="n">
-        <v>0.253</v>
+        <v>0.515</v>
       </c>
       <c r="D185" s="71" t="n">
-        <v>0.295</v>
+        <v>0.516</v>
       </c>
       <c r="E185" s="71" t="n">
-        <v>0.253</v>
+        <v>0.503</v>
       </c>
       <c r="F185" s="71" t="n">
-        <v>0.273</v>
+        <v>0.493</v>
       </c>
       <c r="G185" s="71" t="n">
-        <v>0.27</v>
+        <v>0.51</v>
       </c>
       <c r="H185" s="71" t="n">
-        <v>0.31</v>
+        <v>0.504</v>
       </c>
       <c r="I185" s="71" t="n">
-        <v>0.279</v>
+        <v>0.515</v>
       </c>
       <c r="J185" s="71" t="n">
-        <v>0.26</v>
+        <v>0.506</v>
       </c>
     </row>
     <row r="186" ht="16" customHeight="1">
@@ -11777,25 +11777,25 @@
       </c>
       <c r="C186" s="49" t="n"/>
       <c r="D186" s="75" t="n">
-        <v>0.2158772397532664</v>
+        <v>5.241944878037416e-05</v>
       </c>
       <c r="E186" s="75" t="n">
-        <v>-0.1775485490599969</v>
+        <v>0.09802796722208956</v>
       </c>
       <c r="F186" s="75" t="n">
-        <v>0.09144405691896043</v>
+        <v>-0.05407555726466259</v>
       </c>
       <c r="G186" s="75" t="n">
-        <v>-0.05273725490196078</v>
+        <v>0.07265718090698815</v>
       </c>
       <c r="H186" s="75" t="n">
-        <v>0.2921488659052414</v>
+        <v>0.03838312553908884</v>
       </c>
       <c r="I186" s="75" t="n">
-        <v>-0.1753787906527136</v>
+        <v>0.02016739034673715</v>
       </c>
       <c r="J186" s="75" t="n">
-        <v>0.03402617124537652</v>
+        <v>-0.05218524156955442</v>
       </c>
     </row>
     <row r="187" ht="16" customHeight="1">
@@ -11810,16 +11810,16 @@
       <c r="E187" s="48" t="n"/>
       <c r="F187" s="48" t="n"/>
       <c r="G187" s="71" t="n">
-        <v>0.03388429347799502</v>
+        <v>0.1141753838268527</v>
       </c>
       <c r="H187" s="71" t="n">
-        <v>0.09873955496192112</v>
+        <v>0.1568802744305508</v>
       </c>
       <c r="I187" s="71" t="n">
-        <v>0.1016382055559088</v>
+        <v>0.07484651187461047</v>
       </c>
       <c r="J187" s="71" t="n">
-        <v>0.04368403361344537</v>
+        <v>0.07699446274619752</v>
       </c>
     </row>
     <row r="188" ht="8" customHeight="1"/>
@@ -12017,7 +12017,7 @@
     <row r="196" ht="18" customHeight="1">
       <c r="A196" s="94" t="inlineStr">
         <is>
-          <t>RUN  —  Sunrun Inc.</t>
+          <t>LYFT  —  Lyft, Inc.</t>
         </is>
       </c>
       <c r="C196" s="37" t="inlineStr">
@@ -12027,7 +12027,7 @@
       </c>
       <c r="D196" s="74" t="inlineStr">
         <is>
-          <t>Mkt Cap: $2189M</t>
+          <t>Mkt Cap: $6122M</t>
         </is>
       </c>
       <c r="E196" s="95" t="n"/>
@@ -12094,28 +12094,28 @@
         </is>
       </c>
       <c r="C198" s="97" t="n">
-        <v>458.188</v>
+        <v>1277.201</v>
       </c>
       <c r="D198" s="97" t="n">
-        <v>523.866</v>
+        <v>1435.846</v>
       </c>
       <c r="E198" s="97" t="n">
-        <v>537.173</v>
+        <v>1522.692</v>
       </c>
       <c r="F198" s="97" t="n">
-        <v>518.492</v>
+        <v>1550.277</v>
       </c>
       <c r="G198" s="97" t="n">
-        <v>504.271</v>
+        <v>1450.172</v>
       </c>
       <c r="H198" s="97" t="n">
-        <v>569.336</v>
+        <v>1588.183</v>
       </c>
       <c r="I198" s="97" t="n">
-        <v>724.557</v>
+        <v>1685.195</v>
       </c>
       <c r="J198" s="97" t="n">
-        <v>1158.833</v>
+        <v>1592.711</v>
       </c>
     </row>
     <row r="199" ht="16" customHeight="1">
@@ -12126,28 +12126,28 @@
         </is>
       </c>
       <c r="C199" s="71" t="n">
-        <v>0.07099999999999999</v>
+        <v>0.409</v>
       </c>
       <c r="D199" s="71" t="n">
-        <v>0.181</v>
+        <v>0.429</v>
       </c>
       <c r="E199" s="71" t="n">
-        <v>0.193</v>
+        <v>0.417</v>
       </c>
       <c r="F199" s="71" t="n">
-        <v>0.188</v>
+        <v>0.436</v>
       </c>
       <c r="G199" s="71" t="n">
-        <v>0.196</v>
+        <v>0.405</v>
       </c>
       <c r="H199" s="71" t="n">
-        <v>0.166</v>
+        <v>0.411</v>
       </c>
       <c r="I199" s="71" t="n">
-        <v>0.336</v>
+        <v>0.45</v>
       </c>
       <c r="J199" s="71" t="n">
-        <v>0.353</v>
+        <v>0.39</v>
       </c>
     </row>
     <row r="200" ht="16" customHeight="1">
@@ -12159,25 +12159,25 @@
       </c>
       <c r="C200" s="49" t="n"/>
       <c r="D200" s="75" t="n">
-        <v>0.1433429072782351</v>
+        <v>0.1242130252012017</v>
       </c>
       <c r="E200" s="75" t="n">
-        <v>0.0254015339800636</v>
+        <v>0.06048420234481971</v>
       </c>
       <c r="F200" s="75" t="n">
-        <v>-0.0347765058928874</v>
+        <v>0.01811594202898551</v>
       </c>
       <c r="G200" s="75" t="n">
-        <v>-0.02742761701241292</v>
+        <v>-0.06457233126725095</v>
       </c>
       <c r="H200" s="75" t="n">
-        <v>0.1290278441552261</v>
+        <v>0.095168711021865</v>
       </c>
       <c r="I200" s="75" t="n">
-        <v>0.2726351398822488</v>
+        <v>0.06108364086506404</v>
       </c>
       <c r="J200" s="75" t="n">
-        <v>0.5993676135900972</v>
+        <v>-0.05488029575212364</v>
       </c>
     </row>
     <row r="201" ht="16" customHeight="1">
@@ -12192,23 +12192,23 @@
       <c r="E201" s="48" t="n"/>
       <c r="F201" s="48" t="n"/>
       <c r="G201" s="71" t="n">
-        <v>0.1005766192043441</v>
+        <v>0.1354297405028652</v>
       </c>
       <c r="H201" s="71" t="n">
-        <v>0.0867970053410605</v>
+        <v>0.1060956397830965</v>
       </c>
       <c r="I201" s="71" t="n">
-        <v>0.3488336159859114</v>
+        <v>0.1067208601608204</v>
       </c>
       <c r="J201" s="71" t="n">
-        <v>1.235006518904824</v>
+        <v>0.02737188257324336</v>
       </c>
     </row>
     <row r="202" ht="8" customHeight="1"/>
     <row r="203" ht="18" customHeight="1">
       <c r="A203" s="94" t="inlineStr">
         <is>
-          <t>LYFT  —  Lyft, Inc.</t>
+          <t>RUN  —  Sunrun Inc.</t>
         </is>
       </c>
       <c r="C203" s="37" t="inlineStr">
@@ -12218,7 +12218,7 @@
       </c>
       <c r="D203" s="74" t="inlineStr">
         <is>
-          <t>Mkt Cap: $6122M</t>
+          <t>Mkt Cap: $2189M</t>
         </is>
       </c>
       <c r="E203" s="95" t="n"/>
@@ -12285,28 +12285,28 @@
         </is>
       </c>
       <c r="C205" s="97" t="n">
-        <v>1277.201</v>
+        <v>458.188</v>
       </c>
       <c r="D205" s="97" t="n">
-        <v>1435.846</v>
+        <v>523.866</v>
       </c>
       <c r="E205" s="97" t="n">
-        <v>1522.692</v>
+        <v>537.173</v>
       </c>
       <c r="F205" s="97" t="n">
-        <v>1550.277</v>
+        <v>518.492</v>
       </c>
       <c r="G205" s="97" t="n">
-        <v>1450.172</v>
+        <v>504.271</v>
       </c>
       <c r="H205" s="97" t="n">
-        <v>1588.183</v>
+        <v>569.336</v>
       </c>
       <c r="I205" s="97" t="n">
-        <v>1685.195</v>
+        <v>724.557</v>
       </c>
       <c r="J205" s="97" t="n">
-        <v>1592.711</v>
+        <v>1158.833</v>
       </c>
     </row>
     <row r="206" ht="16" customHeight="1">
@@ -12317,28 +12317,28 @@
         </is>
       </c>
       <c r="C206" s="71" t="n">
-        <v>0.409</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="D206" s="71" t="n">
-        <v>0.429</v>
+        <v>0.181</v>
       </c>
       <c r="E206" s="71" t="n">
-        <v>0.417</v>
+        <v>0.193</v>
       </c>
       <c r="F206" s="71" t="n">
-        <v>0.436</v>
+        <v>0.188</v>
       </c>
       <c r="G206" s="71" t="n">
-        <v>0.405</v>
+        <v>0.196</v>
       </c>
       <c r="H206" s="71" t="n">
-        <v>0.411</v>
+        <v>0.166</v>
       </c>
       <c r="I206" s="71" t="n">
-        <v>0.45</v>
+        <v>0.336</v>
       </c>
       <c r="J206" s="71" t="n">
-        <v>0.39</v>
+        <v>0.353</v>
       </c>
     </row>
     <row r="207" ht="16" customHeight="1">
@@ -12350,25 +12350,25 @@
       </c>
       <c r="C207" s="49" t="n"/>
       <c r="D207" s="75" t="n">
-        <v>0.1242130252012017</v>
+        <v>0.1433429072782351</v>
       </c>
       <c r="E207" s="75" t="n">
-        <v>0.06048420234481971</v>
+        <v>0.0254015339800636</v>
       </c>
       <c r="F207" s="75" t="n">
-        <v>0.01811594202898551</v>
+        <v>-0.0347765058928874</v>
       </c>
       <c r="G207" s="75" t="n">
-        <v>-0.06457233126725095</v>
+        <v>-0.02742761701241292</v>
       </c>
       <c r="H207" s="75" t="n">
-        <v>0.095168711021865</v>
+        <v>0.1290278441552261</v>
       </c>
       <c r="I207" s="75" t="n">
-        <v>0.06108364086506404</v>
+        <v>0.2726351398822488</v>
       </c>
       <c r="J207" s="75" t="n">
-        <v>-0.05488029575212364</v>
+        <v>0.5993676135900972</v>
       </c>
     </row>
     <row r="208" ht="16" customHeight="1">
@@ -12383,23 +12383,23 @@
       <c r="E208" s="48" t="n"/>
       <c r="F208" s="48" t="n"/>
       <c r="G208" s="71" t="n">
-        <v>0.1354297405028652</v>
+        <v>0.1005766192043441</v>
       </c>
       <c r="H208" s="71" t="n">
-        <v>0.1060956397830965</v>
+        <v>0.0867970053410605</v>
       </c>
       <c r="I208" s="71" t="n">
-        <v>0.1067208601608204</v>
+        <v>0.3488336159859114</v>
       </c>
       <c r="J208" s="71" t="n">
-        <v>0.02737188257324336</v>
+        <v>1.235006518904824</v>
       </c>
     </row>
     <row r="209" ht="8" customHeight="1"/>
     <row r="210" ht="18" customHeight="1">
       <c r="A210" s="94" t="inlineStr">
         <is>
-          <t>KN  —  Knowles Corporation</t>
+          <t>ITRI  —  Itron, Inc.</t>
         </is>
       </c>
       <c r="C210" s="37" t="inlineStr">
@@ -12409,7 +12409,7 @@
       </c>
       <c r="D210" s="74" t="inlineStr">
         <is>
-          <t>Mkt Cap: $3043M</t>
+          <t>Mkt Cap: $4193M</t>
         </is>
       </c>
       <c r="E210" s="95" t="n"/>
@@ -12476,28 +12476,28 @@
         </is>
       </c>
       <c r="C212" s="97" t="n">
-        <v>133.3</v>
+        <v>603.442</v>
       </c>
       <c r="D212" s="97" t="n">
-        <v>135.2</v>
+        <v>609.069</v>
       </c>
       <c r="E212" s="97" t="n">
-        <v>142.5</v>
+        <v>615.462</v>
       </c>
       <c r="F212" s="97" t="n">
-        <v>142.5</v>
+        <v>612.864</v>
       </c>
       <c r="G212" s="97" t="n">
-        <v>132.199999</v>
+        <v>607.151</v>
       </c>
       <c r="H212" s="97" t="n">
-        <v>145.9</v>
+        <v>606.761</v>
       </c>
       <c r="I212" s="97" t="n">
-        <v>152.9</v>
+        <v>581.625</v>
       </c>
       <c r="J212" s="97" t="n">
-        <v>162.2</v>
+        <v>571.657</v>
       </c>
     </row>
     <row r="213" ht="16" customHeight="1">
@@ -12508,28 +12508,28 @@
         </is>
       </c>
       <c r="C213" s="71" t="n">
-        <v>0.3720000000000001</v>
+        <v>0.34</v>
       </c>
       <c r="D213" s="71" t="n">
-        <v>0.402</v>
+        <v>0.346</v>
       </c>
       <c r="E213" s="71" t="n">
-        <v>0.411</v>
+        <v>0.341</v>
       </c>
       <c r="F213" s="71" t="n">
-        <v>0.402</v>
+        <v>0.349</v>
       </c>
       <c r="G213" s="71" t="n">
-        <v>0.384</v>
+        <v>0.358</v>
       </c>
       <c r="H213" s="71" t="n">
-        <v>0.408</v>
+        <v>0.369</v>
       </c>
       <c r="I213" s="71" t="n">
-        <v>0.4320000000000001</v>
+        <v>0.377</v>
       </c>
       <c r="J213" s="71" t="n">
-        <v>0.422</v>
+        <v>0.405</v>
       </c>
     </row>
     <row r="214" ht="16" customHeight="1">
@@ -12541,25 +12541,25 @@
       </c>
       <c r="C214" s="49" t="n"/>
       <c r="D214" s="75" t="n">
-        <v>0.01425356339084771</v>
+        <v>0.009324839835477145</v>
       </c>
       <c r="E214" s="75" t="n">
-        <v>0.05399408284023668</v>
+        <v>0.01049634770444728</v>
       </c>
       <c r="F214" s="75" t="n">
-        <v>0</v>
+        <v>-0.004221219181687903</v>
       </c>
       <c r="G214" s="75" t="n">
-        <v>-0.07228070877192982</v>
+        <v>-0.009321807121971596</v>
       </c>
       <c r="H214" s="75" t="n">
-        <v>0.1036308706779945</v>
+        <v>-0.0006423443262055074</v>
       </c>
       <c r="I214" s="75" t="n">
-        <v>0.04797806716929404</v>
+        <v>-0.04142652543588003</v>
       </c>
       <c r="J214" s="75" t="n">
-        <v>0.06082406801831262</v>
+        <v>-0.01713819041478616</v>
       </c>
     </row>
     <row r="215" ht="16" customHeight="1">
@@ -12574,16 +12574,16 @@
       <c r="E215" s="48" t="n"/>
       <c r="F215" s="48" t="n"/>
       <c r="G215" s="71" t="n">
-        <v>-0.008252070517629407</v>
+        <v>0.006146406779773367</v>
       </c>
       <c r="H215" s="71" t="n">
-        <v>0.07914201183431953</v>
+        <v>-0.003789390036268469</v>
       </c>
       <c r="I215" s="71" t="n">
-        <v>0.07298245614035087</v>
+        <v>-0.05497821148990514</v>
       </c>
       <c r="J215" s="71" t="n">
-        <v>0.1382456140350877</v>
+        <v>-0.06723677683792816</v>
       </c>
     </row>
     <row r="216" ht="8" customHeight="1"/>
@@ -15289,10 +15289,10 @@
         <v>68.7</v>
       </c>
       <c r="M7" s="35" t="n">
-        <v>70</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="N7" s="36" t="n">
-        <v>77.40000000000001</v>
+        <v>75.5</v>
       </c>
       <c r="O7" s="37" t="inlineStr">
         <is>
@@ -15365,10 +15365,10 @@
         <v>65.7</v>
       </c>
       <c r="M8" s="42" t="n">
-        <v>67.40000000000001</v>
+        <v>67.09999999999999</v>
       </c>
       <c r="N8" s="36" t="n">
-        <v>72.5</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="O8" s="43" t="inlineStr">
         <is>
@@ -15520,7 +15520,7 @@
         <v>64.90000000000001</v>
       </c>
       <c r="N10" s="22" t="n">
-        <v>65.8</v>
+        <v>65.5</v>
       </c>
       <c r="O10" s="43" t="inlineStr">
         <is>
@@ -15669,10 +15669,10 @@
         <v>62.1</v>
       </c>
       <c r="M12" s="42" t="n">
-        <v>62.4</v>
+        <v>63.1</v>
       </c>
       <c r="N12" s="22" t="n">
-        <v>63.3</v>
+        <v>66.09999999999999</v>
       </c>
       <c r="O12" s="43" t="inlineStr">
         <is>
@@ -15785,54 +15785,54 @@
       </c>
       <c r="B14" s="25" t="inlineStr">
         <is>
-          <t>QUIK</t>
+          <t>KVHI</t>
         </is>
       </c>
       <c r="C14" s="26" t="inlineStr">
         <is>
-          <t>QuickLogic Corporation</t>
+          <t>KVH Industries, Inc.</t>
         </is>
       </c>
       <c r="D14" s="27" t="n">
-        <v>197.1</v>
+        <v>138.8</v>
       </c>
       <c r="E14" s="39" t="n">
-        <v>11.125</v>
+        <v>7.1182</v>
       </c>
       <c r="F14" s="40" t="n">
-        <v>0.487</v>
+        <v>0.267</v>
       </c>
       <c r="G14" s="40" t="n">
-        <v>0.5870000000000001</v>
+        <v>0.338</v>
       </c>
       <c r="H14" s="40" t="n">
-        <v>0.439</v>
+        <v>0.3</v>
       </c>
       <c r="I14" s="40" t="n">
-        <v>0.283</v>
+        <v>0.008</v>
       </c>
       <c r="J14" s="40" t="n">
-        <v>0.06</v>
+        <v>0.35</v>
       </c>
       <c r="K14" s="41" t="n">
-        <v>74.59999999999999</v>
+        <v>81</v>
       </c>
       <c r="L14" s="41" t="n">
-        <v>57.6</v>
+        <v>58.4</v>
       </c>
       <c r="M14" s="42" t="n">
-        <v>61.6</v>
-      </c>
-      <c r="N14" s="36" t="n">
-        <v>75.59999999999999</v>
+        <v>59.4</v>
+      </c>
+      <c r="N14" s="22" t="n">
+        <v>62.3</v>
       </c>
       <c r="O14" s="43" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="P14" s="38" t="n">
-        <v>41.7</v>
+      <c r="P14" s="44" t="n">
+        <v>14.8</v>
       </c>
       <c r="Q14" s="45" t="inlineStr">
         <is>
@@ -15840,19 +15840,19 @@
         </is>
       </c>
       <c r="R14" s="40" t="n">
-        <v>-0.2338154</v>
+        <v>-0.1135492</v>
       </c>
       <c r="S14" s="40" t="n">
-        <v>-0.4646295</v>
+        <v>-0.07315100000000001</v>
       </c>
       <c r="T14" s="40" t="n">
-        <v>0.2772675</v>
+        <v>0.2044332</v>
       </c>
       <c r="U14" s="40" t="n">
-        <v>0.8510814999999999</v>
+        <v>0.0212626</v>
       </c>
       <c r="V14" s="40" t="n">
-        <v>1.1942801</v>
+        <v>0.1612072</v>
       </c>
     </row>
     <row r="17" ht="22" customHeight="1">
@@ -16116,20 +16116,20 @@
     <row r="28" ht="16" customHeight="1">
       <c r="A28" s="25" t="inlineStr">
         <is>
-          <t>QUIK</t>
+          <t>KVHI</t>
         </is>
       </c>
       <c r="B28" s="41" t="n">
-        <v>97.40000000000001</v>
+        <v>53.4</v>
       </c>
       <c r="C28" s="41" t="n">
+        <v>75</v>
+      </c>
+      <c r="D28" s="41" t="n">
         <v>100</v>
       </c>
-      <c r="D28" s="41" t="n">
-        <v>6.8</v>
-      </c>
       <c r="E28" s="41" t="n">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="F28" s="41" t="n">
         <v>100</v>
@@ -16304,17 +16304,17 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>QUIK</t>
+          <t>KVHI</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>43.9</v>
+        <v>30</v>
       </c>
       <c r="C70" t="n">
-        <v>48.7</v>
+        <v>26.7</v>
       </c>
       <c r="D70" t="n">
-        <v>197.1</v>
+        <v>138.8</v>
       </c>
     </row>
   </sheetData>
@@ -16792,10 +16792,10 @@
         <v>85.40000000000001</v>
       </c>
       <c r="M5" s="35" t="n">
-        <v>79.2</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="N5" s="22" t="n">
-        <v>60.7</v>
+        <v>61.4</v>
       </c>
       <c r="O5" s="37" t="inlineStr">
         <is>
@@ -16868,10 +16868,10 @@
         <v>85.40000000000001</v>
       </c>
       <c r="M6" s="42" t="n">
-        <v>78.7</v>
+        <v>78.5</v>
       </c>
       <c r="N6" s="22" t="n">
-        <v>58.7</v>
+        <v>57.8</v>
       </c>
       <c r="O6" s="43" t="inlineStr">
         <is>
@@ -16947,7 +16947,7 @@
         <v>75.09999999999999</v>
       </c>
       <c r="N7" s="22" t="n">
-        <v>52.8</v>
+        <v>52.5</v>
       </c>
       <c r="O7" s="37" t="inlineStr">
         <is>
@@ -16984,46 +16984,46 @@
       </c>
       <c r="B8" s="25" t="inlineStr">
         <is>
-          <t>LXFR</t>
+          <t>EVLV</t>
         </is>
       </c>
       <c r="C8" s="26" t="inlineStr">
         <is>
-          <t>Luxfer Holdings PLC</t>
+          <t>Evolv Technologies Holdings, Inc.</t>
         </is>
       </c>
       <c r="D8" s="27" t="n">
-        <v>463.9</v>
+        <v>912.8</v>
       </c>
       <c r="E8" s="39" t="n">
-        <v>17.33</v>
+        <v>5.089</v>
       </c>
       <c r="F8" s="40" t="n">
-        <v>-0.08</v>
+        <v>0.344</v>
       </c>
       <c r="G8" s="40" t="n">
-        <v>-0.123</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H8" s="40" t="n">
-        <v>0.256</v>
+        <v>0.502</v>
       </c>
       <c r="I8" s="40" t="n">
-        <v>-0.005</v>
+        <v>0.199</v>
       </c>
       <c r="J8" s="40" t="n">
-        <v>0.021</v>
+        <v>0.052</v>
       </c>
       <c r="K8" s="41" t="n">
-        <v>53.8</v>
+        <v>66.59999999999999</v>
       </c>
       <c r="L8" s="41" t="n">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="M8" s="42" t="n">
-        <v>74</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="N8" s="22" t="n">
-        <v>59</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="O8" s="43" t="inlineStr">
         <is>
@@ -17031,7 +17031,7 @@
         </is>
       </c>
       <c r="P8" s="44" t="n">
-        <v>34.7</v>
+        <v>2.3</v>
       </c>
       <c r="Q8" s="23" t="inlineStr">
         <is>
@@ -17039,19 +17039,19 @@
         </is>
       </c>
       <c r="R8" s="40" t="n">
-        <v>0.0134503</v>
+        <v>-0.1703263</v>
       </c>
       <c r="S8" s="40" t="n">
-        <v>-0.007445589900000001</v>
+        <v>-0.126134</v>
       </c>
       <c r="T8" s="40" t="n">
-        <v>0.4465776</v>
+        <v>0.0011614173</v>
       </c>
       <c r="U8" s="40" t="n">
-        <v>0.2808574</v>
+        <v>-0.2896788</v>
       </c>
       <c r="V8" s="40" t="n">
-        <v>0.2733284</v>
+        <v>-0.3850181</v>
       </c>
     </row>
     <row r="9" ht="16" customHeight="1">
@@ -17060,54 +17060,54 @@
       </c>
       <c r="B9" s="19" t="inlineStr">
         <is>
-          <t>CLFD</t>
+          <t>GHM</t>
         </is>
       </c>
       <c r="C9" s="20" t="inlineStr">
         <is>
-          <t>Clearfield, Inc.</t>
+          <t>Graham Corporation</t>
         </is>
       </c>
       <c r="D9" s="21" t="n">
-        <v>394.6</v>
+        <v>1046.6</v>
       </c>
       <c r="E9" s="32" t="n">
-        <v>29.0914</v>
+        <v>89.42</v>
       </c>
       <c r="F9" s="33" t="n">
-        <v>-0.121</v>
+        <v>0.286</v>
       </c>
       <c r="G9" s="33" t="n">
-        <v>-0.144</v>
+        <v>0.175</v>
       </c>
       <c r="H9" s="33" t="n">
-        <v>0.318</v>
+        <v>0.25</v>
       </c>
       <c r="I9" s="33" t="n">
-        <v>-0.109</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="J9" s="33" t="n">
-        <v>0.18</v>
+        <v>0.051</v>
       </c>
       <c r="K9" s="34" t="n">
-        <v>68</v>
+        <v>68.7</v>
       </c>
       <c r="L9" s="34" t="n">
-        <v>68.8</v>
+        <v>88.40000000000001</v>
       </c>
       <c r="M9" s="35" t="n">
-        <v>73.90000000000001</v>
-      </c>
-      <c r="N9" s="36" t="n">
-        <v>89.2</v>
+        <v>70.8</v>
+      </c>
+      <c r="N9" s="22" t="n">
+        <v>59.9</v>
       </c>
       <c r="O9" s="37" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="P9" s="44" t="n">
-        <v>8.800000000000001</v>
+      <c r="P9" s="38" t="n">
+        <v>65.90000000000001</v>
       </c>
       <c r="Q9" s="23" t="inlineStr">
         <is>
@@ -17115,19 +17115,19 @@
         </is>
       </c>
       <c r="R9" s="33" t="n">
-        <v>0.058639</v>
+        <v>-0.1993195</v>
       </c>
       <c r="S9" s="33" t="n">
-        <v>-0.29218</v>
+        <v>-0.0620936</v>
       </c>
       <c r="T9" s="33" t="n">
-        <v>-0.0306098</v>
+        <v>0.09556480000000001</v>
       </c>
       <c r="U9" s="33" t="n">
-        <v>-0.0020102916</v>
+        <v>0.3921843</v>
       </c>
       <c r="V9" s="33" t="n">
-        <v>-0.135214</v>
+        <v>0.8711027</v>
       </c>
     </row>
     <row r="10" ht="16" customHeight="1">
@@ -17136,46 +17136,46 @@
       </c>
       <c r="B10" s="25" t="inlineStr">
         <is>
-          <t>ARRY</t>
+          <t>ADTN</t>
         </is>
       </c>
       <c r="C10" s="26" t="inlineStr">
         <is>
-          <t>Array Technologies, Inc.</t>
+          <t>ADTRAN Holdings Inc.</t>
         </is>
       </c>
       <c r="D10" s="27" t="n">
-        <v>742.2</v>
+        <v>608.1</v>
       </c>
       <c r="E10" s="39" t="n">
-        <v>4.825</v>
+        <v>7.53</v>
       </c>
       <c r="F10" s="40" t="n">
-        <v>-0.05599999999999999</v>
+        <v>0.061</v>
       </c>
       <c r="G10" s="40" t="n">
-        <v>-0.472</v>
+        <v>-0.112</v>
       </c>
       <c r="H10" s="40" t="n">
-        <v>0.291</v>
+        <v>0.37</v>
       </c>
       <c r="I10" s="40" t="n">
+        <v>0.029</v>
+      </c>
+      <c r="J10" s="40" t="n">
         <v>0.019</v>
       </c>
-      <c r="J10" s="40" t="n">
-        <v>0.091</v>
-      </c>
       <c r="K10" s="41" t="n">
-        <v>63.2</v>
+        <v>48.3</v>
       </c>
       <c r="L10" s="41" t="n">
-        <v>78.09999999999999</v>
+        <v>76.7</v>
       </c>
       <c r="M10" s="42" t="n">
-        <v>72.59999999999999</v>
+        <v>70.5</v>
       </c>
       <c r="N10" s="22" t="n">
-        <v>56.2</v>
+        <v>51.9</v>
       </c>
       <c r="O10" s="43" t="inlineStr">
         <is>
@@ -17183,7 +17183,7 @@
         </is>
       </c>
       <c r="P10" s="44" t="n">
-        <v>3.2</v>
+        <v>1.9</v>
       </c>
       <c r="Q10" s="23" t="inlineStr">
         <is>
@@ -17191,19 +17191,19 @@
         </is>
       </c>
       <c r="R10" s="40" t="n">
-        <v>-0.1306306</v>
+        <v>-0.003968254</v>
       </c>
       <c r="S10" s="40" t="n">
-        <v>-0.3845663</v>
+        <v>-0.5299625</v>
       </c>
       <c r="T10" s="40" t="n">
-        <v>-0.2914831</v>
+        <v>-0.2148071</v>
       </c>
       <c r="U10" s="40" t="n">
-        <v>-0.4766811</v>
+        <v>-0.1334868</v>
       </c>
       <c r="V10" s="40" t="n">
-        <v>-0.4485714</v>
+        <v>-0.2617647</v>
       </c>
     </row>
     <row r="11" ht="16" customHeight="1">
@@ -17212,46 +17212,46 @@
       </c>
       <c r="B11" s="19" t="inlineStr">
         <is>
-          <t>EVLV</t>
+          <t>ARLO</t>
         </is>
       </c>
       <c r="C11" s="20" t="inlineStr">
         <is>
-          <t>Evolv Technologies Holdings, Inc.</t>
+          <t>Arlo Technologies, Inc.</t>
         </is>
       </c>
       <c r="D11" s="21" t="n">
-        <v>912.8</v>
+        <v>1512.9</v>
       </c>
       <c r="E11" s="32" t="n">
-        <v>5.089</v>
+        <v>13.935</v>
       </c>
       <c r="F11" s="33" t="n">
-        <v>0.344</v>
+        <v>0.205</v>
       </c>
       <c r="G11" s="33" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.19</v>
       </c>
       <c r="H11" s="33" t="n">
-        <v>0.502</v>
+        <v>0.482</v>
       </c>
       <c r="I11" s="33" t="n">
-        <v>0.199</v>
+        <v>0.147</v>
       </c>
       <c r="J11" s="33" t="n">
-        <v>0.052</v>
+        <v>0.03</v>
       </c>
       <c r="K11" s="34" t="n">
-        <v>66.59999999999999</v>
+        <v>63.7</v>
       </c>
       <c r="L11" s="34" t="n">
-        <v>74</v>
+        <v>73.2</v>
       </c>
       <c r="M11" s="35" t="n">
-        <v>72.09999999999999</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="N11" s="22" t="n">
-        <v>66.40000000000001</v>
+        <v>58.7</v>
       </c>
       <c r="O11" s="37" t="inlineStr">
         <is>
@@ -17259,7 +17259,7 @@
         </is>
       </c>
       <c r="P11" s="44" t="n">
-        <v>2.3</v>
+        <v>13.3</v>
       </c>
       <c r="Q11" s="23" t="inlineStr">
         <is>
@@ -17267,19 +17267,19 @@
         </is>
       </c>
       <c r="R11" s="33" t="n">
-        <v>-0.1703263</v>
+        <v>-0.08502950000000001</v>
       </c>
       <c r="S11" s="33" t="n">
-        <v>-0.126134</v>
+        <v>0.09984209999999999</v>
       </c>
       <c r="T11" s="33" t="n">
-        <v>0.0011614173</v>
+        <v>0.0025179856</v>
       </c>
       <c r="U11" s="33" t="n">
-        <v>-0.2896788</v>
+        <v>-0.0039313796</v>
       </c>
       <c r="V11" s="33" t="n">
-        <v>-0.3850181</v>
+        <v>-0.2296849</v>
       </c>
     </row>
     <row r="12" ht="16" customHeight="1">
@@ -17288,54 +17288,54 @@
       </c>
       <c r="B12" s="25" t="inlineStr">
         <is>
-          <t>GHM</t>
+          <t>TRC</t>
         </is>
       </c>
       <c r="C12" s="26" t="inlineStr">
         <is>
-          <t>Graham Corporation</t>
+          <t>Tejon Ranch Co.</t>
         </is>
       </c>
       <c r="D12" s="27" t="n">
-        <v>1046.6</v>
+        <v>446.5</v>
       </c>
       <c r="E12" s="39" t="n">
-        <v>89.42</v>
+        <v>16.5237</v>
       </c>
       <c r="F12" s="40" t="n">
-        <v>0.286</v>
+        <v>0.7170000000000001</v>
       </c>
       <c r="G12" s="40" t="n">
-        <v>0.175</v>
+        <v>0.257</v>
       </c>
       <c r="H12" s="40" t="n">
-        <v>0.25</v>
+        <v>0.224</v>
       </c>
       <c r="I12" s="40" t="n">
-        <v>0.08400000000000001</v>
+        <v>-0.014</v>
       </c>
       <c r="J12" s="40" t="n">
-        <v>0.051</v>
+        <v>0.081</v>
       </c>
       <c r="K12" s="41" t="n">
-        <v>68.7</v>
+        <v>88.40000000000001</v>
       </c>
       <c r="L12" s="41" t="n">
-        <v>88.40000000000001</v>
+        <v>69.40000000000001</v>
       </c>
       <c r="M12" s="42" t="n">
-        <v>70.7</v>
+        <v>69.3</v>
       </c>
       <c r="N12" s="22" t="n">
-        <v>59.7</v>
+        <v>68.90000000000001</v>
       </c>
       <c r="O12" s="43" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="P12" s="38" t="n">
-        <v>65.90000000000001</v>
+      <c r="P12" s="44" t="n">
+        <v>7.5</v>
       </c>
       <c r="Q12" s="23" t="inlineStr">
         <is>
@@ -17343,19 +17343,19 @@
         </is>
       </c>
       <c r="R12" s="40" t="n">
-        <v>-0.1993195</v>
+        <v>-0.009964050300000001</v>
       </c>
       <c r="S12" s="40" t="n">
-        <v>-0.0620936</v>
+        <v>-0.1380438</v>
       </c>
       <c r="T12" s="40" t="n">
-        <v>0.09556480000000001</v>
+        <v>-0.0779185</v>
       </c>
       <c r="U12" s="40" t="n">
-        <v>0.3921843</v>
+        <v>0.0477933</v>
       </c>
       <c r="V12" s="40" t="n">
-        <v>0.8711027</v>
+        <v>-0.0251504</v>
       </c>
     </row>
     <row r="13" ht="16" customHeight="1">
@@ -17364,46 +17364,46 @@
       </c>
       <c r="B13" s="19" t="inlineStr">
         <is>
-          <t>NNDM</t>
+          <t>INOD</t>
         </is>
       </c>
       <c r="C13" s="20" t="inlineStr">
         <is>
-          <t>Nano Dimension Ltd.</t>
+          <t>Innodata Inc.</t>
         </is>
       </c>
       <c r="D13" s="21" t="n">
-        <v>327.3</v>
+        <v>1822.2</v>
       </c>
       <c r="E13" s="32" t="n">
-        <v>1.55</v>
+        <v>55.93</v>
       </c>
       <c r="F13" s="33" t="n">
-        <v>0.121</v>
+        <v>0.578</v>
       </c>
       <c r="G13" s="33" t="n">
-        <v>-0.603</v>
+        <v>-0.216</v>
       </c>
       <c r="H13" s="33" t="n">
-        <v>0.459</v>
+        <v>0.461</v>
       </c>
       <c r="I13" s="33" t="n">
-        <v>-0.183</v>
+        <v>0.176</v>
       </c>
       <c r="J13" s="33" t="n">
-        <v>0.036</v>
+        <v>0.051</v>
       </c>
       <c r="K13" s="34" t="n">
-        <v>52.7</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="L13" s="34" t="n">
-        <v>71</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="M13" s="35" t="n">
-        <v>70.5</v>
+        <v>68.2</v>
       </c>
       <c r="N13" s="22" t="n">
-        <v>69.2</v>
+        <v>61.7</v>
       </c>
       <c r="O13" s="37" t="inlineStr">
         <is>
@@ -17411,7 +17411,7 @@
         </is>
       </c>
       <c r="P13" s="44" t="n">
-        <v>14.5</v>
+        <v>22.8</v>
       </c>
       <c r="Q13" s="23" t="inlineStr">
         <is>
@@ -17419,19 +17419,19 @@
         </is>
       </c>
       <c r="R13" s="33" t="n">
-        <v>-0.0490798</v>
+        <v>-0.1026793</v>
       </c>
       <c r="S13" s="33" t="n">
-        <v>0.0264901</v>
+        <v>-0.4558809</v>
       </c>
       <c r="T13" s="33" t="n">
-        <v>-0.1483516</v>
+        <v>0.2387597</v>
       </c>
       <c r="U13" s="33" t="n">
-        <v>0.0064935065</v>
+        <v>0.09774290000000001</v>
       </c>
       <c r="V13" s="33" t="n">
-        <v>0.0763889</v>
+        <v>0.1720453</v>
       </c>
     </row>
     <row r="14" ht="16" customHeight="1">
@@ -17440,46 +17440,46 @@
       </c>
       <c r="B14" s="25" t="inlineStr">
         <is>
-          <t>ADTN</t>
+          <t>CDRE</t>
         </is>
       </c>
       <c r="C14" s="26" t="inlineStr">
         <is>
-          <t>ADTRAN Holdings Inc.</t>
+          <t>Cadre Holdings, Inc.</t>
         </is>
       </c>
       <c r="D14" s="27" t="n">
-        <v>608.1</v>
+        <v>1279.2</v>
       </c>
       <c r="E14" s="39" t="n">
-        <v>7.53</v>
+        <v>29.925</v>
       </c>
       <c r="F14" s="40" t="n">
-        <v>0.061</v>
+        <v>0.318</v>
       </c>
       <c r="G14" s="40" t="n">
-        <v>-0.112</v>
+        <v>0.229</v>
       </c>
       <c r="H14" s="40" t="n">
-        <v>0.37</v>
+        <v>0.421</v>
       </c>
       <c r="I14" s="40" t="n">
-        <v>0.029</v>
+        <v>0.139</v>
       </c>
       <c r="J14" s="40" t="n">
-        <v>0.019</v>
+        <v>0.343</v>
       </c>
       <c r="K14" s="41" t="n">
-        <v>48.3</v>
+        <v>82</v>
       </c>
       <c r="L14" s="41" t="n">
-        <v>76.7</v>
+        <v>67.3</v>
       </c>
       <c r="M14" s="42" t="n">
-        <v>70.40000000000001</v>
+        <v>67</v>
       </c>
       <c r="N14" s="22" t="n">
-        <v>51.5</v>
+        <v>66.2</v>
       </c>
       <c r="O14" s="43" t="inlineStr">
         <is>
@@ -17487,7 +17487,7 @@
         </is>
       </c>
       <c r="P14" s="44" t="n">
-        <v>1.9</v>
+        <v>8</v>
       </c>
       <c r="Q14" s="23" t="inlineStr">
         <is>
@@ -17495,19 +17495,19 @@
         </is>
       </c>
       <c r="R14" s="40" t="n">
-        <v>-0.003968254</v>
+        <v>-0.08820840000000001</v>
       </c>
       <c r="S14" s="40" t="n">
-        <v>-0.5299625</v>
+        <v>-0.0081206497</v>
       </c>
       <c r="T14" s="40" t="n">
-        <v>-0.2148071</v>
+        <v>-0.3122271</v>
       </c>
       <c r="U14" s="40" t="n">
-        <v>-0.1334868</v>
+        <v>-0.2672625</v>
       </c>
       <c r="V14" s="40" t="n">
-        <v>-0.2617647</v>
+        <v>-0.0610292</v>
       </c>
     </row>
     <row r="17" ht="22" customHeight="1">
@@ -17639,130 +17639,130 @@
     <row r="22" ht="16" customHeight="1">
       <c r="A22" s="25" t="inlineStr">
         <is>
-          <t>LXFR</t>
+          <t>EVLV</t>
         </is>
       </c>
       <c r="B22" s="41" t="n">
-        <v>0</v>
+        <v>68.8</v>
       </c>
       <c r="C22" s="41" t="n">
-        <v>64</v>
+        <v>100</v>
       </c>
       <c r="D22" s="41" t="n">
-        <v>100</v>
+        <v>40.4</v>
       </c>
       <c r="E22" s="41" t="n">
-        <v>21</v>
+        <v>52</v>
       </c>
       <c r="F22" s="41" t="n">
-        <v>19.2</v>
+        <v>67.5</v>
       </c>
     </row>
     <row r="23" ht="16" customHeight="1">
       <c r="A23" s="19" t="inlineStr">
         <is>
-          <t>CLFD</t>
+          <t>GHM</t>
         </is>
       </c>
       <c r="B23" s="34" t="n">
-        <v>0</v>
+        <v>57.2</v>
       </c>
       <c r="C23" s="34" t="n">
-        <v>79.5</v>
+        <v>62.5</v>
       </c>
       <c r="D23" s="34" t="n">
-        <v>100</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="E23" s="34" t="n">
-        <v>100</v>
+        <v>51</v>
       </c>
       <c r="F23" s="34" t="n">
-        <v>14</v>
+        <v>93.8</v>
       </c>
     </row>
     <row r="24" ht="16" customHeight="1">
       <c r="A24" s="25" t="inlineStr">
         <is>
-          <t>ARRY</t>
+          <t>ADTN</t>
         </is>
       </c>
       <c r="B24" s="41" t="n">
-        <v>0</v>
+        <v>12.2</v>
       </c>
       <c r="C24" s="41" t="n">
-        <v>72.8</v>
+        <v>92.5</v>
       </c>
       <c r="D24" s="41" t="n">
         <v>100</v>
       </c>
       <c r="E24" s="41" t="n">
-        <v>91</v>
+        <v>19</v>
       </c>
       <c r="F24" s="41" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
     </row>
     <row r="25" ht="16" customHeight="1">
       <c r="A25" s="19" t="inlineStr">
         <is>
-          <t>EVLV</t>
+          <t>ARLO</t>
         </is>
       </c>
       <c r="B25" s="34" t="n">
-        <v>68.8</v>
+        <v>41</v>
       </c>
       <c r="C25" s="34" t="n">
         <v>100</v>
       </c>
       <c r="D25" s="34" t="n">
-        <v>40.4</v>
+        <v>61.2</v>
       </c>
       <c r="E25" s="34" t="n">
-        <v>52</v>
+        <v>30</v>
       </c>
       <c r="F25" s="34" t="n">
-        <v>67.5</v>
+        <v>97.5</v>
       </c>
     </row>
     <row r="26" ht="16" customHeight="1">
       <c r="A26" s="25" t="inlineStr">
         <is>
-          <t>GHM</t>
+          <t>TRC</t>
         </is>
       </c>
       <c r="B26" s="41" t="n">
-        <v>57.2</v>
+        <v>100</v>
       </c>
       <c r="C26" s="41" t="n">
-        <v>62.5</v>
+        <v>56</v>
       </c>
       <c r="D26" s="41" t="n">
-        <v>86.40000000000001</v>
+        <v>100</v>
       </c>
       <c r="E26" s="41" t="n">
-        <v>51</v>
+        <v>81</v>
       </c>
       <c r="F26" s="41" t="n">
-        <v>93.8</v>
+        <v>100</v>
       </c>
     </row>
     <row r="27" ht="16" customHeight="1">
       <c r="A27" s="19" t="inlineStr">
         <is>
-          <t>NNDM</t>
+          <t>INOD</t>
         </is>
       </c>
       <c r="B27" s="34" t="n">
-        <v>24.2</v>
+        <v>100</v>
       </c>
       <c r="C27" s="34" t="n">
         <v>100</v>
       </c>
       <c r="D27" s="34" t="n">
-        <v>100</v>
+        <v>49.6</v>
       </c>
       <c r="E27" s="34" t="n">
-        <v>36</v>
+        <v>51</v>
       </c>
       <c r="F27" s="34" t="n">
         <v>0</v>
@@ -17771,23 +17771,23 @@
     <row r="28" ht="16" customHeight="1">
       <c r="A28" s="25" t="inlineStr">
         <is>
-          <t>ADTN</t>
+          <t>CDRE</t>
         </is>
       </c>
       <c r="B28" s="41" t="n">
-        <v>12.2</v>
+        <v>63.6</v>
       </c>
       <c r="C28" s="41" t="n">
-        <v>92.5</v>
+        <v>100</v>
       </c>
       <c r="D28" s="41" t="n">
+        <v>64.40000000000001</v>
+      </c>
+      <c r="E28" s="41" t="n">
         <v>100</v>
       </c>
-      <c r="E28" s="41" t="n">
-        <v>19</v>
-      </c>
       <c r="F28" s="41" t="n">
-        <v>22</v>
+        <v>100</v>
       </c>
     </row>
     <row r="60">
@@ -17863,113 +17863,113 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>LXFR</t>
+          <t>EVLV</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>25.6</v>
+        <v>50.2</v>
       </c>
       <c r="C64" t="n">
-        <v>-8</v>
+        <v>34.4</v>
       </c>
       <c r="D64" t="n">
-        <v>463.9</v>
+        <v>912.8</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>CLFD</t>
+          <t>GHM</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>31.8</v>
+        <v>25</v>
       </c>
       <c r="C65" t="n">
-        <v>-12.1</v>
+        <v>28.6</v>
       </c>
       <c r="D65" t="n">
-        <v>394.6</v>
+        <v>1046.6</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>ARRY</t>
+          <t>ADTN</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>29.1</v>
+        <v>37</v>
       </c>
       <c r="C66" t="n">
-        <v>-5.6</v>
+        <v>6.1</v>
       </c>
       <c r="D66" t="n">
-        <v>742.2</v>
+        <v>608.1</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>EVLV</t>
+          <t>ARLO</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>50.2</v>
+        <v>48.2</v>
       </c>
       <c r="C67" t="n">
-        <v>34.4</v>
+        <v>20.5</v>
       </c>
       <c r="D67" t="n">
-        <v>912.8</v>
+        <v>1512.9</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>GHM</t>
+          <t>TRC</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>25</v>
+        <v>22.4</v>
       </c>
       <c r="C68" t="n">
-        <v>28.6</v>
+        <v>71.7</v>
       </c>
       <c r="D68" t="n">
-        <v>1046.6</v>
+        <v>446.5</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>NNDM</t>
+          <t>INOD</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>45.9</v>
+        <v>46.1</v>
       </c>
       <c r="C69" t="n">
-        <v>12.1</v>
+        <v>57.8</v>
       </c>
       <c r="D69" t="n">
-        <v>327.3</v>
+        <v>1822.2</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>ADTN</t>
+          <t>CDRE</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>37</v>
+        <v>42.1</v>
       </c>
       <c r="C70" t="n">
-        <v>6.1</v>
+        <v>31.8</v>
       </c>
       <c r="D70" t="n">
-        <v>608.1</v>
+        <v>1279.2</v>
       </c>
     </row>
   </sheetData>
@@ -18447,10 +18447,10 @@
         <v>83.90000000000001</v>
       </c>
       <c r="M5" s="35" t="n">
-        <v>77.2</v>
+        <v>77.5</v>
       </c>
       <c r="N5" s="22" t="n">
-        <v>57.1</v>
+        <v>58.3</v>
       </c>
       <c r="O5" s="37" t="inlineStr">
         <is>
@@ -18599,10 +18599,10 @@
         <v>79.40000000000001</v>
       </c>
       <c r="M7" s="35" t="n">
-        <v>73</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="N7" s="22" t="n">
-        <v>53.9</v>
+        <v>54</v>
       </c>
       <c r="O7" s="37" t="inlineStr">
         <is>
@@ -18675,10 +18675,10 @@
         <v>79.59999999999999</v>
       </c>
       <c r="M8" s="42" t="n">
-        <v>71.5</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="N8" s="22" t="n">
-        <v>57.8</v>
+        <v>58</v>
       </c>
       <c r="O8" s="43" t="inlineStr">
         <is>
@@ -18715,46 +18715,46 @@
       </c>
       <c r="B9" s="19" t="inlineStr">
         <is>
-          <t>BRC</t>
+          <t>MRCY</t>
         </is>
       </c>
       <c r="C9" s="20" t="inlineStr">
         <is>
-          <t>Brady Corporation</t>
+          <t>Mercury Systems, Inc.</t>
         </is>
       </c>
       <c r="D9" s="21" t="n">
-        <v>4139.7</v>
+        <v>5093.4</v>
       </c>
       <c r="E9" s="32" t="n">
-        <v>87.88</v>
+        <v>84.825</v>
       </c>
       <c r="F9" s="33" t="n">
-        <v>0.1</v>
+        <v>0.061</v>
       </c>
       <c r="G9" s="33" t="n">
-        <v>-0.057</v>
+        <v>-0.038</v>
       </c>
       <c r="H9" s="33" t="n">
-        <v>0.529</v>
+        <v>0.273</v>
       </c>
       <c r="I9" s="33" t="n">
-        <v>-0.025</v>
+        <v>0.043</v>
       </c>
       <c r="J9" s="33" t="n">
-        <v>0.1</v>
+        <v>0.075</v>
       </c>
       <c r="K9" s="34" t="n">
-        <v>66.40000000000001</v>
+        <v>54.6</v>
       </c>
       <c r="L9" s="34" t="n">
-        <v>75.2</v>
+        <v>71.2</v>
       </c>
       <c r="M9" s="35" t="n">
-        <v>69.90000000000001</v>
+        <v>69.8</v>
       </c>
       <c r="N9" s="22" t="n">
-        <v>54</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="O9" s="37" t="inlineStr">
         <is>
@@ -18762,7 +18762,7 @@
         </is>
       </c>
       <c r="P9" s="44" t="n">
-        <v>31.9</v>
+        <v>27</v>
       </c>
       <c r="Q9" s="23" t="inlineStr">
         <is>
@@ -18770,19 +18770,19 @@
         </is>
       </c>
       <c r="R9" s="33" t="n">
-        <v>-0.0942074</v>
+        <v>-0.2192102</v>
       </c>
       <c r="S9" s="33" t="n">
-        <v>0.1673751</v>
+        <v>-0.2353975</v>
       </c>
       <c r="T9" s="33" t="n">
-        <v>-0.0183199</v>
+        <v>-0.0184564</v>
       </c>
       <c r="U9" s="33" t="n">
-        <v>0.1213475</v>
+        <v>0.1618271</v>
       </c>
       <c r="V9" s="33" t="n">
-        <v>0.0930348</v>
+        <v>0.2350757</v>
       </c>
     </row>
     <row r="10" ht="16" customHeight="1">
@@ -18791,46 +18791,46 @@
       </c>
       <c r="B10" s="25" t="inlineStr">
         <is>
-          <t>MRCY</t>
+          <t>BRC</t>
         </is>
       </c>
       <c r="C10" s="26" t="inlineStr">
         <is>
-          <t>Mercury Systems, Inc.</t>
+          <t>Brady Corporation</t>
         </is>
       </c>
       <c r="D10" s="27" t="n">
-        <v>5093.4</v>
+        <v>4139.7</v>
       </c>
       <c r="E10" s="39" t="n">
-        <v>84.825</v>
+        <v>87.88</v>
       </c>
       <c r="F10" s="40" t="n">
-        <v>0.061</v>
+        <v>0.1</v>
       </c>
       <c r="G10" s="40" t="n">
-        <v>-0.038</v>
+        <v>-0.057</v>
       </c>
       <c r="H10" s="40" t="n">
-        <v>0.273</v>
+        <v>0.529</v>
       </c>
       <c r="I10" s="40" t="n">
-        <v>0.043</v>
+        <v>-0.025</v>
       </c>
       <c r="J10" s="40" t="n">
-        <v>0.075</v>
+        <v>0.1</v>
       </c>
       <c r="K10" s="41" t="n">
-        <v>54.6</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="L10" s="41" t="n">
-        <v>71.2</v>
+        <v>75.2</v>
       </c>
       <c r="M10" s="42" t="n">
-        <v>69.8</v>
+        <v>69.7</v>
       </c>
       <c r="N10" s="22" t="n">
-        <v>65.59999999999999</v>
+        <v>53.1</v>
       </c>
       <c r="O10" s="43" t="inlineStr">
         <is>
@@ -18838,7 +18838,7 @@
         </is>
       </c>
       <c r="P10" s="44" t="n">
-        <v>27</v>
+        <v>31.9</v>
       </c>
       <c r="Q10" s="23" t="inlineStr">
         <is>
@@ -18846,19 +18846,19 @@
         </is>
       </c>
       <c r="R10" s="40" t="n">
-        <v>-0.2192102</v>
+        <v>-0.0942074</v>
       </c>
       <c r="S10" s="40" t="n">
-        <v>-0.2353975</v>
+        <v>0.1673751</v>
       </c>
       <c r="T10" s="40" t="n">
-        <v>-0.0184564</v>
+        <v>-0.0183199</v>
       </c>
       <c r="U10" s="40" t="n">
-        <v>0.1618271</v>
+        <v>0.1213475</v>
       </c>
       <c r="V10" s="40" t="n">
-        <v>0.2350757</v>
+        <v>0.0930348</v>
       </c>
     </row>
     <row r="11" ht="16" customHeight="1">
@@ -18943,46 +18943,46 @@
       </c>
       <c r="B12" s="25" t="inlineStr">
         <is>
-          <t>RUN</t>
+          <t>LYFT</t>
         </is>
       </c>
       <c r="C12" s="26" t="inlineStr">
         <is>
-          <t>Sunrun Inc.</t>
+          <t>Lyft, Inc.</t>
         </is>
       </c>
       <c r="D12" s="27" t="n">
-        <v>2188.7</v>
+        <v>6122.4</v>
       </c>
       <c r="E12" s="39" t="n">
-        <v>9.167999999999999</v>
+        <v>16.14</v>
       </c>
       <c r="F12" s="40" t="n">
-        <v>0.528</v>
+        <v>0.161</v>
       </c>
       <c r="G12" s="40" t="n">
-        <v>0.441</v>
+        <v>0.055</v>
       </c>
       <c r="H12" s="40" t="n">
-        <v>0.377</v>
+        <v>0.4970000000000001</v>
       </c>
       <c r="I12" s="40" t="n">
-        <v>0.1</v>
+        <v>-0.023</v>
       </c>
       <c r="J12" s="40" t="n">
-        <v>0.035</v>
+        <v>0.101</v>
       </c>
       <c r="K12" s="41" t="n">
-        <v>85.09999999999999</v>
+        <v>74.2</v>
       </c>
       <c r="L12" s="41" t="n">
-        <v>71.09999999999999</v>
+        <v>77.59999999999999</v>
       </c>
       <c r="M12" s="42" t="n">
-        <v>69.09999999999999</v>
-      </c>
-      <c r="N12" s="22" t="n">
-        <v>63.2</v>
+        <v>69</v>
+      </c>
+      <c r="N12" s="41" t="n">
+        <v>43.1</v>
       </c>
       <c r="O12" s="43" t="inlineStr">
         <is>
@@ -18990,7 +18990,7 @@
         </is>
       </c>
       <c r="P12" s="44" t="n">
-        <v>3.3</v>
+        <v>12.3</v>
       </c>
       <c r="Q12" s="23" t="inlineStr">
         <is>
@@ -18998,19 +18998,19 @@
         </is>
       </c>
       <c r="R12" s="40" t="n">
-        <v>-0.1011765</v>
+        <v>-0.0756014</v>
       </c>
       <c r="S12" s="40" t="n">
-        <v>-0.3188707</v>
+        <v>0.1512126</v>
       </c>
       <c r="T12" s="40" t="n">
-        <v>-0.1915344</v>
+        <v>0.2181132</v>
       </c>
       <c r="U12" s="40" t="n">
-        <v>-0.5017391</v>
+        <v>-0.1667527</v>
       </c>
       <c r="V12" s="40" t="n">
-        <v>-0.458156</v>
+        <v>-0.08865050000000001</v>
       </c>
     </row>
     <row r="13" ht="16" customHeight="1">
@@ -19019,46 +19019,46 @@
       </c>
       <c r="B13" s="19" t="inlineStr">
         <is>
-          <t>LYFT</t>
+          <t>RUN</t>
         </is>
       </c>
       <c r="C13" s="20" t="inlineStr">
         <is>
-          <t>Lyft, Inc.</t>
+          <t>Sunrun Inc.</t>
         </is>
       </c>
       <c r="D13" s="21" t="n">
-        <v>6122.4</v>
+        <v>2188.7</v>
       </c>
       <c r="E13" s="32" t="n">
-        <v>16.14</v>
+        <v>9.167999999999999</v>
       </c>
       <c r="F13" s="33" t="n">
-        <v>0.161</v>
+        <v>0.528</v>
       </c>
       <c r="G13" s="33" t="n">
-        <v>0.055</v>
+        <v>0.441</v>
       </c>
       <c r="H13" s="33" t="n">
-        <v>0.4970000000000001</v>
+        <v>0.377</v>
       </c>
       <c r="I13" s="33" t="n">
-        <v>-0.023</v>
+        <v>0.1</v>
       </c>
       <c r="J13" s="33" t="n">
-        <v>0.101</v>
+        <v>0.035</v>
       </c>
       <c r="K13" s="34" t="n">
-        <v>74.2</v>
+        <v>85.09999999999999</v>
       </c>
       <c r="L13" s="34" t="n">
-        <v>77.59999999999999</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="M13" s="35" t="n">
-        <v>69.09999999999999</v>
-      </c>
-      <c r="N13" s="34" t="n">
-        <v>43.7</v>
+        <v>68.90000000000001</v>
+      </c>
+      <c r="N13" s="22" t="n">
+        <v>62.5</v>
       </c>
       <c r="O13" s="37" t="inlineStr">
         <is>
@@ -19066,7 +19066,7 @@
         </is>
       </c>
       <c r="P13" s="44" t="n">
-        <v>12.3</v>
+        <v>3.3</v>
       </c>
       <c r="Q13" s="23" t="inlineStr">
         <is>
@@ -19074,19 +19074,19 @@
         </is>
       </c>
       <c r="R13" s="33" t="n">
-        <v>-0.0756014</v>
+        <v>-0.1011765</v>
       </c>
       <c r="S13" s="33" t="n">
-        <v>0.1512126</v>
+        <v>-0.3188707</v>
       </c>
       <c r="T13" s="33" t="n">
-        <v>0.2181132</v>
+        <v>-0.1915344</v>
       </c>
       <c r="U13" s="33" t="n">
-        <v>-0.1667527</v>
+        <v>-0.5017391</v>
       </c>
       <c r="V13" s="33" t="n">
-        <v>-0.08865050000000001</v>
+        <v>-0.458156</v>
       </c>
     </row>
     <row r="14" ht="16" customHeight="1">
@@ -19095,54 +19095,54 @@
       </c>
       <c r="B14" s="25" t="inlineStr">
         <is>
-          <t>KN</t>
+          <t>ITRI</t>
         </is>
       </c>
       <c r="C14" s="26" t="inlineStr">
         <is>
-          <t>Knowles Corporation</t>
+          <t>Itron, Inc.</t>
         </is>
       </c>
       <c r="D14" s="27" t="n">
-        <v>3043.2</v>
+        <v>4193.1</v>
       </c>
       <c r="E14" s="39" t="n">
-        <v>35.75</v>
+        <v>96.06999999999999</v>
       </c>
       <c r="F14" s="40" t="n">
-        <v>0.143</v>
+        <v>-0.07200000000000001</v>
       </c>
       <c r="G14" s="40" t="n">
-        <v>0.064</v>
+        <v>-0.068</v>
       </c>
       <c r="H14" s="40" t="n">
-        <v>0.424</v>
+        <v>0.41</v>
       </c>
       <c r="I14" s="40" t="n">
-        <v>-0.05599999999999999</v>
+        <v>-0.023</v>
       </c>
       <c r="J14" s="40" t="n">
-        <v>0.018</v>
+        <v>0.017</v>
       </c>
       <c r="K14" s="41" t="n">
-        <v>61.2</v>
+        <v>62.5</v>
       </c>
       <c r="L14" s="41" t="n">
-        <v>70.2</v>
+        <v>73.7</v>
       </c>
       <c r="M14" s="42" t="n">
         <v>68.2</v>
       </c>
       <c r="N14" s="22" t="n">
-        <v>67</v>
+        <v>51.5</v>
       </c>
       <c r="O14" s="43" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="P14" s="38" t="n">
-        <v>43.4</v>
+      <c r="P14" s="44" t="n">
+        <v>19.3</v>
       </c>
       <c r="Q14" s="23" t="inlineStr">
         <is>
@@ -19150,19 +19150,19 @@
         </is>
       </c>
       <c r="R14" s="40" t="n">
-        <v>-0.0852098</v>
+        <v>-0.0740241</v>
       </c>
       <c r="S14" s="40" t="n">
-        <v>-0.0646259</v>
+        <v>0.1744499</v>
       </c>
       <c r="T14" s="40" t="n">
-        <v>0.4397906</v>
+        <v>0.0528219</v>
       </c>
       <c r="U14" s="40" t="n">
-        <v>0.6682220999999999</v>
+        <v>0.0345682</v>
       </c>
       <c r="V14" s="40" t="n">
-        <v>0.6705607</v>
+        <v>-0.2002165</v>
       </c>
     </row>
     <row r="17" ht="22" customHeight="1">
@@ -19316,45 +19316,45 @@
     <row r="23" ht="16" customHeight="1">
       <c r="A23" s="19" t="inlineStr">
         <is>
-          <t>BRC</t>
+          <t>MRCY</t>
         </is>
       </c>
       <c r="B23" s="34" t="n">
-        <v>20</v>
+        <v>12.2</v>
       </c>
       <c r="C23" s="34" t="n">
-        <v>100</v>
+        <v>68.2</v>
       </c>
       <c r="D23" s="34" t="n">
         <v>100</v>
       </c>
       <c r="E23" s="34" t="n">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="F23" s="34" t="n">
-        <v>35.8</v>
+        <v>40.5</v>
       </c>
     </row>
     <row r="24" ht="16" customHeight="1">
       <c r="A24" s="25" t="inlineStr">
         <is>
-          <t>MRCY</t>
+          <t>BRC</t>
         </is>
       </c>
       <c r="B24" s="41" t="n">
-        <v>12.2</v>
+        <v>20</v>
       </c>
       <c r="C24" s="41" t="n">
-        <v>68.2</v>
+        <v>100</v>
       </c>
       <c r="D24" s="41" t="n">
         <v>100</v>
       </c>
       <c r="E24" s="41" t="n">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="F24" s="41" t="n">
-        <v>40.5</v>
+        <v>35.8</v>
       </c>
     </row>
     <row r="25" ht="16" customHeight="1">
@@ -19382,55 +19382,55 @@
     <row r="26" ht="16" customHeight="1">
       <c r="A26" s="25" t="inlineStr">
         <is>
-          <t>RUN</t>
+          <t>LYFT</t>
         </is>
       </c>
       <c r="B26" s="41" t="n">
+        <v>32.2</v>
+      </c>
+      <c r="C26" s="41" t="n">
         <v>100</v>
       </c>
-      <c r="C26" s="41" t="n">
-        <v>94.3</v>
-      </c>
       <c r="D26" s="41" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="E26" s="41" t="n">
-        <v>35</v>
+        <v>100</v>
       </c>
       <c r="F26" s="41" t="n">
-        <v>100</v>
+        <v>63.7</v>
       </c>
     </row>
     <row r="27" ht="16" customHeight="1">
       <c r="A27" s="19" t="inlineStr">
         <is>
-          <t>LYFT</t>
+          <t>RUN</t>
         </is>
       </c>
       <c r="B27" s="34" t="n">
-        <v>32.2</v>
+        <v>100</v>
       </c>
       <c r="C27" s="34" t="n">
+        <v>94.3</v>
+      </c>
+      <c r="D27" s="34" t="n">
+        <v>80</v>
+      </c>
+      <c r="E27" s="34" t="n">
+        <v>35</v>
+      </c>
+      <c r="F27" s="34" t="n">
         <v>100</v>
-      </c>
-      <c r="D27" s="34" t="n">
-        <v>100</v>
-      </c>
-      <c r="E27" s="34" t="n">
-        <v>100</v>
-      </c>
-      <c r="F27" s="34" t="n">
-        <v>63.7</v>
       </c>
     </row>
     <row r="28" ht="16" customHeight="1">
       <c r="A28" s="25" t="inlineStr">
         <is>
-          <t>KN</t>
+          <t>ITRI</t>
         </is>
       </c>
       <c r="B28" s="41" t="n">
-        <v>28.6</v>
+        <v>0</v>
       </c>
       <c r="C28" s="41" t="n">
         <v>100</v>
@@ -19439,10 +19439,10 @@
         <v>100</v>
       </c>
       <c r="E28" s="41" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F28" s="41" t="n">
-        <v>66</v>
+        <v>33</v>
       </c>
     </row>
     <row r="60">
@@ -19534,33 +19534,33 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>BRC</t>
+          <t>MRCY</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>52.9</v>
+        <v>27.3</v>
       </c>
       <c r="C65" t="n">
-        <v>10</v>
+        <v>6.1</v>
       </c>
       <c r="D65" t="n">
-        <v>4139.7</v>
+        <v>5093.4</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>MRCY</t>
+          <t>BRC</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>27.3</v>
+        <v>52.9</v>
       </c>
       <c r="C66" t="n">
-        <v>6.1</v>
+        <v>10</v>
       </c>
       <c r="D66" t="n">
-        <v>5093.4</v>
+        <v>4139.7</v>
       </c>
     </row>
     <row r="67">
@@ -19582,49 +19582,49 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>RUN</t>
+          <t>LYFT</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>37.7</v>
+        <v>49.7</v>
       </c>
       <c r="C68" t="n">
-        <v>52.8</v>
+        <v>16.1</v>
       </c>
       <c r="D68" t="n">
-        <v>2188.7</v>
+        <v>6122.4</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>LYFT</t>
+          <t>RUN</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>49.7</v>
+        <v>37.7</v>
       </c>
       <c r="C69" t="n">
-        <v>16.1</v>
+        <v>52.8</v>
       </c>
       <c r="D69" t="n">
-        <v>6122.4</v>
+        <v>2188.7</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>KN</t>
+          <t>ITRI</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>42.4</v>
+        <v>41</v>
       </c>
       <c r="C70" t="n">
-        <v>14.3</v>
+        <v>-7.2</v>
       </c>
       <c r="D70" t="n">
-        <v>3043.2</v>
+        <v>4193.1</v>
       </c>
     </row>
   </sheetData>
@@ -20445,12 +20445,12 @@
     <row r="14" ht="60" customHeight="1">
       <c r="A14" s="25" t="inlineStr">
         <is>
-          <t>QUIK</t>
+          <t>KVHI</t>
         </is>
       </c>
       <c r="B14" s="26" t="inlineStr">
         <is>
-          <t>QuickLogic Corporation</t>
+          <t>KVH Industries, Inc.</t>
         </is>
       </c>
       <c r="C14" s="26" t="inlineStr">
@@ -20458,9 +20458,9 @@
           <t>Technology</t>
         </is>
       </c>
-      <c r="D14" s="47" t="inlineStr">
-        <is>
-          <t>Semiconductors</t>
+      <c r="D14" s="51" t="inlineStr">
+        <is>
+          <t>Communication Equipment</t>
         </is>
       </c>
       <c r="E14" s="49" t="inlineStr">
@@ -20470,7 +20470,7 @@
       </c>
       <c r="F14" s="50" t="inlineStr">
         <is>
-          <t>QuickLogic Corporation operates as a fabless semiconductor company. The company offers embedded FPGA intellectual property, low power, multicore semiconductor system-on-chips, discrete FPGAs, and AI software; and end-to-end artificial intelligence/machine learning solution with accurate sensor algorithms using AI technology. It also provides various products, such as software tools, and eFPGA IP enables the practical and efficient field programmability for aerospace and defense, consumer/industrial IoT, and consumer electronics markets. In addition, the company engages in the eFPGA IP Licensing business and associated professional services, consisting of development and integration of eFPGA technology into custom semiconductor solutions. Further, the company offers silicon products, such as EOS, QuickAI, ArcticLink III, PolarPro 3, PolarPro II, PolarPro, and Eclipse II products; Software as a Service (SaaS) subscriptions; and PASIC 3 and QuickRAM, as well as programming hardware and de</t>
+          <t>KVH Industries, Inc., together with its subsidiaries, designs, develops, manufactures, and markets mobile connectivity and managed services for the marine and land mobile markets. The company offers Internet and VoIP airtime services; AgilePlans, a connectivity as a Service solution; CommBox, a data management software for maritime communications; CommBox Edge, an advanced maritime network optimization and management solution; KVH Link, a crew wellbeing content subscription service; KVH ONE, a global hybrid communication network supporting Internet, VoIP, content delivery, and other; and KVH OneCare, a services and support for TracNet and TracPhone systems. It also provides MOVIElink, a movie distribution solution; MUSIClink, a music and karaoke delivery solution; NEWSlink, a maritime news delivery solution; OpenNet, a KVH VSAT data delivering service for non-KVH Ku-band VSAT terminals; TracNet, an integrated hybrid two-way communication terminal with VSAT, 5G/LTE, and shore-based Wi-F</t>
         </is>
       </c>
     </row>
@@ -20573,12 +20573,12 @@
     <row r="18" ht="60" customHeight="1">
       <c r="A18" s="25" t="inlineStr">
         <is>
-          <t>LXFR</t>
+          <t>EVLV</t>
         </is>
       </c>
       <c r="B18" s="26" t="inlineStr">
         <is>
-          <t>Luxfer Holdings PLC</t>
+          <t>Evolv Technologies Holdings, Inc.</t>
         </is>
       </c>
       <c r="C18" s="26" t="inlineStr">
@@ -20588,7 +20588,7 @@
       </c>
       <c r="D18" s="26" t="inlineStr">
         <is>
-          <t>Industrial - Machinery</t>
+          <t>Security &amp; Protection Services</t>
         </is>
       </c>
       <c r="E18" s="49" t="inlineStr">
@@ -20598,29 +20598,29 @@
       </c>
       <c r="F18" s="50" t="inlineStr">
         <is>
-          <t>Luxfer Holdings PLC is a company that develops, produces, and distributes advanced materials, specialized components, and high-pressure gas containment solutions. These offerings cater to critical sectors such as defense and emergency services, healthcare, transportation, and a wide array of general industrial applications. The company's operations are divided into two primary divisions: Elektron and Gas Cylinders. The Elektron segment focuses on crafting specialty materials from magnesium and zirconium. This includes providing magnesium alloys for various industrial applications, magnesium powders utilized in products like countermeasure flares and self-heating food packages, and photoengraving plates for graphic arts. Furthermore, it supplies zirconium-based materials and oxides, which are crucial for catalysts, advanced ceramic production, fiber-optic fuel cells, and other high-performance items. The Gas Cylinders segment specializes in manufacturing and marketing robust pressurized</t>
+          <t>Evolv Technologies Holdings, Inc. develops, manufactures, markets, and sells security screening products and specific services in the United States and internationally. It offers Evolv Express, that is designed to detect firearms, improvised explosive devices, and large tactical knives in unstructured people flows; Evolv eXpedite, an autonomous AI-based weapon detection system for bags being brought to venues by visitors in high clutter environments; and Evolv Insights Analytics Application which provides self-serve access, insights regarding visitor flow and arrival curves, location specific performance, system detection performance and alarm statistics, and comparisons across multiple business dimensions. The company serves various industries comprising education, healthcare, professional sports, notable performing arts and entertainment venues, major tourist destinations and cultural attractions, government and corporate offices, hospitality facilities, distribution facilities, larg</t>
         </is>
       </c>
     </row>
     <row r="19" ht="60" customHeight="1">
       <c r="A19" s="19" t="inlineStr">
         <is>
-          <t>CLFD</t>
+          <t>GHM</t>
         </is>
       </c>
       <c r="B19" s="20" t="inlineStr">
         <is>
-          <t>Clearfield, Inc.</t>
+          <t>Graham Corporation</t>
         </is>
       </c>
       <c r="C19" s="20" t="inlineStr">
         <is>
-          <t>Technology</t>
-        </is>
-      </c>
-      <c r="D19" s="51" t="inlineStr">
-        <is>
-          <t>Communication Equipment</t>
+          <t>Industrials</t>
+        </is>
+      </c>
+      <c r="D19" s="20" t="inlineStr">
+        <is>
+          <t>Industrial - Machinery</t>
         </is>
       </c>
       <c r="E19" s="48" t="inlineStr">
@@ -20630,29 +20630,29 @@
       </c>
       <c r="F19" s="46" t="inlineStr">
         <is>
-          <t>Clearfield, Inc. specializes in the development, manufacturing, and global distribution of both standard and customized passive fiber optic connectivity solutions. These products cater to a diverse clientele, including entities engaged in fiber-to-the-premises (FTTP) deployments, enterprise networks, and original equipment manufacturers (OEMs) across the United States and internationally. The company's extensive product portfolio encompasses several key lines: FieldSmart: A range of physical infrastructure components such as panels, cabinets, and wall boxes, specifically designed for housing and protecting fiber optic connections. WaveSmart: Optical components critical for managing light signals, enabling functions like coupling, splitting, termination, multiplexing, demultiplexing, and attenuation when integrated into their fiber management systems. Solutions for outdoor network installations, including outdoor and fiber active cabinet products. StreetSmart: Various fiber management p</t>
+          <t>Graham Corporation, founded in 1936 and based in Batavia, New York, is an engineering and manufacturing company that, along with its subsidiaries, specializes in creating advanced fluid, power, heat transfer, and vacuum equipment. This specialized machinery serves a broad spectrum of critical industries, including chemical and petrochemical processing, defense, aerospace, petroleum refining, cryogenic applications, and energy. The company's diverse product range includes: Power Generation Solutions: Such as ejectors and surface condensers for power plants, as well as turbines, generators, compressors, and pumps. Defense and Space Technologies: Providing torpedo ejection and power systems that integrate turbines, alternators, regulators, pumps, and blowers; also supplying rocket propulsion systems like turbopumps and fuel pumps. Thermal Management and Life Support Systems: Offering pumps, blowers, and electronics for thermal control, cooling systems featuring pumps, compressors, fans, a</t>
         </is>
       </c>
     </row>
     <row r="20" ht="60" customHeight="1">
       <c r="A20" s="25" t="inlineStr">
         <is>
-          <t>ARRY</t>
+          <t>ADTN</t>
         </is>
       </c>
       <c r="B20" s="26" t="inlineStr">
         <is>
-          <t>Array Technologies, Inc.</t>
+          <t>ADTRAN Holdings Inc.</t>
         </is>
       </c>
       <c r="C20" s="26" t="inlineStr">
         <is>
-          <t>Energy</t>
-        </is>
-      </c>
-      <c r="D20" s="53" t="inlineStr">
-        <is>
-          <t>Solar</t>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="D20" s="51" t="inlineStr">
+        <is>
+          <t>Communication Equipment</t>
         </is>
       </c>
       <c r="E20" s="49" t="inlineStr">
@@ -20662,29 +20662,29 @@
       </c>
       <c r="F20" s="50" t="inlineStr">
         <is>
-          <t>Array Technologies, Inc. (ARRY) develops, manufactures, and provides solar tracking solutions and complementary products for customers both within the United States and internationally. A key offering is the DuraTrack HZ v3, a system designed for single-axis solar panel tracking. Additionally, the company offers SmarTrack, an intelligent software powered by machine learning that continuously determines the optimal alignment for solar arrays in real time to maximize energy output. This enterprise was established in 1989 and its corporate headquarters are situated in Albuquerque, New Mexico.</t>
+          <t>ADTRAN Holdings, Inc. develops and provides network access solutions. It is a global provider of open, disaggregated networking and communications equipment that enable voice, data, video and internet communications across any network infrastructure. It operates through the Network Solutions and Services and Support segments. The Network Solutions segment offers hardware and software products. The Service and Support segment manages a comprehensive portfolio of network design, implementation, maintenance and cloud-hosted services supporting its subscriber, access and aggregation, and optical networking solutions. The company was founded in 1985 and is headquartered in Huntsville, AL.</t>
         </is>
       </c>
     </row>
     <row r="21" ht="60" customHeight="1">
       <c r="A21" s="19" t="inlineStr">
         <is>
-          <t>EVLV</t>
+          <t>ARLO</t>
         </is>
       </c>
       <c r="B21" s="20" t="inlineStr">
         <is>
-          <t>Evolv Technologies Holdings, Inc.</t>
+          <t>Arlo Technologies, Inc.</t>
         </is>
       </c>
       <c r="C21" s="20" t="inlineStr">
         <is>
-          <t>Industrials</t>
-        </is>
-      </c>
-      <c r="D21" s="20" t="inlineStr">
-        <is>
-          <t>Security &amp; Protection Services</t>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="D21" s="51" t="inlineStr">
+        <is>
+          <t>Communication Equipment</t>
         </is>
       </c>
       <c r="E21" s="48" t="inlineStr">
@@ -20694,19 +20694,19 @@
       </c>
       <c r="F21" s="46" t="inlineStr">
         <is>
-          <t>Evolv Technologies Holdings, Inc. develops, manufactures, markets, and sells security screening products and specific services in the United States and internationally. It offers Evolv Express, that is designed to detect firearms, improvised explosive devices, and large tactical knives in unstructured people flows; Evolv eXpedite, an autonomous AI-based weapon detection system for bags being brought to venues by visitors in high clutter environments; and Evolv Insights Analytics Application which provides self-serve access, insights regarding visitor flow and arrival curves, location specific performance, system detection performance and alarm statistics, and comparisons across multiple business dimensions. The company serves various industries comprising education, healthcare, professional sports, notable performing arts and entertainment venues, major tourist destinations and cultural attractions, government and corporate offices, hospitality facilities, distribution facilities, larg</t>
+          <t>Arlo Technologies, Inc. delivers a comprehensive, cloud-centric smart security ecosystem across the Americas, Europe, the Middle East, Africa, and Asia Pacific regions. This system seamlessly integrates an intelligent cloud backbone and a user-friendly mobile application with a diverse array of smart, internet-connected hardware. Its product portfolio encompasses a wide selection of security cameras, such as the Arlo Essential Indoor camera, the versatile Arlo Go 2 (supporting both LTE and Wi-Fi), and the mobile, wire-free Arlo Go LTE camera. For indoor monitoring, they offer the wired Arlo Q and Q Plus models. Specialized devices include the Arlo Baby monitor, equipped with air quality and temperature sensors, motion and audio detection, and superior night vision capabilities. The Arlo Chime, designed to complement the Arlo Video Doorbell, provides customizable ringtones and siren functionality. Arlo's advanced camera range features models like the Arlo Ultra and Ultra 2 (with integra</t>
         </is>
       </c>
     </row>
     <row r="22" ht="60" customHeight="1">
       <c r="A22" s="25" t="inlineStr">
         <is>
-          <t>GHM</t>
+          <t>TRC</t>
         </is>
       </c>
       <c r="B22" s="26" t="inlineStr">
         <is>
-          <t>Graham Corporation</t>
+          <t>Tejon Ranch Co.</t>
         </is>
       </c>
       <c r="C22" s="26" t="inlineStr">
@@ -20716,7 +20716,7 @@
       </c>
       <c r="D22" s="26" t="inlineStr">
         <is>
-          <t>Industrial - Machinery</t>
+          <t>Conglomerates</t>
         </is>
       </c>
       <c r="E22" s="49" t="inlineStr">
@@ -20726,19 +20726,19 @@
       </c>
       <c r="F22" s="50" t="inlineStr">
         <is>
-          <t>Graham Corporation, founded in 1936 and based in Batavia, New York, is an engineering and manufacturing company that, along with its subsidiaries, specializes in creating advanced fluid, power, heat transfer, and vacuum equipment. This specialized machinery serves a broad spectrum of critical industries, including chemical and petrochemical processing, defense, aerospace, petroleum refining, cryogenic applications, and energy. The company's diverse product range includes: Power Generation Solutions: Such as ejectors and surface condensers for power plants, as well as turbines, generators, compressors, and pumps. Defense and Space Technologies: Providing torpedo ejection and power systems that integrate turbines, alternators, regulators, pumps, and blowers; also supplying rocket propulsion systems like turbopumps and fuel pumps. Thermal Management and Life Support Systems: Offering pumps, blowers, and electronics for thermal control, cooling systems featuring pumps, compressors, fans, a</t>
+          <t>Tejon Ranch Co., through its various subsidiaries, operates as a multifaceted enterprise primarily focused on real estate development and agricultural operations. Its business is structured across five distinct divisions: Commercial/Industrial Real Estate Development, Resort/Residential Real Estate Development, Mineral Resources, Farming, and Ranch Operations. The Commercial/Industrial Real Estate Development division handles the entire process from land planning and obtaining permits to constructing vital infrastructure and developing properties for lease or sale, which includes creating ready-to-occupy buildings or selling plots to other developers. Additionally, it manages communication leases and landscaping services. This segment generates revenue by leasing land to various commercial tenants, such as two auto service stations with convenience stores, thirteen fast-food establishments, a motel, an antique shop, and a post office. It also provides sites for microwave repeaters, rad</t>
         </is>
       </c>
     </row>
     <row r="23" ht="60" customHeight="1">
       <c r="A23" s="19" t="inlineStr">
         <is>
-          <t>NNDM</t>
+          <t>INOD</t>
         </is>
       </c>
       <c r="B23" s="20" t="inlineStr">
         <is>
-          <t>Nano Dimension Ltd.</t>
+          <t>Innodata Inc.</t>
         </is>
       </c>
       <c r="C23" s="20" t="inlineStr">
@@ -20748,7 +20748,7 @@
       </c>
       <c r="D23" s="20" t="inlineStr">
         <is>
-          <t>Computer Hardware</t>
+          <t>Information Technology Services</t>
         </is>
       </c>
       <c r="E23" s="48" t="inlineStr">
@@ -20758,29 +20758,29 @@
       </c>
       <c r="F23" s="46" t="inlineStr">
         <is>
-          <t>Nano Dimension Ltd., an Israeli enterprise operating globally through its subsidiaries, focuses on delivering additive electronics solutions. The cornerstone of its offerings is the DragonFly IV system, an advanced platform engineered to address the manufacturing requirements of high-performance electronic devices across numerous sectors. This innovative system functions by precisely laying down specialized conductive and dielectric materials, and it possesses the capability to embed components such as capacitors, antennas, coils, transformers, and electromechanical parts directly. Beyond its primary system, Nano Dimension also supplies nanotechnology-derived conductive and dielectric inks, alongside the FLIGHT software platform, which empowers users with the 3D design of intricate electrical and mechanical functionalities. The company's diverse clientele includes organizations involved in creating products with electronic components, spanning critical industries like defense, automoti</t>
+          <t>Innodata Inc. is a global enterprise specializing in data engineering, with operations spanning the United States, the United Kingdom, the Netherlands, Canada, and other international locations. The firm conducts its business across three distinct divisions: Digital Data Solutions (DDS), Synodex, and Agility. Its Digital Data Solutions (DDS) division furnishes clients with AI-powered software platforms and outsourced services. These offerings cater to businesses needing data for the instruction of artificial intelligence (AI) and machine learning (ML) algorithms. DDS also delivers AI-driven digital transformation strategies, assisting organizations in leveraging AI/ML to extract critical insights from textual information. Furthermore, DDS provides a comprehensive suite of data engineering support functions, encompassing activities such as data annotation, transformation, curation, hygiene, consolidation, compliance, and master data management. The Synodex segment supplies an industry-s</t>
         </is>
       </c>
     </row>
     <row r="24" ht="60" customHeight="1">
       <c r="A24" s="25" t="inlineStr">
         <is>
-          <t>ADTN</t>
+          <t>CDRE</t>
         </is>
       </c>
       <c r="B24" s="26" t="inlineStr">
         <is>
-          <t>ADTRAN Holdings Inc.</t>
+          <t>Cadre Holdings, Inc.</t>
         </is>
       </c>
       <c r="C24" s="26" t="inlineStr">
         <is>
-          <t>Technology</t>
-        </is>
-      </c>
-      <c r="D24" s="51" t="inlineStr">
-        <is>
-          <t>Communication Equipment</t>
+          <t>Industrials</t>
+        </is>
+      </c>
+      <c r="D24" s="52" t="inlineStr">
+        <is>
+          <t>Aerospace &amp; Defense</t>
         </is>
       </c>
       <c r="E24" s="49" t="inlineStr">
@@ -20790,7 +20790,7 @@
       </c>
       <c r="F24" s="50" t="inlineStr">
         <is>
-          <t>ADTRAN Holdings, Inc. develops and provides network access solutions. It is a global provider of open, disaggregated networking and communications equipment that enable voice, data, video and internet communications across any network infrastructure. It operates through the Network Solutions and Services and Support segments. The Network Solutions segment offers hardware and software products. The Service and Support segment manages a comprehensive portfolio of network design, implementation, maintenance and cloud-hosted services supporting its subscriber, access and aggregation, and optical networking solutions. The company was founded in 1985 and is headquartered in Huntsville, AL.</t>
+          <t xml:space="preserve">Cadre Holdings, Inc. specializes in manufacturing and distributing vital safety and survival gear designed to protect individuals in perilous or life-threatening environments, both within the United States and globally. The company operates through two distinct divisions: its proprietary Products segment and a Distribution arm. Under its well-known Safariland and Protech Tactical brands, Cadre produces a wide array of body armor, encompassing discreet concealable vests, correctional facility-specific protection, and tactical models. Their extensive product line also features survival suits, remotely operated vehicles (ROVs), specialized tools, blast detection sensors, various ancillary items, vehicle blast attenuation seating for explosive ordnance disposal technicians, and full bomb suits. Furthermore, they supply essential duty equipment, such as belts and accessories, alongside other protective and law enforcement essentials, including communications systems, forensic investigation </t>
         </is>
       </c>
     </row>
@@ -20925,12 +20925,12 @@
     <row r="29" ht="60" customHeight="1">
       <c r="A29" s="19" t="inlineStr">
         <is>
-          <t>BRC</t>
+          <t>MRCY</t>
         </is>
       </c>
       <c r="B29" s="20" t="inlineStr">
         <is>
-          <t>Brady Corporation</t>
+          <t>Mercury Systems, Inc.</t>
         </is>
       </c>
       <c r="C29" s="20" t="inlineStr">
@@ -20938,9 +20938,9 @@
           <t>Industrials</t>
         </is>
       </c>
-      <c r="D29" s="20" t="inlineStr">
-        <is>
-          <t>Security &amp; Protection Services</t>
+      <c r="D29" s="52" t="inlineStr">
+        <is>
+          <t>Aerospace &amp; Defense</t>
         </is>
       </c>
       <c r="E29" s="48" t="inlineStr">
@@ -20950,19 +20950,19 @@
       </c>
       <c r="F29" s="46" t="inlineStr">
         <is>
-          <t>Brady Corporation, established in 1914 and based in Milwaukee, Wisconsin, operates as a global supplier of specialized identification and workplace safety products. The company’s core focus is on delivering solutions that facilitate the identification and protection of facilities, goods, and individuals across numerous industries worldwide. Its Identification Solutions (IDS) division provides a wide range of products for safeguarding and marking premises, including safety signs, floor-marking tapes, pipe markers, advanced labeling systems, spill control items, and lockout/tagout devices. For product management, IDS offers crucial materials, printing technologies, and RFID/barcode scanners used for initial product identification, brand integrity, tracking items through production, and final product labeling. Wire identification needs are met with handheld printers, wire markers, sleeves, and tags. Human identification offerings include name tags, badges, lanyards, rigid card printing sy</t>
+          <t>Mercury Systems, Inc. is a technology firm dedicated to the creation and delivery of a wide range of advanced components, modules, and integrated subsystems, primarily catering to the aerospace and defense industries. The company's operations span globally, with a presence in the United States, Europe, and the Asia Pacific regions. Its sophisticated solutions are vital to approximately 300 programs, supporting 25 defense contractors and numerous commercial aviation customers. The company's extensive product line includes intricate components such as power amplifiers, limiters, switches, oscillators, filters, equalizers, digital and analog converters, various chips, monolithic microwave integrated circuits (MMICs), and advanced memory and storage devices. Furthermore, it offers sophisticated modules and sub-assemblies, including embedded processing boards, switched fabric boards, digital receiver boards, multi-chip modules, integrated radio frequency (RF) and microwave multi-function as</t>
         </is>
       </c>
     </row>
     <row r="30" ht="60" customHeight="1">
       <c r="A30" s="25" t="inlineStr">
         <is>
-          <t>MRCY</t>
+          <t>BRC</t>
         </is>
       </c>
       <c r="B30" s="26" t="inlineStr">
         <is>
-          <t>Mercury Systems, Inc.</t>
+          <t>Brady Corporation</t>
         </is>
       </c>
       <c r="C30" s="26" t="inlineStr">
@@ -20970,9 +20970,9 @@
           <t>Industrials</t>
         </is>
       </c>
-      <c r="D30" s="52" t="inlineStr">
-        <is>
-          <t>Aerospace &amp; Defense</t>
+      <c r="D30" s="26" t="inlineStr">
+        <is>
+          <t>Security &amp; Protection Services</t>
         </is>
       </c>
       <c r="E30" s="49" t="inlineStr">
@@ -20982,7 +20982,7 @@
       </c>
       <c r="F30" s="50" t="inlineStr">
         <is>
-          <t>Mercury Systems, Inc. is a technology firm dedicated to the creation and delivery of a wide range of advanced components, modules, and integrated subsystems, primarily catering to the aerospace and defense industries. The company's operations span globally, with a presence in the United States, Europe, and the Asia Pacific regions. Its sophisticated solutions are vital to approximately 300 programs, supporting 25 defense contractors and numerous commercial aviation customers. The company's extensive product line includes intricate components such as power amplifiers, limiters, switches, oscillators, filters, equalizers, digital and analog converters, various chips, monolithic microwave integrated circuits (MMICs), and advanced memory and storage devices. Furthermore, it offers sophisticated modules and sub-assemblies, including embedded processing boards, switched fabric boards, digital receiver boards, multi-chip modules, integrated radio frequency (RF) and microwave multi-function as</t>
+          <t>Brady Corporation, established in 1914 and based in Milwaukee, Wisconsin, operates as a global supplier of specialized identification and workplace safety products. The company’s core focus is on delivering solutions that facilitate the identification and protection of facilities, goods, and individuals across numerous industries worldwide. Its Identification Solutions (IDS) division provides a wide range of products for safeguarding and marking premises, including safety signs, floor-marking tapes, pipe markers, advanced labeling systems, spill control items, and lockout/tagout devices. For product management, IDS offers crucial materials, printing technologies, and RFID/barcode scanners used for initial product identification, brand integrity, tracking items through production, and final product labeling. Wire identification needs are met with handheld printers, wire markers, sleeves, and tags. Human identification offerings include name tags, badges, lanyards, rigid card printing sy</t>
         </is>
       </c>
     </row>
@@ -21021,22 +21021,22 @@
     <row r="32" ht="60" customHeight="1">
       <c r="A32" s="25" t="inlineStr">
         <is>
-          <t>RUN</t>
+          <t>LYFT</t>
         </is>
       </c>
       <c r="B32" s="26" t="inlineStr">
         <is>
-          <t>Sunrun Inc.</t>
+          <t>Lyft, Inc.</t>
         </is>
       </c>
       <c r="C32" s="26" t="inlineStr">
         <is>
-          <t>Energy</t>
-        </is>
-      </c>
-      <c r="D32" s="53" t="inlineStr">
-        <is>
-          <t>Solar</t>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="D32" s="26" t="inlineStr">
+        <is>
+          <t>Software - Application</t>
         </is>
       </c>
       <c r="E32" s="49" t="inlineStr">
@@ -21046,29 +21046,29 @@
       </c>
       <c r="F32" s="50" t="inlineStr">
         <is>
-          <t>Sunrun Inc. is a company operating in the United States that specializes in providing comprehensive residential solar energy solutions. Their services encompass the entire lifecycle of a solar system, from initial design and development through installation, sales, ongoing ownership, and maintenance. In addition to complete solar energy systems, Sunrun also offers individual components like solar panels and racking equipment. They further enhance their offerings by integrating battery storage capabilities with their solar installations. Residential homeowners are the primary clientele for Sunrun. The company utilizes a direct-to-consumer sales approach, employing a broad spectrum of marketing and sales channels, including online platforms, retail partnerships, mass and digital media advertising, door-to-door canvassing, field marketing, and referral programs. Sunrun Inc. was founded in 2007 and is headquartered in San Francisco, California.</t>
+          <t>Lyft, Inc. facilitates a comprehensive, on-demand transportation platform spanning the United States and Canada. Its core mission involves offering users personalized and immediate access to diverse mobility solutions through its multimodal network. Among its primary services is the Ridesharing Marketplace, which seamlessly connects drivers with passengers. For drivers, the company provides Express Drive, a flexible program for vehicle rentals. Consumers can also utilize Lyft Rentals for longer-distance travel needs. Furthermore, in numerous urban centers, Lyft operates a fleet of shared bikes and scooters, ideal for shorter journeys. The Lyft app enhances its utility by incorporating public transit data, thereby expanding the array of available transport options for users. Beyond these offerings, the company also provides access to autonomous vehicles, specialized enterprise transportation solutions (including concierge services for organizations), and subscription benefits through it</t>
         </is>
       </c>
     </row>
     <row r="33" ht="60" customHeight="1">
       <c r="A33" s="19" t="inlineStr">
         <is>
-          <t>LYFT</t>
+          <t>RUN</t>
         </is>
       </c>
       <c r="B33" s="20" t="inlineStr">
         <is>
-          <t>Lyft, Inc.</t>
+          <t>Sunrun Inc.</t>
         </is>
       </c>
       <c r="C33" s="20" t="inlineStr">
         <is>
-          <t>Technology</t>
-        </is>
-      </c>
-      <c r="D33" s="20" t="inlineStr">
-        <is>
-          <t>Software - Application</t>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="D33" s="53" t="inlineStr">
+        <is>
+          <t>Solar</t>
         </is>
       </c>
       <c r="E33" s="48" t="inlineStr">
@@ -21078,19 +21078,19 @@
       </c>
       <c r="F33" s="46" t="inlineStr">
         <is>
-          <t>Lyft, Inc. facilitates a comprehensive, on-demand transportation platform spanning the United States and Canada. Its core mission involves offering users personalized and immediate access to diverse mobility solutions through its multimodal network. Among its primary services is the Ridesharing Marketplace, which seamlessly connects drivers with passengers. For drivers, the company provides Express Drive, a flexible program for vehicle rentals. Consumers can also utilize Lyft Rentals for longer-distance travel needs. Furthermore, in numerous urban centers, Lyft operates a fleet of shared bikes and scooters, ideal for shorter journeys. The Lyft app enhances its utility by incorporating public transit data, thereby expanding the array of available transport options for users. Beyond these offerings, the company also provides access to autonomous vehicles, specialized enterprise transportation solutions (including concierge services for organizations), and subscription benefits through it</t>
+          <t>Sunrun Inc. is a company operating in the United States that specializes in providing comprehensive residential solar energy solutions. Their services encompass the entire lifecycle of a solar system, from initial design and development through installation, sales, ongoing ownership, and maintenance. In addition to complete solar energy systems, Sunrun also offers individual components like solar panels and racking equipment. They further enhance their offerings by integrating battery storage capabilities with their solar installations. Residential homeowners are the primary clientele for Sunrun. The company utilizes a direct-to-consumer sales approach, employing a broad spectrum of marketing and sales channels, including online platforms, retail partnerships, mass and digital media advertising, door-to-door canvassing, field marketing, and referral programs. Sunrun Inc. was founded in 2007 and is headquartered in San Francisco, California.</t>
         </is>
       </c>
     </row>
     <row r="34" ht="60" customHeight="1">
       <c r="A34" s="25" t="inlineStr">
         <is>
-          <t>KN</t>
+          <t>ITRI</t>
         </is>
       </c>
       <c r="B34" s="26" t="inlineStr">
         <is>
-          <t>Knowles Corporation</t>
+          <t>Itron, Inc.</t>
         </is>
       </c>
       <c r="C34" s="26" t="inlineStr">
@@ -21110,7 +21110,7 @@
       </c>
       <c r="F34" s="50" t="inlineStr">
         <is>
-          <t xml:space="preserve">Knowles Corporation is a leading provider of specialized electronic components, offering an array of micro-acoustic microphones, sophisticated balanced armature speakers, comprehensive audio solutions, high-performance capacitors, and advanced radio frequency products. These precision technologies serve diverse industries, including consumer electronics, medical technology (medtech), defense, electric vehicles, industrial applications, and communications. The company operates through two distinct segments. Its Audio segment is dedicated to engineering and manufacturing innovative audio components, such as microphones, balanced armature speakers, and audio processors. These are integral to applications across mobile devices, hearing health solutions, True Wireless Stereo (TWS) products, the Internet of Things (IoT), and computing platforms. Concurrently, the Precision Devices (PD) segment focuses on the development and delivery of high-specification capacitor products and RF solutions. </t>
+          <t>Itron, Inc., a technology, solutions, and service company, provides end-to-end solutions that help manage energy, water, and smart city operations worldwide. It operates in four segments: Device Solutions, Networked Solutions, Outcomes, and Resiliency Solution. The Device Solutions segment offers hardware products that are used for measurement, control, or sensing, such as standard gas, electricity, water, and communicating meters, as well as heat and allocation products. The Networked Solutions segment provides communicating devices, such as smart meters, modules, endpoints, and sensors; network infrastructure; network design services; and associated heat-end management and application software for acquiring and transporting application-specific data. This segment also products and software for the implementation, installation, and management of communicating devices and data networks; offers industrial internet of things solutions, including automated meter reading; advanced metering</t>
         </is>
       </c>
     </row>
@@ -21544,17 +21544,17 @@
     <row r="14" ht="80" customHeight="1">
       <c r="A14" s="25" t="inlineStr">
         <is>
-          <t>QUIK</t>
+          <t>KVHI</t>
         </is>
       </c>
       <c r="B14" s="26" t="inlineStr">
         <is>
-          <t>QuickLogic Corporation</t>
+          <t>KVH Industries, Inc.</t>
         </is>
       </c>
       <c r="C14" s="26" t="inlineStr">
         <is>
-          <t>Semiconductors</t>
+          <t>Communication Equipment</t>
         </is>
       </c>
       <c r="D14" s="49" t="inlineStr">
@@ -21564,7 +21564,7 @@
       </c>
       <c r="E14" s="49" t="inlineStr">
         <is>
-          <t>44%</t>
+          <t>30%</t>
         </is>
       </c>
       <c r="F14" s="49" t="inlineStr">
@@ -21574,7 +21574,7 @@
       </c>
       <c r="G14" s="50" t="inlineStr">
         <is>
-          <t>Healthy margins (GM 44%) indicate differentiated products with some pricing power above commodity levels. Solid revenue growth (49% YoY) suggests growing demand and competitive positioning in target markets. Revenue acceleration (59% QoQ) — growth is compounding, indicating an inflection point or expanding customer adoption. Dilution risk (28% 3yr share growth) — heavy equity issuance may erode per-share value over time. Semiconductor design/fab expertise represents years of R&amp;D investment — a significant moat against new entrants.</t>
+          <t>Moderate margins (GM 30%) — competitive market, but cost structure supports reinvestment. Solid revenue growth (27% YoY) suggests growing demand and competitive positioning in target markets. Revenue acceleration (34% QoQ) — growth is compounding, indicating an inflection point or expanding customer adoption. Exceptional capital discipline (1% share growth over 3yr) — management avoids dilution, signaling confidence in organic cash generation. High insider ownership (35%) — founder/management skin in the game strongly aligns incentives with shareholders. Networking/communications infrastructure — installed base and switching costs create customer lock-in.</t>
         </is>
       </c>
     </row>
@@ -21692,17 +21692,17 @@
     <row r="18" ht="80" customHeight="1">
       <c r="A18" s="25" t="inlineStr">
         <is>
-          <t>LXFR</t>
+          <t>EVLV</t>
         </is>
       </c>
       <c r="B18" s="26" t="inlineStr">
         <is>
-          <t>Luxfer Holdings PLC</t>
+          <t>Evolv Technologies Holdings, Inc.</t>
         </is>
       </c>
       <c r="C18" s="26" t="inlineStr">
         <is>
-          <t>Industrial - Machinery</t>
+          <t>Security &amp; Protection Services</t>
         </is>
       </c>
       <c r="D18" s="49" t="inlineStr">
@@ -21712,34 +21712,34 @@
       </c>
       <c r="E18" s="49" t="inlineStr">
         <is>
-          <t>26%</t>
+          <t>50%</t>
         </is>
       </c>
       <c r="F18" s="49" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>74</t>
         </is>
       </c>
       <c r="G18" s="50" t="inlineStr">
         <is>
-          <t>Moderate margins (GM 26%) — competitive market, but cost structure supports reinvestment. Exceptional capital discipline (-0% share growth over 3yr) — management avoids dilution, signaling confidence in organic cash generation. Fingerprint score of 79 — structural profile closely matches historical multi-bagger winners at their inflection points.</t>
+          <t>Healthy margins (GM 50%) indicate differentiated products with some pricing power above commodity levels. Solid revenue growth (34% YoY) suggests growing demand and competitive positioning in target markets. Revenue acceleration (7% QoQ) — growth is compounding, indicating an inflection point or expanding customer adoption. Fingerprint score of 74 — structural profile closely matches historical multi-bagger winners at their inflection points.</t>
         </is>
       </c>
     </row>
     <row r="19" ht="80" customHeight="1">
       <c r="A19" s="19" t="inlineStr">
         <is>
-          <t>CLFD</t>
+          <t>GHM</t>
         </is>
       </c>
       <c r="B19" s="20" t="inlineStr">
         <is>
-          <t>Clearfield, Inc.</t>
+          <t>Graham Corporation</t>
         </is>
       </c>
       <c r="C19" s="20" t="inlineStr">
         <is>
-          <t>Communication Equipment</t>
+          <t>Industrial - Machinery</t>
         </is>
       </c>
       <c r="D19" s="48" t="inlineStr">
@@ -21749,34 +21749,34 @@
       </c>
       <c r="E19" s="48" t="inlineStr">
         <is>
-          <t>32%</t>
+          <t>25%</t>
         </is>
       </c>
       <c r="F19" s="48" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>88</t>
         </is>
       </c>
       <c r="G19" s="46" t="inlineStr">
         <is>
-          <t>Moderate margins (GM 32%) — competitive market, but cost structure supports reinvestment. Exceptional capital discipline (-11% share growth over 3yr) — management avoids dilution, signaling confidence in organic cash generation. Meaningful insider ownership (18%) — management has material personal stake in company performance. Networking/communications infrastructure — installed base and switching costs create customer lock-in. Fingerprint score of 69 — structural profile closely matches historical multi-bagger winners at their inflection points.</t>
+          <t>Moderate margins (GM 25%) — competitive market, but cost structure supports reinvestment. Solid revenue growth (29% YoY) suggests growing demand and competitive positioning in target markets. Revenue acceleration (18% QoQ) — growth is compounding, indicating an inflection point or expanding customer adoption. Reasonable capital discipline (8% 3yr dilution) — moderate equity issuance suggests funded growth without excessive shareholder dilution. Fingerprint score of 88 — structural profile closely matches historical multi-bagger winners at their inflection points.</t>
         </is>
       </c>
     </row>
     <row r="20" ht="80" customHeight="1">
       <c r="A20" s="25" t="inlineStr">
         <is>
-          <t>ARRY</t>
+          <t>ADTN</t>
         </is>
       </c>
       <c r="B20" s="26" t="inlineStr">
         <is>
-          <t>Array Technologies, Inc.</t>
+          <t>ADTRAN Holdings Inc.</t>
         </is>
       </c>
       <c r="C20" s="26" t="inlineStr">
         <is>
-          <t>Solar</t>
+          <t>Communication Equipment</t>
         </is>
       </c>
       <c r="D20" s="49" t="inlineStr">
@@ -21786,34 +21786,34 @@
       </c>
       <c r="E20" s="49" t="inlineStr">
         <is>
-          <t>29%</t>
+          <t>37%</t>
         </is>
       </c>
       <c r="F20" s="49" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>77</t>
         </is>
       </c>
       <c r="G20" s="50" t="inlineStr">
         <is>
-          <t>Moderate margins (GM 29%) — competitive market, but cost structure supports reinvestment. Exceptional capital discipline (2% share growth over 3yr) — management avoids dilution, signaling confidence in organic cash generation. Fingerprint score of 78 — structural profile closely matches historical multi-bagger winners at their inflection points.</t>
+          <t>Moderate margins (GM 37%) — competitive market, but cost structure supports reinvestment. Exceptional capital discipline (3% share growth over 3yr) — management avoids dilution, signaling confidence in organic cash generation. Networking/communications infrastructure — installed base and switching costs create customer lock-in. Fingerprint score of 77 — structural profile closely matches historical multi-bagger winners at their inflection points.</t>
         </is>
       </c>
     </row>
     <row r="21" ht="80" customHeight="1">
       <c r="A21" s="19" t="inlineStr">
         <is>
-          <t>EVLV</t>
+          <t>ARLO</t>
         </is>
       </c>
       <c r="B21" s="20" t="inlineStr">
         <is>
-          <t>Evolv Technologies Holdings, Inc.</t>
+          <t>Arlo Technologies, Inc.</t>
         </is>
       </c>
       <c r="C21" s="20" t="inlineStr">
         <is>
-          <t>Security &amp; Protection Services</t>
+          <t>Communication Equipment</t>
         </is>
       </c>
       <c r="D21" s="48" t="inlineStr">
@@ -21823,34 +21823,34 @@
       </c>
       <c r="E21" s="48" t="inlineStr">
         <is>
-          <t>50%</t>
+          <t>48%</t>
         </is>
       </c>
       <c r="F21" s="48" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>73</t>
         </is>
       </c>
       <c r="G21" s="46" t="inlineStr">
         <is>
-          <t>Healthy margins (GM 50%) indicate differentiated products with some pricing power above commodity levels. Solid revenue growth (34% YoY) suggests growing demand and competitive positioning in target markets. Revenue acceleration (7% QoQ) — growth is compounding, indicating an inflection point or expanding customer adoption. Fingerprint score of 74 — structural profile closely matches historical multi-bagger winners at their inflection points.</t>
+          <t>Healthy margins (GM 48%) indicate differentiated products with some pricing power above commodity levels. Revenue acceleration (19% QoQ) — growth is compounding, indicating an inflection point or expanding customer adoption. Networking/communications infrastructure — installed base and switching costs create customer lock-in. Fingerprint score of 73 — structural profile closely matches historical multi-bagger winners at their inflection points.</t>
         </is>
       </c>
     </row>
     <row r="22" ht="80" customHeight="1">
       <c r="A22" s="25" t="inlineStr">
         <is>
-          <t>GHM</t>
+          <t>TRC</t>
         </is>
       </c>
       <c r="B22" s="26" t="inlineStr">
         <is>
-          <t>Graham Corporation</t>
+          <t>Tejon Ranch Co.</t>
         </is>
       </c>
       <c r="C22" s="26" t="inlineStr">
         <is>
-          <t>Industrial - Machinery</t>
+          <t>Conglomerates</t>
         </is>
       </c>
       <c r="D22" s="49" t="inlineStr">
@@ -21860,34 +21860,34 @@
       </c>
       <c r="E22" s="49" t="inlineStr">
         <is>
-          <t>25%</t>
+          <t>22%</t>
         </is>
       </c>
       <c r="F22" s="49" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>69</t>
         </is>
       </c>
       <c r="G22" s="50" t="inlineStr">
         <is>
-          <t>Moderate margins (GM 25%) — competitive market, but cost structure supports reinvestment. Solid revenue growth (29% YoY) suggests growing demand and competitive positioning in target markets. Revenue acceleration (18% QoQ) — growth is compounding, indicating an inflection point or expanding customer adoption. Reasonable capital discipline (8% 3yr dilution) — moderate equity issuance suggests funded growth without excessive shareholder dilution. Fingerprint score of 88 — structural profile closely matches historical multi-bagger winners at their inflection points.</t>
+          <t>Rapid revenue growth (72% YoY) signals strong product-market fit and expanding TAM capture. Revenue acceleration (26% QoQ) — growth is compounding, indicating an inflection point or expanding customer adoption. Exceptional capital discipline (-1% share growth over 3yr) — management avoids dilution, signaling confidence in organic cash generation. Fingerprint score of 69 — structural profile closely matches historical multi-bagger winners at their inflection points.</t>
         </is>
       </c>
     </row>
     <row r="23" ht="80" customHeight="1">
       <c r="A23" s="19" t="inlineStr">
         <is>
-          <t>NNDM</t>
+          <t>INOD</t>
         </is>
       </c>
       <c r="B23" s="20" t="inlineStr">
         <is>
-          <t>Nano Dimension Ltd.</t>
+          <t>Innodata Inc.</t>
         </is>
       </c>
       <c r="C23" s="20" t="inlineStr">
         <is>
-          <t>Computer Hardware</t>
+          <t>Information Technology Services</t>
         </is>
       </c>
       <c r="D23" s="48" t="inlineStr">
@@ -21902,29 +21902,29 @@
       </c>
       <c r="F23" s="48" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>70</t>
         </is>
       </c>
       <c r="G23" s="46" t="inlineStr">
         <is>
-          <t>Healthy margins (GM 46%) indicate differentiated products with some pricing power above commodity levels. Exceptional capital discipline (-18% share growth over 3yr) — management avoids dilution, signaling confidence in organic cash generation. Fingerprint score of 71 — structural profile closely matches historical multi-bagger winners at their inflection points.</t>
+          <t>Healthy margins (GM 46%) indicate differentiated products with some pricing power above commodity levels. Rapid revenue growth (58% YoY) signals strong product-market fit and expanding TAM capture. Fingerprint score of 70 — structural profile closely matches historical multi-bagger winners at their inflection points.</t>
         </is>
       </c>
     </row>
     <row r="24" ht="80" customHeight="1">
       <c r="A24" s="25" t="inlineStr">
         <is>
-          <t>ADTN</t>
+          <t>CDRE</t>
         </is>
       </c>
       <c r="B24" s="26" t="inlineStr">
         <is>
-          <t>ADTRAN Holdings Inc.</t>
+          <t>Cadre Holdings, Inc.</t>
         </is>
       </c>
       <c r="C24" s="26" t="inlineStr">
         <is>
-          <t>Communication Equipment</t>
+          <t>Aerospace &amp; Defense</t>
         </is>
       </c>
       <c r="D24" s="49" t="inlineStr">
@@ -21934,17 +21934,17 @@
       </c>
       <c r="E24" s="49" t="inlineStr">
         <is>
-          <t>37%</t>
+          <t>42%</t>
         </is>
       </c>
       <c r="F24" s="49" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>67</t>
         </is>
       </c>
       <c r="G24" s="50" t="inlineStr">
         <is>
-          <t>Moderate margins (GM 37%) — competitive market, but cost structure supports reinvestment. Exceptional capital discipline (3% share growth over 3yr) — management avoids dilution, signaling confidence in organic cash generation. Networking/communications infrastructure — installed base and switching costs create customer lock-in. Fingerprint score of 77 — structural profile closely matches historical multi-bagger winners at their inflection points.</t>
+          <t>Healthy margins (GM 42%) indicate differentiated products with some pricing power above commodity levels. Solid revenue growth (32% YoY) suggests growing demand and competitive positioning in target markets. Revenue acceleration (23% QoQ) — growth is compounding, indicating an inflection point or expanding customer adoption. High insider ownership (34%) — founder/management skin in the game strongly aligns incentives with shareholders. Defense/aerospace positioning creates high barriers to entry via security clearances, government contracts, and long procurement cycles. Fingerprint score of 67 — structural profile closely matches historical multi-bagger winners at their inflection points.</t>
         </is>
       </c>
     </row>
@@ -22099,17 +22099,17 @@
     <row r="29" ht="80" customHeight="1">
       <c r="A29" s="19" t="inlineStr">
         <is>
-          <t>BRC</t>
+          <t>MRCY</t>
         </is>
       </c>
       <c r="B29" s="20" t="inlineStr">
         <is>
-          <t>Brady Corporation</t>
+          <t>Mercury Systems, Inc.</t>
         </is>
       </c>
       <c r="C29" s="20" t="inlineStr">
         <is>
-          <t>Security &amp; Protection Services</t>
+          <t>Aerospace &amp; Defense</t>
         </is>
       </c>
       <c r="D29" s="48" t="inlineStr">
@@ -22119,34 +22119,34 @@
       </c>
       <c r="E29" s="48" t="inlineStr">
         <is>
-          <t>53%</t>
+          <t>27%</t>
         </is>
       </c>
       <c r="F29" s="48" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>71</t>
         </is>
       </c>
       <c r="G29" s="46" t="inlineStr">
         <is>
-          <t>Healthy margins (GM 53%) indicate differentiated products with some pricing power above commodity levels. Exceptional capital discipline (-2% share growth over 3yr) — management avoids dilution, signaling confidence in organic cash generation. Meaningful insider ownership (10%) — management has material personal stake in company performance. Fingerprint score of 75 — structural profile closely matches historical multi-bagger winners at their inflection points.</t>
+          <t>Moderate margins (GM 27%) — competitive market, but cost structure supports reinvestment. Reasonable capital discipline (4% 3yr dilution) — moderate equity issuance suggests funded growth without excessive shareholder dilution. Defense/aerospace positioning creates high barriers to entry via security clearances, government contracts, and long procurement cycles. Fingerprint score of 71 — structural profile closely matches historical multi-bagger winners at their inflection points.</t>
         </is>
       </c>
     </row>
     <row r="30" ht="80" customHeight="1">
       <c r="A30" s="25" t="inlineStr">
         <is>
-          <t>MRCY</t>
+          <t>BRC</t>
         </is>
       </c>
       <c r="B30" s="26" t="inlineStr">
         <is>
-          <t>Mercury Systems, Inc.</t>
+          <t>Brady Corporation</t>
         </is>
       </c>
       <c r="C30" s="26" t="inlineStr">
         <is>
-          <t>Aerospace &amp; Defense</t>
+          <t>Security &amp; Protection Services</t>
         </is>
       </c>
       <c r="D30" s="49" t="inlineStr">
@@ -22156,17 +22156,17 @@
       </c>
       <c r="E30" s="49" t="inlineStr">
         <is>
-          <t>27%</t>
+          <t>53%</t>
         </is>
       </c>
       <c r="F30" s="49" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>75</t>
         </is>
       </c>
       <c r="G30" s="50" t="inlineStr">
         <is>
-          <t>Moderate margins (GM 27%) — competitive market, but cost structure supports reinvestment. Reasonable capital discipline (4% 3yr dilution) — moderate equity issuance suggests funded growth without excessive shareholder dilution. Defense/aerospace positioning creates high barriers to entry via security clearances, government contracts, and long procurement cycles. Fingerprint score of 71 — structural profile closely matches historical multi-bagger winners at their inflection points.</t>
+          <t>Healthy margins (GM 53%) indicate differentiated products with some pricing power above commodity levels. Exceptional capital discipline (-2% share growth over 3yr) — management avoids dilution, signaling confidence in organic cash generation. Meaningful insider ownership (10%) — management has material personal stake in company performance. Fingerprint score of 75 — structural profile closely matches historical multi-bagger winners at their inflection points.</t>
         </is>
       </c>
     </row>
@@ -22210,17 +22210,17 @@
     <row r="32" ht="80" customHeight="1">
       <c r="A32" s="25" t="inlineStr">
         <is>
-          <t>RUN</t>
+          <t>LYFT</t>
         </is>
       </c>
       <c r="B32" s="26" t="inlineStr">
         <is>
-          <t>Sunrun Inc.</t>
+          <t>Lyft, Inc.</t>
         </is>
       </c>
       <c r="C32" s="26" t="inlineStr">
         <is>
-          <t>Solar</t>
+          <t>Software - Application</t>
         </is>
       </c>
       <c r="D32" s="49" t="inlineStr">
@@ -22230,34 +22230,34 @@
       </c>
       <c r="E32" s="49" t="inlineStr">
         <is>
-          <t>38%</t>
+          <t>50%</t>
         </is>
       </c>
       <c r="F32" s="49" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>78</t>
         </is>
       </c>
       <c r="G32" s="50" t="inlineStr">
         <is>
-          <t>Moderate margins (GM 38%) — competitive market, but cost structure supports reinvestment. Rapid revenue growth (53% YoY) signals strong product-market fit and expanding TAM capture. Revenue acceleration (44% QoQ) — growth is compounding, indicating an inflection point or expanding customer adoption. Reasonable capital discipline (10% 3yr dilution) — moderate equity issuance suggests funded growth without excessive shareholder dilution. Fingerprint score of 71 — structural profile closely matches historical multi-bagger winners at their inflection points.</t>
+          <t>Healthy margins (GM 50%) indicate differentiated products with some pricing power above commodity levels. Revenue acceleration (6% QoQ) — growth is compounding, indicating an inflection point or expanding customer adoption. Exceptional capital discipline (-2% share growth over 3yr) — management avoids dilution, signaling confidence in organic cash generation. Meaningful insider ownership (10%) — management has material personal stake in company performance. Fingerprint score of 78 — structural profile closely matches historical multi-bagger winners at their inflection points.</t>
         </is>
       </c>
     </row>
     <row r="33" ht="80" customHeight="1">
       <c r="A33" s="19" t="inlineStr">
         <is>
-          <t>LYFT</t>
+          <t>RUN</t>
         </is>
       </c>
       <c r="B33" s="20" t="inlineStr">
         <is>
-          <t>Lyft, Inc.</t>
+          <t>Sunrun Inc.</t>
         </is>
       </c>
       <c r="C33" s="20" t="inlineStr">
         <is>
-          <t>Software - Application</t>
+          <t>Solar</t>
         </is>
       </c>
       <c r="D33" s="48" t="inlineStr">
@@ -22267,29 +22267,29 @@
       </c>
       <c r="E33" s="48" t="inlineStr">
         <is>
-          <t>50%</t>
+          <t>38%</t>
         </is>
       </c>
       <c r="F33" s="48" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>71</t>
         </is>
       </c>
       <c r="G33" s="46" t="inlineStr">
         <is>
-          <t>Healthy margins (GM 50%) indicate differentiated products with some pricing power above commodity levels. Revenue acceleration (6% QoQ) — growth is compounding, indicating an inflection point or expanding customer adoption. Exceptional capital discipline (-2% share growth over 3yr) — management avoids dilution, signaling confidence in organic cash generation. Meaningful insider ownership (10%) — management has material personal stake in company performance. Fingerprint score of 78 — structural profile closely matches historical multi-bagger winners at their inflection points.</t>
+          <t>Moderate margins (GM 38%) — competitive market, but cost structure supports reinvestment. Rapid revenue growth (53% YoY) signals strong product-market fit and expanding TAM capture. Revenue acceleration (44% QoQ) — growth is compounding, indicating an inflection point or expanding customer adoption. Reasonable capital discipline (10% 3yr dilution) — moderate equity issuance suggests funded growth without excessive shareholder dilution. Fingerprint score of 71 — structural profile closely matches historical multi-bagger winners at their inflection points.</t>
         </is>
       </c>
     </row>
     <row r="34" ht="80" customHeight="1">
       <c r="A34" s="25" t="inlineStr">
         <is>
-          <t>KN</t>
+          <t>ITRI</t>
         </is>
       </c>
       <c r="B34" s="26" t="inlineStr">
         <is>
-          <t>Knowles Corporation</t>
+          <t>Itron, Inc.</t>
         </is>
       </c>
       <c r="C34" s="26" t="inlineStr">
@@ -22304,17 +22304,17 @@
       </c>
       <c r="E34" s="49" t="inlineStr">
         <is>
-          <t>42%</t>
+          <t>41%</t>
         </is>
       </c>
       <c r="F34" s="49" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>74</t>
         </is>
       </c>
       <c r="G34" s="50" t="inlineStr">
         <is>
-          <t>Healthy margins (GM 42%) indicate differentiated products with some pricing power above commodity levels. Revenue acceleration (6% QoQ) — growth is compounding, indicating an inflection point or expanding customer adoption. Exceptional capital discipline (-6% share growth over 3yr) — management avoids dilution, signaling confidence in organic cash generation. Fingerprint score of 70 — structural profile closely matches historical multi-bagger winners at their inflection points.</t>
+          <t>Healthy margins (GM 41%) indicate differentiated products with some pricing power above commodity levels. Exceptional capital discipline (-2% share growth over 3yr) — management avoids dilution, signaling confidence in organic cash generation. Fingerprint score of 74 — structural profile closely matches historical multi-bagger winners at their inflection points.</t>
         </is>
       </c>
     </row>
@@ -22497,7 +22497,7 @@
         </is>
       </c>
       <c r="E6" s="34" t="n">
-        <v>79.2</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="F6" s="48" t="inlineStr">
         <is>
@@ -22505,7 +22505,7 @@
         </is>
       </c>
       <c r="G6" s="59" t="n">
-        <v>79.2</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="I6" s="58" t="inlineStr">
         <is>
@@ -22514,24 +22514,24 @@
       </c>
       <c r="J6" s="19" t="inlineStr">
         <is>
-          <t>NNDM</t>
+          <t>RELL</t>
         </is>
       </c>
       <c r="K6" s="20" t="inlineStr">
         <is>
-          <t>Nano Dimension Ltd.</t>
+          <t>Richardson Electronics, Ltd.</t>
         </is>
       </c>
       <c r="L6" s="34" t="n">
-        <v>-18.3</v>
+        <v>-7.9</v>
       </c>
       <c r="M6" s="48" t="inlineStr">
         <is>
-          <t>Small Cap</t>
+          <t>Nano Cap</t>
         </is>
       </c>
       <c r="N6" s="59" t="n">
-        <v>70.5</v>
+        <v>69.59999999999999</v>
       </c>
     </row>
     <row r="7" ht="16" customHeight="1">
@@ -22551,7 +22551,7 @@
         </is>
       </c>
       <c r="E7" s="41" t="n">
-        <v>78.7</v>
+        <v>78.5</v>
       </c>
       <c r="F7" s="49" t="inlineStr">
         <is>
@@ -22559,7 +22559,7 @@
         </is>
       </c>
       <c r="G7" s="61" t="n">
-        <v>78.7</v>
+        <v>78.5</v>
       </c>
       <c r="I7" s="60" t="inlineStr">
         <is>
@@ -22568,24 +22568,24 @@
       </c>
       <c r="J7" s="25" t="inlineStr">
         <is>
-          <t>CLFD</t>
+          <t>CALX</t>
         </is>
       </c>
       <c r="K7" s="26" t="inlineStr">
         <is>
-          <t>Clearfield, Inc.</t>
+          <t>Calix, Inc.</t>
         </is>
       </c>
       <c r="L7" s="41" t="n">
-        <v>-10.9</v>
+        <v>-4.2</v>
       </c>
       <c r="M7" s="49" t="inlineStr">
         <is>
-          <t>Small Cap</t>
+          <t>Breakout</t>
         </is>
       </c>
       <c r="N7" s="61" t="n">
-        <v>73.90000000000001</v>
+        <v>77.5</v>
       </c>
     </row>
     <row r="8" ht="16" customHeight="1">
@@ -22605,7 +22605,7 @@
         </is>
       </c>
       <c r="E8" s="34" t="n">
-        <v>77.2</v>
+        <v>77.5</v>
       </c>
       <c r="F8" s="48" t="inlineStr">
         <is>
@@ -22613,7 +22613,7 @@
         </is>
       </c>
       <c r="G8" s="59" t="n">
-        <v>77.2</v>
+        <v>77.5</v>
       </c>
       <c r="I8" s="58" t="inlineStr">
         <is>
@@ -22622,24 +22622,24 @@
       </c>
       <c r="J8" s="19" t="inlineStr">
         <is>
-          <t>RELL</t>
+          <t>DCI</t>
         </is>
       </c>
       <c r="K8" s="20" t="inlineStr">
         <is>
-          <t>Richardson Electronics, Ltd.</t>
+          <t>Donaldson Company, Inc.</t>
         </is>
       </c>
       <c r="L8" s="34" t="n">
-        <v>-7.9</v>
+        <v>-4.2</v>
       </c>
       <c r="M8" s="48" t="inlineStr">
         <is>
-          <t>Nano Cap</t>
+          <t>Breakout</t>
         </is>
       </c>
       <c r="N8" s="59" t="n">
-        <v>70</v>
+        <v>73.09999999999999</v>
       </c>
     </row>
     <row r="9" ht="16" customHeight="1">
@@ -22676,24 +22676,24 @@
       </c>
       <c r="J9" s="25" t="inlineStr">
         <is>
-          <t>KN</t>
+          <t>SWBI</t>
         </is>
       </c>
       <c r="K9" s="26" t="inlineStr">
         <is>
-          <t>Knowles Corporation</t>
+          <t>Smith &amp; Wesson Brands, Inc.</t>
         </is>
       </c>
       <c r="L9" s="41" t="n">
-        <v>-5.6</v>
+        <v>-2.6</v>
       </c>
       <c r="M9" s="49" t="inlineStr">
         <is>
-          <t>Breakout</t>
+          <t>Small Cap</t>
         </is>
       </c>
       <c r="N9" s="61" t="n">
-        <v>68.2</v>
+        <v>79.40000000000001</v>
       </c>
     </row>
     <row r="10" ht="16" customHeight="1">
@@ -22704,24 +22704,24 @@
       </c>
       <c r="C10" s="19" t="inlineStr">
         <is>
-          <t>LXFR</t>
+          <t>ADEA</t>
         </is>
       </c>
       <c r="D10" s="20" t="inlineStr">
         <is>
-          <t>Luxfer Holdings PLC</t>
+          <t>Adeia Inc.</t>
         </is>
       </c>
       <c r="E10" s="34" t="n">
-        <v>74</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="F10" s="48" t="inlineStr">
         <is>
-          <t>Small Cap</t>
+          <t>Breakout</t>
         </is>
       </c>
       <c r="G10" s="59" t="n">
-        <v>74</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="I10" s="58" t="inlineStr">
         <is>
@@ -22730,16 +22730,16 @@
       </c>
       <c r="J10" s="19" t="inlineStr">
         <is>
-          <t>CALX</t>
+          <t>BRC</t>
         </is>
       </c>
       <c r="K10" s="20" t="inlineStr">
         <is>
-          <t>Calix, Inc.</t>
+          <t>Brady Corporation</t>
         </is>
       </c>
       <c r="L10" s="34" t="n">
-        <v>-4.2</v>
+        <v>-2.5</v>
       </c>
       <c r="M10" s="48" t="inlineStr">
         <is>
@@ -22747,7 +22747,7 @@
         </is>
       </c>
       <c r="N10" s="59" t="n">
-        <v>77.2</v>
+        <v>69.7</v>
       </c>
     </row>
     <row r="12" ht="22" customHeight="1">
@@ -22859,7 +22859,7 @@
         </is>
       </c>
       <c r="G14" s="59" t="n">
-        <v>70.7</v>
+        <v>70.8</v>
       </c>
       <c r="I14" s="58" t="inlineStr">
         <is>
@@ -22913,7 +22913,7 @@
         </is>
       </c>
       <c r="G15" s="61" t="n">
-        <v>79.2</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="I15" s="60" t="inlineStr">
         <is>
@@ -22922,16 +22922,16 @@
       </c>
       <c r="J15" s="25" t="inlineStr">
         <is>
-          <t>ASYS</t>
+          <t>KVHI</t>
         </is>
       </c>
       <c r="K15" s="26" t="inlineStr">
         <is>
-          <t>Amtech Systems, Inc.</t>
+          <t>KVH Industries, Inc.</t>
         </is>
       </c>
       <c r="L15" s="41" t="n">
-        <v>26.3</v>
+        <v>35</v>
       </c>
       <c r="M15" s="49" t="inlineStr">
         <is>
@@ -22939,7 +22939,7 @@
         </is>
       </c>
       <c r="N15" s="61" t="n">
-        <v>61.6</v>
+        <v>59.4</v>
       </c>
     </row>
     <row r="16" ht="16" customHeight="1">
@@ -22967,7 +22967,7 @@
         </is>
       </c>
       <c r="G16" s="59" t="n">
-        <v>78.7</v>
+        <v>78.5</v>
       </c>
       <c r="I16" s="58" t="inlineStr">
         <is>
@@ -22976,24 +22976,24 @@
       </c>
       <c r="J16" s="19" t="inlineStr">
         <is>
-          <t>BKTI</t>
+          <t>CDRE</t>
         </is>
       </c>
       <c r="K16" s="20" t="inlineStr">
         <is>
-          <t>BK Technologies Corporation</t>
+          <t>Cadre Holdings, Inc.</t>
         </is>
       </c>
       <c r="L16" s="34" t="n">
-        <v>24</v>
+        <v>34.3</v>
       </c>
       <c r="M16" s="48" t="inlineStr">
         <is>
-          <t>Nano Cap</t>
+          <t>Small Cap</t>
         </is>
       </c>
       <c r="N16" s="59" t="n">
-        <v>62.4</v>
+        <v>67</v>
       </c>
     </row>
     <row r="17" ht="16" customHeight="1">
@@ -23021,7 +23021,7 @@
         </is>
       </c>
       <c r="G17" s="61" t="n">
-        <v>77.2</v>
+        <v>77.5</v>
       </c>
       <c r="I17" s="60" t="inlineStr">
         <is>
@@ -23030,16 +23030,16 @@
       </c>
       <c r="J17" s="25" t="inlineStr">
         <is>
-          <t>SODI</t>
+          <t>ASYS</t>
         </is>
       </c>
       <c r="K17" s="26" t="inlineStr">
         <is>
-          <t>Solitron Devices, Inc.</t>
+          <t>Amtech Systems, Inc.</t>
         </is>
       </c>
       <c r="L17" s="41" t="n">
-        <v>23</v>
+        <v>26.3</v>
       </c>
       <c r="M17" s="49" t="inlineStr">
         <is>
@@ -23047,7 +23047,7 @@
         </is>
       </c>
       <c r="N17" s="61" t="n">
-        <v>70.90000000000001</v>
+        <v>61.6</v>
       </c>
     </row>
     <row r="18" ht="16" customHeight="1">
@@ -23084,16 +23084,16 @@
       </c>
       <c r="J18" s="19" t="inlineStr">
         <is>
-          <t>LTRX</t>
+          <t>BKTI</t>
         </is>
       </c>
       <c r="K18" s="20" t="inlineStr">
         <is>
-          <t>Lantronix, Inc.</t>
+          <t>BK Technologies Corporation</t>
         </is>
       </c>
       <c r="L18" s="34" t="n">
-        <v>22.5</v>
+        <v>24</v>
       </c>
       <c r="M18" s="48" t="inlineStr">
         <is>
@@ -23101,7 +23101,7 @@
         </is>
       </c>
       <c r="N18" s="59" t="n">
-        <v>66</v>
+        <v>63.1</v>
       </c>
     </row>
     <row r="20" ht="22" customHeight="1">
@@ -23304,24 +23304,24 @@
       </c>
       <c r="C24" s="19" t="inlineStr">
         <is>
-          <t>RUN</t>
+          <t>TRC</t>
         </is>
       </c>
       <c r="D24" s="20" t="inlineStr">
         <is>
-          <t>Sunrun Inc.</t>
+          <t>Tejon Ranch Co.</t>
         </is>
       </c>
       <c r="E24" s="34" t="n">
-        <v>52.8</v>
+        <v>71.7</v>
       </c>
       <c r="F24" s="48" t="inlineStr">
         <is>
-          <t>Breakout</t>
+          <t>Small Cap</t>
         </is>
       </c>
       <c r="G24" s="59" t="n">
-        <v>69.09999999999999</v>
+        <v>69.3</v>
       </c>
       <c r="I24" s="58" t="inlineStr">
         <is>
@@ -23347,7 +23347,7 @@
         </is>
       </c>
       <c r="N24" s="59" t="n">
-        <v>67.40000000000001</v>
+        <v>67.09999999999999</v>
       </c>
     </row>
     <row r="25" ht="16" customHeight="1">
@@ -23358,50 +23358,50 @@
       </c>
       <c r="C25" s="25" t="inlineStr">
         <is>
-          <t>QUIK</t>
+          <t>INOD</t>
         </is>
       </c>
       <c r="D25" s="26" t="inlineStr">
         <is>
-          <t>QuickLogic Corporation</t>
+          <t>Innodata Inc.</t>
         </is>
       </c>
       <c r="E25" s="41" t="n">
-        <v>48.7</v>
+        <v>57.8</v>
       </c>
       <c r="F25" s="49" t="inlineStr">
         <is>
+          <t>Small Cap</t>
+        </is>
+      </c>
+      <c r="G25" s="61" t="n">
+        <v>68.2</v>
+      </c>
+      <c r="I25" s="60" t="inlineStr">
+        <is>
+          <t>4th</t>
+        </is>
+      </c>
+      <c r="J25" s="25" t="inlineStr">
+        <is>
+          <t>KVHI</t>
+        </is>
+      </c>
+      <c r="K25" s="26" t="inlineStr">
+        <is>
+          <t>KVH Industries, Inc.</t>
+        </is>
+      </c>
+      <c r="L25" s="27" t="n">
+        <v>138.8</v>
+      </c>
+      <c r="M25" s="49" t="inlineStr">
+        <is>
           <t>Nano Cap</t>
         </is>
       </c>
-      <c r="G25" s="61" t="n">
-        <v>61.6</v>
-      </c>
-      <c r="I25" s="60" t="inlineStr">
-        <is>
-          <t>4th</t>
-        </is>
-      </c>
-      <c r="J25" s="25" t="inlineStr">
-        <is>
-          <t>INTT</t>
-        </is>
-      </c>
-      <c r="K25" s="26" t="inlineStr">
-        <is>
-          <t>inTEST Corporation</t>
-        </is>
-      </c>
-      <c r="L25" s="27" t="n">
-        <v>146.3</v>
-      </c>
-      <c r="M25" s="49" t="inlineStr">
-        <is>
-          <t>Nano Cap</t>
-        </is>
-      </c>
       <c r="N25" s="61" t="n">
-        <v>70.2</v>
+        <v>59.4</v>
       </c>
     </row>
     <row r="26" ht="16" customHeight="1">
@@ -23412,24 +23412,24 @@
       </c>
       <c r="C26" s="19" t="inlineStr">
         <is>
-          <t>EVLV</t>
+          <t>RUN</t>
         </is>
       </c>
       <c r="D26" s="20" t="inlineStr">
         <is>
-          <t>Evolv Technologies Holdings, Inc.</t>
+          <t>Sunrun Inc.</t>
         </is>
       </c>
       <c r="E26" s="34" t="n">
-        <v>34.4</v>
+        <v>52.8</v>
       </c>
       <c r="F26" s="48" t="inlineStr">
         <is>
-          <t>Small Cap</t>
+          <t>Breakout</t>
         </is>
       </c>
       <c r="G26" s="59" t="n">
-        <v>72.09999999999999</v>
+        <v>68.90000000000001</v>
       </c>
       <c r="I26" s="58" t="inlineStr">
         <is>
@@ -23438,16 +23438,16 @@
       </c>
       <c r="J26" s="19" t="inlineStr">
         <is>
-          <t>QUIK</t>
+          <t>INTT</t>
         </is>
       </c>
       <c r="K26" s="20" t="inlineStr">
         <is>
-          <t>QuickLogic Corporation</t>
+          <t>inTEST Corporation</t>
         </is>
       </c>
       <c r="L26" s="21" t="n">
-        <v>197.1</v>
+        <v>146.3</v>
       </c>
       <c r="M26" s="48" t="inlineStr">
         <is>
@@ -23455,7 +23455,7 @@
         </is>
       </c>
       <c r="N26" s="59" t="n">
-        <v>61.6</v>
+        <v>70.2</v>
       </c>
     </row>
     <row r="28" ht="22" customHeight="1">
@@ -23555,7 +23555,7 @@
         </is>
       </c>
       <c r="G31" s="61" t="n">
-        <v>71.5</v>
+        <v>71.59999999999999</v>
       </c>
     </row>
     <row r="32" ht="16" customHeight="1">
@@ -23566,16 +23566,16 @@
       </c>
       <c r="C32" s="19" t="inlineStr">
         <is>
-          <t>BRC</t>
+          <t>ITRI</t>
         </is>
       </c>
       <c r="D32" s="20" t="inlineStr">
         <is>
-          <t>Brady Corporation</t>
+          <t>Itron, Inc.</t>
         </is>
       </c>
       <c r="E32" s="34" t="n">
-        <v>16.73751</v>
+        <v>17.44499</v>
       </c>
       <c r="F32" s="48" t="inlineStr">
         <is>
@@ -23583,7 +23583,7 @@
         </is>
       </c>
       <c r="G32" s="59" t="n">
-        <v>69.90000000000001</v>
+        <v>68.2</v>
       </c>
     </row>
     <row r="33" ht="16" customHeight="1">
@@ -23594,16 +23594,16 @@
       </c>
       <c r="C33" s="25" t="inlineStr">
         <is>
-          <t>LYFT</t>
+          <t>BRC</t>
         </is>
       </c>
       <c r="D33" s="26" t="inlineStr">
         <is>
-          <t>Lyft, Inc.</t>
+          <t>Brady Corporation</t>
         </is>
       </c>
       <c r="E33" s="41" t="n">
-        <v>15.12126</v>
+        <v>16.73751</v>
       </c>
       <c r="F33" s="49" t="inlineStr">
         <is>
@@ -23611,7 +23611,7 @@
         </is>
       </c>
       <c r="G33" s="61" t="n">
-        <v>69.09999999999999</v>
+        <v>69.7</v>
       </c>
     </row>
     <row r="34" ht="16" customHeight="1">
@@ -23622,16 +23622,16 @@
       </c>
       <c r="C34" s="19" t="inlineStr">
         <is>
-          <t>DCI</t>
+          <t>LYFT</t>
         </is>
       </c>
       <c r="D34" s="20" t="inlineStr">
         <is>
-          <t>Donaldson Company, Inc.</t>
+          <t>Lyft, Inc.</t>
         </is>
       </c>
       <c r="E34" s="34" t="n">
-        <v>9.0855</v>
+        <v>15.12126</v>
       </c>
       <c r="F34" s="48" t="inlineStr">
         <is>
@@ -23639,7 +23639,7 @@
         </is>
       </c>
       <c r="G34" s="59" t="n">
-        <v>73</v>
+        <v>69</v>
       </c>
     </row>
   </sheetData>
@@ -23807,7 +23807,7 @@
         </is>
       </c>
       <c r="F6" s="34" t="n">
-        <v>79.2</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="G6" s="46" t="inlineStr">
         <is>
@@ -23855,7 +23855,7 @@
         </is>
       </c>
       <c r="F7" s="41" t="n">
-        <v>78.7</v>
+        <v>78.5</v>
       </c>
       <c r="G7" s="50" t="inlineStr">
         <is>
@@ -23901,7 +23901,7 @@
         </is>
       </c>
       <c r="F8" s="34" t="n">
-        <v>77.2</v>
+        <v>77.5</v>
       </c>
       <c r="G8" s="46" t="inlineStr">
         <is>
@@ -23972,17 +23972,17 @@
     <row r="10" ht="40" customHeight="1">
       <c r="A10" s="19" t="inlineStr">
         <is>
-          <t>LXFR</t>
+          <t>ADEA</t>
         </is>
       </c>
       <c r="B10" s="20" t="inlineStr">
         <is>
-          <t>Luxfer Holdings PLC</t>
+          <t>Adeia Inc.</t>
         </is>
       </c>
       <c r="C10" s="48" t="inlineStr">
         <is>
-          <t>Small Cap</t>
+          <t>Breakout</t>
         </is>
       </c>
       <c r="D10" s="23" t="inlineStr">
@@ -23996,7 +23996,7 @@
         </is>
       </c>
       <c r="F10" s="34" t="n">
-        <v>74</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="G10" s="46" t="inlineStr">
         <is>
@@ -24019,17 +24019,17 @@
     <row r="11" ht="40" customHeight="1">
       <c r="A11" s="25" t="inlineStr">
         <is>
-          <t>CLFD</t>
+          <t>DCI</t>
         </is>
       </c>
       <c r="B11" s="26" t="inlineStr">
         <is>
-          <t>Clearfield, Inc.</t>
+          <t>Donaldson Company, Inc.</t>
         </is>
       </c>
       <c r="C11" s="49" t="inlineStr">
         <is>
-          <t>Small Cap</t>
+          <t>Breakout</t>
         </is>
       </c>
       <c r="D11" s="23" t="inlineStr">
@@ -24043,39 +24043,40 @@
         </is>
       </c>
       <c r="F11" s="41" t="n">
-        <v>73.90000000000001</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="G11" s="50" t="inlineStr">
         <is>
-          <t>Strengths: high insider alignment, minimal dilution. Risks: modest growth.</t>
+          <t>Strengths: healthy margins, minimal dilution. Risks: low insider ownership, modest growth.</t>
         </is>
       </c>
       <c r="H11" s="64" t="inlineStr">
         <is>
-          <t>✓ high insider alignment
+          <t>✓ healthy margins
 ✓ minimal dilution</t>
         </is>
       </c>
       <c r="I11" s="65" t="inlineStr">
         <is>
-          <t>⚠ modest growth</t>
+          <t>⚠ low insider ownership
+⚠ modest growth</t>
         </is>
       </c>
     </row>
     <row r="12" ht="40" customHeight="1">
       <c r="A12" s="19" t="inlineStr">
         <is>
-          <t>ADEA</t>
+          <t>EVLV</t>
         </is>
       </c>
       <c r="B12" s="20" t="inlineStr">
         <is>
-          <t>Adeia Inc.</t>
+          <t>Evolv Technologies Holdings, Inc.</t>
         </is>
       </c>
       <c r="C12" s="48" t="inlineStr">
         <is>
-          <t>Breakout</t>
+          <t>Small Cap</t>
         </is>
       </c>
       <c r="D12" s="23" t="inlineStr">
@@ -24085,39 +24086,38 @@
       </c>
       <c r="E12" s="20" t="inlineStr">
         <is>
-          <t>Emerging Watch</t>
+          <t>Growth Inflection</t>
         </is>
       </c>
       <c r="F12" s="34" t="n">
-        <v>73.40000000000001</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="G12" s="46" t="inlineStr">
         <is>
-          <t>Strengths: minimal dilution. Risks: thin margins, low insider ownership, modest growth.</t>
+          <t>Strengths: solid revenue growth, high-margin business. Risks: significant dilution.</t>
         </is>
       </c>
       <c r="H12" s="64" t="inlineStr">
         <is>
-          <t>✓ minimal dilution</t>
+          <t>✓ solid revenue growth
+✓ high-margin business</t>
         </is>
       </c>
       <c r="I12" s="65" t="inlineStr">
         <is>
-          <t>⚠ thin margins
-⚠ low insider ownership
-⚠ modest growth</t>
+          <t>⚠ significant dilution</t>
         </is>
       </c>
     </row>
     <row r="13" ht="40" customHeight="1">
       <c r="A13" s="25" t="inlineStr">
         <is>
-          <t>DCI</t>
+          <t>CACI</t>
         </is>
       </c>
       <c r="B13" s="26" t="inlineStr">
         <is>
-          <t>Donaldson Company, Inc.</t>
+          <t>CACI International Inc</t>
         </is>
       </c>
       <c r="C13" s="49" t="inlineStr">
@@ -24136,40 +24136,38 @@
         </is>
       </c>
       <c r="F13" s="41" t="n">
-        <v>73</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="G13" s="50" t="inlineStr">
         <is>
-          <t>Strengths: healthy margins, minimal dilution. Risks: low insider ownership, modest growth.</t>
+          <t>Strengths: minimal dilution. Risks: low insider ownership.</t>
         </is>
       </c>
       <c r="H13" s="64" t="inlineStr">
         <is>
-          <t>✓ healthy margins
-✓ minimal dilution</t>
+          <t>✓ minimal dilution</t>
         </is>
       </c>
       <c r="I13" s="65" t="inlineStr">
         <is>
-          <t>⚠ low insider ownership
-⚠ modest growth</t>
+          <t>⚠ low insider ownership</t>
         </is>
       </c>
     </row>
     <row r="14" ht="40" customHeight="1">
       <c r="A14" s="19" t="inlineStr">
         <is>
-          <t>ARRY</t>
+          <t>SODI</t>
         </is>
       </c>
       <c r="B14" s="20" t="inlineStr">
         <is>
-          <t>Array Technologies, Inc.</t>
+          <t>Solitron Devices, Inc.</t>
         </is>
       </c>
       <c r="C14" s="48" t="inlineStr">
         <is>
-          <t>Small Cap</t>
+          <t>Nano Cap</t>
         </is>
       </c>
       <c r="D14" s="23" t="inlineStr">
@@ -24179,156 +24177,18 @@
       </c>
       <c r="E14" s="20" t="inlineStr">
         <is>
-          <t>Emerging Watch</t>
+          <t>High-Growth Quality</t>
         </is>
       </c>
       <c r="F14" s="34" t="n">
-        <v>72.59999999999999</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="G14" s="46" t="inlineStr">
         <is>
-          <t>Strengths: minimal dilution. Risks: thin margins, negative momentum, modest growth.</t>
+          <t>Strengths: strong revenue growth, healthy margins, high insider alignment, minimal dilution, positive momentum. Risks: none significant.</t>
         </is>
       </c>
       <c r="H14" s="64" t="inlineStr">
-        <is>
-          <t>✓ minimal dilution</t>
-        </is>
-      </c>
-      <c r="I14" s="65" t="inlineStr">
-        <is>
-          <t>⚠ thin margins
-⚠ negative momentum
-⚠ modest growth</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="40" customHeight="1">
-      <c r="A15" s="25" t="inlineStr">
-        <is>
-          <t>EVLV</t>
-        </is>
-      </c>
-      <c r="B15" s="26" t="inlineStr">
-        <is>
-          <t>Evolv Technologies Holdings, Inc.</t>
-        </is>
-      </c>
-      <c r="C15" s="49" t="inlineStr">
-        <is>
-          <t>Small Cap</t>
-        </is>
-      </c>
-      <c r="D15" s="23" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="E15" s="26" t="inlineStr">
-        <is>
-          <t>Growth Inflection</t>
-        </is>
-      </c>
-      <c r="F15" s="41" t="n">
-        <v>72.09999999999999</v>
-      </c>
-      <c r="G15" s="50" t="inlineStr">
-        <is>
-          <t>Strengths: solid revenue growth, high-margin business. Risks: significant dilution.</t>
-        </is>
-      </c>
-      <c r="H15" s="64" t="inlineStr">
-        <is>
-          <t>✓ solid revenue growth
-✓ high-margin business</t>
-        </is>
-      </c>
-      <c r="I15" s="65" t="inlineStr">
-        <is>
-          <t>⚠ significant dilution</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="40" customHeight="1">
-      <c r="A16" s="19" t="inlineStr">
-        <is>
-          <t>CACI</t>
-        </is>
-      </c>
-      <c r="B16" s="20" t="inlineStr">
-        <is>
-          <t>CACI International Inc</t>
-        </is>
-      </c>
-      <c r="C16" s="48" t="inlineStr">
-        <is>
-          <t>Breakout</t>
-        </is>
-      </c>
-      <c r="D16" s="23" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="E16" s="20" t="inlineStr">
-        <is>
-          <t>Emerging Watch</t>
-        </is>
-      </c>
-      <c r="F16" s="34" t="n">
-        <v>71.5</v>
-      </c>
-      <c r="G16" s="46" t="inlineStr">
-        <is>
-          <t>Strengths: minimal dilution. Risks: low insider ownership.</t>
-        </is>
-      </c>
-      <c r="H16" s="64" t="inlineStr">
-        <is>
-          <t>✓ minimal dilution</t>
-        </is>
-      </c>
-      <c r="I16" s="65" t="inlineStr">
-        <is>
-          <t>⚠ low insider ownership</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="40" customHeight="1">
-      <c r="A17" s="25" t="inlineStr">
-        <is>
-          <t>SODI</t>
-        </is>
-      </c>
-      <c r="B17" s="26" t="inlineStr">
-        <is>
-          <t>Solitron Devices, Inc.</t>
-        </is>
-      </c>
-      <c r="C17" s="49" t="inlineStr">
-        <is>
-          <t>Nano Cap</t>
-        </is>
-      </c>
-      <c r="D17" s="23" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="E17" s="26" t="inlineStr">
-        <is>
-          <t>High-Growth Quality</t>
-        </is>
-      </c>
-      <c r="F17" s="41" t="n">
-        <v>70.90000000000001</v>
-      </c>
-      <c r="G17" s="50" t="inlineStr">
-        <is>
-          <t>Strengths: strong revenue growth, healthy margins, high insider alignment, minimal dilution, positive momentum. Risks: none significant.</t>
-        </is>
-      </c>
-      <c r="H17" s="64" t="inlineStr">
         <is>
           <t>✓ strong revenue growth
 ✓ healthy margins
@@ -24337,146 +24197,99 @@
 ✓ positive momentum</t>
         </is>
       </c>
-      <c r="I17" s="65" t="inlineStr">
+      <c r="I14" s="65" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="40" customHeight="1">
-      <c r="A18" s="19" t="inlineStr">
+    <row r="15" ht="40" customHeight="1">
+      <c r="A15" s="25" t="inlineStr">
         <is>
           <t>GHM</t>
         </is>
       </c>
-      <c r="B18" s="20" t="inlineStr">
+      <c r="B15" s="26" t="inlineStr">
         <is>
           <t>Graham Corporation</t>
         </is>
       </c>
-      <c r="C18" s="48" t="inlineStr">
+      <c r="C15" s="49" t="inlineStr">
         <is>
           <t>Small Cap</t>
         </is>
       </c>
-      <c r="D18" s="23" t="inlineStr">
+      <c r="D15" s="23" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E18" s="20" t="inlineStr">
+      <c r="E15" s="26" t="inlineStr">
         <is>
           <t>Fingerprint Match</t>
         </is>
       </c>
-      <c r="F18" s="34" t="n">
-        <v>70.7</v>
-      </c>
-      <c r="G18" s="46" t="inlineStr">
+      <c r="F15" s="41" t="n">
+        <v>70.8</v>
+      </c>
+      <c r="G15" s="50" t="inlineStr">
         <is>
           <t>Strengths: solid revenue growth, strong fingerprint match. Risks: thin margins.</t>
         </is>
       </c>
-      <c r="H18" s="64" t="inlineStr">
+      <c r="H15" s="64" t="inlineStr">
         <is>
           <t>✓ solid revenue growth
 ✓ strong fingerprint match</t>
         </is>
       </c>
-      <c r="I18" s="65" t="inlineStr">
+      <c r="I15" s="65" t="inlineStr">
         <is>
           <t>⚠ thin margins</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="40" customHeight="1">
-      <c r="A19" s="25" t="inlineStr">
-        <is>
-          <t>NNDM</t>
-        </is>
-      </c>
-      <c r="B19" s="26" t="inlineStr">
-        <is>
-          <t>Nano Dimension Ltd.</t>
-        </is>
-      </c>
-      <c r="C19" s="49" t="inlineStr">
+    <row r="16" ht="40" customHeight="1">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
+          <t>ADTN</t>
+        </is>
+      </c>
+      <c r="B16" s="20" t="inlineStr">
+        <is>
+          <t>ADTRAN Holdings Inc.</t>
+        </is>
+      </c>
+      <c r="C16" s="48" t="inlineStr">
         <is>
           <t>Small Cap</t>
         </is>
       </c>
-      <c r="D19" s="23" t="inlineStr">
+      <c r="D16" s="23" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E19" s="26" t="inlineStr">
+      <c r="E16" s="20" t="inlineStr">
         <is>
           <t>Emerging Watch</t>
         </is>
       </c>
-      <c r="F19" s="41" t="n">
+      <c r="F16" s="34" t="n">
         <v>70.5</v>
       </c>
-      <c r="G19" s="50" t="inlineStr">
-        <is>
-          <t>Strengths: healthy margins, minimal dilution. Risks: low insider ownership, modest growth.</t>
-        </is>
-      </c>
-      <c r="H19" s="64" t="inlineStr">
+      <c r="G16" s="46" t="inlineStr">
+        <is>
+          <t>Strengths: healthy margins, minimal dilution. Risks: low insider ownership, negative momentum, modest growth.</t>
+        </is>
+      </c>
+      <c r="H16" s="64" t="inlineStr">
         <is>
           <t>✓ healthy margins
 ✓ minimal dilution</t>
         </is>
       </c>
-      <c r="I19" s="65" t="inlineStr">
-        <is>
-          <t>⚠ low insider ownership
-⚠ modest growth</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="40" customHeight="1">
-      <c r="A20" s="19" t="inlineStr">
-        <is>
-          <t>ADTN</t>
-        </is>
-      </c>
-      <c r="B20" s="20" t="inlineStr">
-        <is>
-          <t>ADTRAN Holdings Inc.</t>
-        </is>
-      </c>
-      <c r="C20" s="48" t="inlineStr">
-        <is>
-          <t>Small Cap</t>
-        </is>
-      </c>
-      <c r="D20" s="23" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="E20" s="20" t="inlineStr">
-        <is>
-          <t>Emerging Watch</t>
-        </is>
-      </c>
-      <c r="F20" s="34" t="n">
-        <v>70.40000000000001</v>
-      </c>
-      <c r="G20" s="46" t="inlineStr">
-        <is>
-          <t>Strengths: healthy margins, minimal dilution. Risks: low insider ownership, negative momentum, modest growth.</t>
-        </is>
-      </c>
-      <c r="H20" s="64" t="inlineStr">
-        <is>
-          <t>✓ healthy margins
-✓ minimal dilution</t>
-        </is>
-      </c>
-      <c r="I20" s="65" t="inlineStr">
+      <c r="I16" s="65" t="inlineStr">
         <is>
           <t>⚠ low insider ownership
 ⚠ negative momentum
@@ -24484,114 +24297,298 @@
         </is>
       </c>
     </row>
-    <row r="21" ht="40" customHeight="1">
-      <c r="A21" s="25" t="inlineStr">
+    <row r="17" ht="40" customHeight="1">
+      <c r="A17" s="25" t="inlineStr">
         <is>
           <t>INTT</t>
         </is>
       </c>
-      <c r="B21" s="26" t="inlineStr">
+      <c r="B17" s="26" t="inlineStr">
         <is>
           <t>inTEST Corporation</t>
         </is>
       </c>
-      <c r="C21" s="49" t="inlineStr">
+      <c r="C17" s="49" t="inlineStr">
         <is>
           <t>Nano Cap</t>
         </is>
       </c>
-      <c r="D21" s="23" t="inlineStr">
+      <c r="D17" s="23" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E21" s="26" t="inlineStr">
+      <c r="E17" s="26" t="inlineStr">
         <is>
           <t>Emerging Watch</t>
         </is>
       </c>
-      <c r="F21" s="41" t="n">
+      <c r="F17" s="41" t="n">
         <v>70.2</v>
       </c>
-      <c r="G21" s="50" t="inlineStr">
+      <c r="G17" s="50" t="inlineStr">
         <is>
           <t>Strengths: solid revenue growth, healthy margins, minimal dilution. Risks: none significant.</t>
         </is>
       </c>
-      <c r="H21" s="64" t="inlineStr">
+      <c r="H17" s="64" t="inlineStr">
         <is>
           <t>✓ solid revenue growth
 ✓ healthy margins
 ✓ minimal dilution</t>
         </is>
       </c>
-      <c r="I21" s="65" t="inlineStr">
+      <c r="I17" s="65" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
-    <row r="22" ht="40" customHeight="1">
-      <c r="A22" s="19" t="inlineStr">
+    <row r="18" ht="40" customHeight="1">
+      <c r="A18" s="19" t="inlineStr">
+        <is>
+          <t>MRCY</t>
+        </is>
+      </c>
+      <c r="B18" s="20" t="inlineStr">
+        <is>
+          <t>Mercury Systems, Inc.</t>
+        </is>
+      </c>
+      <c r="C18" s="48" t="inlineStr">
+        <is>
+          <t>Breakout</t>
+        </is>
+      </c>
+      <c r="D18" s="23" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E18" s="20" t="inlineStr">
+        <is>
+          <t>Emerging Watch</t>
+        </is>
+      </c>
+      <c r="F18" s="34" t="n">
+        <v>69.8</v>
+      </c>
+      <c r="G18" s="46" t="inlineStr">
+        <is>
+          <t>Strengths: minimal dilution. Risks: thin margins, modest growth.</t>
+        </is>
+      </c>
+      <c r="H18" s="64" t="inlineStr">
+        <is>
+          <t>✓ minimal dilution</t>
+        </is>
+      </c>
+      <c r="I18" s="65" t="inlineStr">
+        <is>
+          <t>⚠ thin margins
+⚠ modest growth</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="40" customHeight="1">
+      <c r="A19" s="25" t="inlineStr">
+        <is>
+          <t>BRC</t>
+        </is>
+      </c>
+      <c r="B19" s="26" t="inlineStr">
+        <is>
+          <t>Brady Corporation</t>
+        </is>
+      </c>
+      <c r="C19" s="49" t="inlineStr">
+        <is>
+          <t>Breakout</t>
+        </is>
+      </c>
+      <c r="D19" s="23" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E19" s="26" t="inlineStr">
+        <is>
+          <t>Emerging Watch</t>
+        </is>
+      </c>
+      <c r="F19" s="41" t="n">
+        <v>69.7</v>
+      </c>
+      <c r="G19" s="50" t="inlineStr">
+        <is>
+          <t>Strengths: high-margin business, minimal dilution. Risks: modest growth.</t>
+        </is>
+      </c>
+      <c r="H19" s="64" t="inlineStr">
+        <is>
+          <t>✓ high-margin business
+✓ minimal dilution</t>
+        </is>
+      </c>
+      <c r="I19" s="65" t="inlineStr">
+        <is>
+          <t>⚠ modest growth</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="40" customHeight="1">
+      <c r="A20" s="19" t="inlineStr">
         <is>
           <t>RELL</t>
         </is>
       </c>
-      <c r="B22" s="20" t="inlineStr">
+      <c r="B20" s="20" t="inlineStr">
         <is>
           <t>Richardson Electronics, Ltd.</t>
         </is>
       </c>
-      <c r="C22" s="48" t="inlineStr">
+      <c r="C20" s="48" t="inlineStr">
         <is>
           <t>Nano Cap</t>
         </is>
       </c>
-      <c r="D22" s="23" t="inlineStr">
+      <c r="D20" s="23" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E22" s="20" t="inlineStr">
+      <c r="E20" s="20" t="inlineStr">
         <is>
           <t>Emerging Watch</t>
         </is>
       </c>
-      <c r="F22" s="34" t="n">
-        <v>70</v>
-      </c>
-      <c r="G22" s="46" t="inlineStr">
+      <c r="F20" s="34" t="n">
+        <v>69.59999999999999</v>
+      </c>
+      <c r="G20" s="46" t="inlineStr">
         <is>
           <t>Strengths: solid revenue growth, high insider alignment, minimal dilution. Risks: none significant.</t>
         </is>
       </c>
-      <c r="H22" s="64" t="inlineStr">
+      <c r="H20" s="64" t="inlineStr">
         <is>
           <t>✓ solid revenue growth
 ✓ high insider alignment
 ✓ minimal dilution</t>
         </is>
       </c>
+      <c r="I20" s="65" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="40" customHeight="1">
+      <c r="A21" s="25" t="inlineStr">
+        <is>
+          <t>ARLO</t>
+        </is>
+      </c>
+      <c r="B21" s="26" t="inlineStr">
+        <is>
+          <t>Arlo Technologies, Inc.</t>
+        </is>
+      </c>
+      <c r="C21" s="49" t="inlineStr">
+        <is>
+          <t>Small Cap</t>
+        </is>
+      </c>
+      <c r="D21" s="23" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E21" s="26" t="inlineStr">
+        <is>
+          <t>Emerging Watch</t>
+        </is>
+      </c>
+      <c r="F21" s="41" t="n">
+        <v>69.59999999999999</v>
+      </c>
+      <c r="G21" s="50" t="inlineStr">
+        <is>
+          <t>Strengths: solid revenue growth, healthy margins. Risks: low insider ownership.</t>
+        </is>
+      </c>
+      <c r="H21" s="64" t="inlineStr">
+        <is>
+          <t>✓ solid revenue growth
+✓ healthy margins</t>
+        </is>
+      </c>
+      <c r="I21" s="65" t="inlineStr">
+        <is>
+          <t>⚠ low insider ownership</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="40" customHeight="1">
+      <c r="A22" s="19" t="inlineStr">
+        <is>
+          <t>CE</t>
+        </is>
+      </c>
+      <c r="B22" s="20" t="inlineStr">
+        <is>
+          <t>Celanese Corporation</t>
+        </is>
+      </c>
+      <c r="C22" s="48" t="inlineStr">
+        <is>
+          <t>Breakout</t>
+        </is>
+      </c>
+      <c r="D22" s="23" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E22" s="20" t="inlineStr">
+        <is>
+          <t>Emerging Watch</t>
+        </is>
+      </c>
+      <c r="F22" s="34" t="n">
+        <v>69.5</v>
+      </c>
+      <c r="G22" s="46" t="inlineStr">
+        <is>
+          <t>Strengths: minimal dilution. Risks: thin margins, modest growth.</t>
+        </is>
+      </c>
+      <c r="H22" s="64" t="inlineStr">
+        <is>
+          <t>✓ minimal dilution</t>
+        </is>
+      </c>
       <c r="I22" s="65" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>⚠ thin margins
+⚠ modest growth</t>
         </is>
       </c>
     </row>
     <row r="23" ht="40" customHeight="1">
       <c r="A23" s="25" t="inlineStr">
         <is>
-          <t>BRC</t>
+          <t>TRC</t>
         </is>
       </c>
       <c r="B23" s="26" t="inlineStr">
         <is>
-          <t>Brady Corporation</t>
+          <t>Tejon Ranch Co.</t>
         </is>
       </c>
       <c r="C23" s="49" t="inlineStr">
         <is>
-          <t>Breakout</t>
+          <t>Small Cap</t>
         </is>
       </c>
       <c r="D23" s="23" t="inlineStr">
@@ -24601,38 +24598,38 @@
       </c>
       <c r="E23" s="26" t="inlineStr">
         <is>
-          <t>Emerging Watch</t>
+          <t>Growth Inflection</t>
         </is>
       </c>
       <c r="F23" s="41" t="n">
-        <v>69.90000000000001</v>
+        <v>69.3</v>
       </c>
       <c r="G23" s="50" t="inlineStr">
         <is>
-          <t>Strengths: high-margin business, minimal dilution. Risks: modest growth.</t>
+          <t>Strengths: strong revenue growth, minimal dilution. Risks: thin margins.</t>
         </is>
       </c>
       <c r="H23" s="64" t="inlineStr">
         <is>
-          <t>✓ high-margin business
+          <t>✓ strong revenue growth
 ✓ minimal dilution</t>
         </is>
       </c>
       <c r="I23" s="65" t="inlineStr">
         <is>
-          <t>⚠ modest growth</t>
+          <t>⚠ thin margins</t>
         </is>
       </c>
     </row>
     <row r="24" ht="40" customHeight="1">
       <c r="A24" s="19" t="inlineStr">
         <is>
-          <t>MRCY</t>
+          <t>LYFT</t>
         </is>
       </c>
       <c r="B24" s="20" t="inlineStr">
         <is>
-          <t>Mercury Systems, Inc.</t>
+          <t>Lyft, Inc.</t>
         </is>
       </c>
       <c r="C24" s="48" t="inlineStr">
@@ -24651,34 +24648,34 @@
         </is>
       </c>
       <c r="F24" s="34" t="n">
-        <v>69.8</v>
+        <v>69</v>
       </c>
       <c r="G24" s="46" t="inlineStr">
         <is>
-          <t>Strengths: minimal dilution. Risks: thin margins, modest growth.</t>
+          <t>Strengths: healthy margins, minimal dilution. Risks: none significant.</t>
         </is>
       </c>
       <c r="H24" s="64" t="inlineStr">
         <is>
-          <t>✓ minimal dilution</t>
+          <t>✓ healthy margins
+✓ minimal dilution</t>
         </is>
       </c>
       <c r="I24" s="65" t="inlineStr">
         <is>
-          <t>⚠ thin margins
-⚠ modest growth</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="25" ht="40" customHeight="1">
       <c r="A25" s="25" t="inlineStr">
         <is>
-          <t>CE</t>
+          <t>RUN</t>
         </is>
       </c>
       <c r="B25" s="26" t="inlineStr">
         <is>
-          <t>Celanese Corporation</t>
+          <t>Sunrun Inc.</t>
         </is>
       </c>
       <c r="C25" s="49" t="inlineStr">
@@ -24693,43 +24690,44 @@
       </c>
       <c r="E25" s="26" t="inlineStr">
         <is>
-          <t>Emerging Watch</t>
+          <t>Growth Inflection</t>
         </is>
       </c>
       <c r="F25" s="41" t="n">
-        <v>69.5</v>
+        <v>68.90000000000001</v>
       </c>
       <c r="G25" s="50" t="inlineStr">
         <is>
-          <t>Strengths: minimal dilution. Risks: thin margins, modest growth.</t>
+          <t>Strengths: strong revenue growth, healthy margins. Risks: low insider ownership, negative momentum.</t>
         </is>
       </c>
       <c r="H25" s="64" t="inlineStr">
         <is>
-          <t>✓ minimal dilution</t>
+          <t>✓ strong revenue growth
+✓ healthy margins</t>
         </is>
       </c>
       <c r="I25" s="65" t="inlineStr">
         <is>
-          <t>⚠ thin margins
-⚠ modest growth</t>
+          <t>⚠ low insider ownership
+⚠ negative momentum</t>
         </is>
       </c>
     </row>
     <row r="26" ht="40" customHeight="1">
       <c r="A26" s="19" t="inlineStr">
         <is>
-          <t>RUN</t>
+          <t>INOD</t>
         </is>
       </c>
       <c r="B26" s="20" t="inlineStr">
         <is>
-          <t>Sunrun Inc.</t>
+          <t>Innodata Inc.</t>
         </is>
       </c>
       <c r="C26" s="48" t="inlineStr">
         <is>
-          <t>Breakout</t>
+          <t>Small Cap</t>
         </is>
       </c>
       <c r="D26" s="23" t="inlineStr">
@@ -24739,15 +24737,15 @@
       </c>
       <c r="E26" s="20" t="inlineStr">
         <is>
-          <t>Growth Inflection</t>
+          <t>High-Growth Quality</t>
         </is>
       </c>
       <c r="F26" s="34" t="n">
-        <v>69.09999999999999</v>
+        <v>68.2</v>
       </c>
       <c r="G26" s="46" t="inlineStr">
         <is>
-          <t>Strengths: strong revenue growth, healthy margins. Risks: low insider ownership, negative momentum.</t>
+          <t>Strengths: strong revenue growth, healthy margins. Risks: significant dilution, negative momentum.</t>
         </is>
       </c>
       <c r="H26" s="64" t="inlineStr">
@@ -24758,7 +24756,7 @@
       </c>
       <c r="I26" s="65" t="inlineStr">
         <is>
-          <t>⚠ low insider ownership
+          <t>⚠ significant dilution
 ⚠ negative momentum</t>
         </is>
       </c>
@@ -24766,12 +24764,12 @@
     <row r="27" ht="40" customHeight="1">
       <c r="A27" s="25" t="inlineStr">
         <is>
-          <t>LYFT</t>
+          <t>ITRI</t>
         </is>
       </c>
       <c r="B27" s="26" t="inlineStr">
         <is>
-          <t>Lyft, Inc.</t>
+          <t>Itron, Inc.</t>
         </is>
       </c>
       <c r="C27" s="49" t="inlineStr">
@@ -24790,11 +24788,11 @@
         </is>
       </c>
       <c r="F27" s="41" t="n">
-        <v>69.09999999999999</v>
+        <v>68.2</v>
       </c>
       <c r="G27" s="50" t="inlineStr">
         <is>
-          <t>Strengths: healthy margins, minimal dilution. Risks: none significant.</t>
+          <t>Strengths: healthy margins, minimal dilution. Risks: low insider ownership, modest growth.</t>
         </is>
       </c>
       <c r="H27" s="64" t="inlineStr">
@@ -24805,24 +24803,25 @@
       </c>
       <c r="I27" s="65" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>⚠ low insider ownership
+⚠ modest growth</t>
         </is>
       </c>
     </row>
     <row r="28" ht="40" customHeight="1">
       <c r="A28" s="19" t="inlineStr">
         <is>
-          <t>KN</t>
+          <t>RFIL</t>
         </is>
       </c>
       <c r="B28" s="20" t="inlineStr">
         <is>
-          <t>Knowles Corporation</t>
+          <t>RF Industries, Ltd.</t>
         </is>
       </c>
       <c r="C28" s="48" t="inlineStr">
         <is>
-          <t>Breakout</t>
+          <t>Nano Cap</t>
         </is>
       </c>
       <c r="D28" s="23" t="inlineStr">
@@ -24832,78 +24831,78 @@
       </c>
       <c r="E28" s="20" t="inlineStr">
         <is>
-          <t>Emerging Watch</t>
+          <t>Insider Conviction</t>
         </is>
       </c>
       <c r="F28" s="34" t="n">
-        <v>68.2</v>
+        <v>67.09999999999999</v>
       </c>
       <c r="G28" s="46" t="inlineStr">
         <is>
-          <t>Strengths: healthy margins, minimal dilution. Risks: low insider ownership, modest growth.</t>
+          <t>Strengths: healthy margins, high insider alignment, minimal dilution. Risks: negative momentum, modest growth.</t>
         </is>
       </c>
       <c r="H28" s="64" t="inlineStr">
-        <is>
-          <t>✓ healthy margins
-✓ minimal dilution</t>
-        </is>
-      </c>
-      <c r="I28" s="65" t="inlineStr">
-        <is>
-          <t>⚠ low insider ownership
-⚠ modest growth</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="40" customHeight="1">
-      <c r="A29" s="25" t="inlineStr">
-        <is>
-          <t>RFIL</t>
-        </is>
-      </c>
-      <c r="B29" s="26" t="inlineStr">
-        <is>
-          <t>RF Industries, Ltd.</t>
-        </is>
-      </c>
-      <c r="C29" s="49" t="inlineStr">
-        <is>
-          <t>Nano Cap</t>
-        </is>
-      </c>
-      <c r="D29" s="23" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="E29" s="26" t="inlineStr">
-        <is>
-          <t>Insider Conviction</t>
-        </is>
-      </c>
-      <c r="F29" s="41" t="n">
-        <v>67.40000000000001</v>
-      </c>
-      <c r="G29" s="50" t="inlineStr">
-        <is>
-          <t>Strengths: healthy margins, high insider alignment, minimal dilution. Risks: negative momentum, modest growth.</t>
-        </is>
-      </c>
-      <c r="H29" s="64" t="inlineStr">
         <is>
           <t>✓ healthy margins
 ✓ high insider alignment
 ✓ minimal dilution</t>
         </is>
       </c>
-      <c r="I29" s="65" t="inlineStr">
+      <c r="I28" s="65" t="inlineStr">
         <is>
           <t>⚠ negative momentum
 ⚠ modest growth</t>
         </is>
       </c>
     </row>
+    <row r="29" ht="40" customHeight="1">
+      <c r="A29" s="25" t="inlineStr">
+        <is>
+          <t>CDRE</t>
+        </is>
+      </c>
+      <c r="B29" s="26" t="inlineStr">
+        <is>
+          <t>Cadre Holdings, Inc.</t>
+        </is>
+      </c>
+      <c r="C29" s="49" t="inlineStr">
+        <is>
+          <t>Small Cap</t>
+        </is>
+      </c>
+      <c r="D29" s="23" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E29" s="26" t="inlineStr">
+        <is>
+          <t>Growth Inflection</t>
+        </is>
+      </c>
+      <c r="F29" s="41" t="n">
+        <v>67</v>
+      </c>
+      <c r="G29" s="50" t="inlineStr">
+        <is>
+          <t>Strengths: solid revenue growth, healthy margins, high insider alignment. Risks: none significant.</t>
+        </is>
+      </c>
+      <c r="H29" s="64" t="inlineStr">
+        <is>
+          <t>✓ solid revenue growth
+✓ healthy margins
+✓ high insider alignment</t>
+        </is>
+      </c>
+      <c r="I29" s="65" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
     <row r="30" ht="40" customHeight="1">
       <c r="A30" s="19" t="inlineStr">
         <is>
@@ -25069,7 +25068,7 @@
         </is>
       </c>
       <c r="F33" s="41" t="n">
-        <v>62.4</v>
+        <v>63.1</v>
       </c>
       <c r="G33" s="50" t="inlineStr">
         <is>
@@ -25137,12 +25136,12 @@
     <row r="35" ht="40" customHeight="1">
       <c r="A35" s="25" t="inlineStr">
         <is>
-          <t>QUIK</t>
+          <t>KVHI</t>
         </is>
       </c>
       <c r="B35" s="26" t="inlineStr">
         <is>
-          <t>QuickLogic Corporation</t>
+          <t>KVH Industries, Inc.</t>
         </is>
       </c>
       <c r="C35" s="49" t="inlineStr">
@@ -25157,27 +25156,27 @@
       </c>
       <c r="E35" s="26" t="inlineStr">
         <is>
-          <t>High-Growth Quality</t>
+          <t>Insider Conviction</t>
         </is>
       </c>
       <c r="F35" s="41" t="n">
-        <v>61.6</v>
+        <v>59.4</v>
       </c>
       <c r="G35" s="50" t="inlineStr">
         <is>
-          <t>Strengths: strong revenue growth, healthy margins. Risks: significant dilution, negative momentum.</t>
+          <t>Strengths: solid revenue growth, high insider alignment, minimal dilution. Risks: none significant.</t>
         </is>
       </c>
       <c r="H35" s="64" t="inlineStr">
         <is>
-          <t>✓ strong revenue growth
-✓ healthy margins</t>
+          <t>✓ solid revenue growth
+✓ high insider alignment
+✓ minimal dilution</t>
         </is>
       </c>
       <c r="I35" s="65" t="inlineStr">
         <is>
-          <t>⚠ significant dilution
-⚠ negative momentum</t>
+          <t>—</t>
         </is>
       </c>
     </row>

--- a/output/screener_output_20260908.xlsx
+++ b/output/screener_output_20260908.xlsx
@@ -14865,15 +14865,16 @@
     <col width="12" customWidth="1" min="11" max="11"/>
     <col width="12" customWidth="1" min="12" max="12"/>
     <col width="12" customWidth="1" min="13" max="13"/>
-    <col width="10" customWidth="1" min="14" max="14"/>
-    <col width="14" customWidth="1" min="15" max="15"/>
+    <col width="12" customWidth="1" min="14" max="14"/>
+    <col width="10" customWidth="1" min="15" max="15"/>
     <col width="14" customWidth="1" min="16" max="16"/>
-    <col width="12" customWidth="1" min="17" max="17"/>
-    <col width="10" customWidth="1" min="18" max="18"/>
+    <col width="14" customWidth="1" min="17" max="17"/>
+    <col width="12" customWidth="1" min="18" max="18"/>
     <col width="10" customWidth="1" min="19" max="19"/>
     <col width="10" customWidth="1" min="20" max="20"/>
     <col width="10" customWidth="1" min="21" max="21"/>
     <col width="10" customWidth="1" min="22" max="22"/>
+    <col width="10" customWidth="1" min="23" max="23"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -15108,19 +15109,24 @@
       <c r="Q5" s="39" t="n">
         <v>4.4</v>
       </c>
-      <c r="R5" s="34" t="n">
+      <c r="R5" s="23" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="S5" s="34" t="n">
         <v>0.007246376799999999</v>
       </c>
-      <c r="S5" s="34" t="n">
+      <c r="T5" s="34" t="n">
         <v>-0.2553571</v>
       </c>
-      <c r="T5" s="34" t="n">
+      <c r="U5" s="34" t="n">
         <v>-0.2132075</v>
       </c>
-      <c r="U5" s="34" t="n">
+      <c r="V5" s="34" t="n">
         <v>-0.2785467</v>
       </c>
-      <c r="V5" s="34" t="n">
+      <c r="W5" s="34" t="n">
         <v>-0.5162413</v>
       </c>
     </row>
@@ -15182,19 +15188,24 @@
       <c r="Q6" s="39" t="n">
         <v>27.8</v>
       </c>
-      <c r="R6" s="41" t="n">
+      <c r="R6" s="27" t="inlineStr">
+        <is>
+          <t>Speculative</t>
+        </is>
+      </c>
+      <c r="S6" s="41" t="n">
         <v>-0.175089</v>
       </c>
-      <c r="S6" s="41" t="n">
+      <c r="T6" s="41" t="n">
         <v>-0.2584773</v>
       </c>
-      <c r="T6" s="41" t="n">
+      <c r="U6" s="41" t="n">
         <v>-0.1246224</v>
       </c>
-      <c r="U6" s="41" t="n">
+      <c r="V6" s="41" t="n">
         <v>0.5515395000000001</v>
       </c>
-      <c r="V6" s="41" t="n">
+      <c r="W6" s="41" t="n">
         <v>0.6097222</v>
       </c>
     </row>
@@ -15256,19 +15267,24 @@
       <c r="Q7" s="39" t="n">
         <v>14.8</v>
       </c>
-      <c r="R7" s="34" t="n">
+      <c r="R7" s="27" t="inlineStr">
+        <is>
+          <t>Speculative</t>
+        </is>
+      </c>
+      <c r="S7" s="34" t="n">
         <v>-0.1135492</v>
       </c>
-      <c r="S7" s="34" t="n">
+      <c r="T7" s="34" t="n">
         <v>-0.07315100000000001</v>
       </c>
-      <c r="T7" s="34" t="n">
+      <c r="U7" s="34" t="n">
         <v>0.2044332</v>
       </c>
-      <c r="U7" s="34" t="n">
+      <c r="V7" s="34" t="n">
         <v>0.0212626</v>
       </c>
-      <c r="V7" s="34" t="n">
+      <c r="W7" s="34" t="n">
         <v>0.1612072</v>
       </c>
     </row>
@@ -15330,19 +15346,24 @@
       <c r="Q8" s="39" t="n">
         <v>27.6</v>
       </c>
-      <c r="R8" s="41" t="n">
+      <c r="R8" s="27" t="inlineStr">
+        <is>
+          <t>Speculative</t>
+        </is>
+      </c>
+      <c r="S8" s="41" t="n">
         <v>-0.1526151</v>
       </c>
-      <c r="S8" s="41" t="n">
+      <c r="T8" s="41" t="n">
         <v>-0.3488302</v>
       </c>
-      <c r="T8" s="41" t="n">
+      <c r="U8" s="41" t="n">
         <v>0.039751</v>
       </c>
-      <c r="U8" s="41" t="n">
+      <c r="V8" s="41" t="n">
         <v>0.8780277</v>
       </c>
-      <c r="V8" s="41" t="n">
+      <c r="W8" s="41" t="n">
         <v>0.4829235</v>
       </c>
     </row>
@@ -15404,19 +15425,24 @@
       <c r="Q9" s="39" t="n">
         <v>13.8</v>
       </c>
-      <c r="R9" s="34" t="n">
+      <c r="R9" s="27" t="inlineStr">
+        <is>
+          <t>Speculative</t>
+        </is>
+      </c>
+      <c r="S9" s="34" t="n">
         <v>-0.0546512</v>
       </c>
-      <c r="S9" s="34" t="n">
+      <c r="T9" s="34" t="n">
         <v>0.101626</v>
       </c>
-      <c r="T9" s="34" t="n">
+      <c r="U9" s="34" t="n">
         <v>-0.151357</v>
       </c>
-      <c r="U9" s="34" t="n">
+      <c r="V9" s="34" t="n">
         <v>-0.4761598</v>
       </c>
-      <c r="V9" s="34" t="n">
+      <c r="W9" s="34" t="n">
         <v>-0.2930435</v>
       </c>
     </row>
@@ -15478,19 +15504,24 @@
       <c r="Q10" s="45" t="n">
         <v>43.6</v>
       </c>
-      <c r="R10" s="41" t="n">
+      <c r="R10" s="27" t="inlineStr">
+        <is>
+          <t>Speculative</t>
+        </is>
+      </c>
+      <c r="S10" s="41" t="n">
         <v>-0.0071860914</v>
       </c>
-      <c r="S10" s="41" t="n">
+      <c r="T10" s="41" t="n">
         <v>-0.2177372</v>
       </c>
-      <c r="T10" s="41" t="n">
+      <c r="U10" s="41" t="n">
         <v>0.1933746</v>
       </c>
-      <c r="U10" s="41" t="n">
+      <c r="V10" s="41" t="n">
         <v>0.2285578</v>
       </c>
-      <c r="V10" s="41" t="n">
+      <c r="W10" s="41" t="n">
         <v>0.9443127</v>
       </c>
     </row>
@@ -15552,19 +15583,24 @@
       <c r="Q11" s="39" t="n">
         <v>11.3</v>
       </c>
-      <c r="R11" s="34" t="n">
+      <c r="R11" s="27" t="inlineStr">
+        <is>
+          <t>Speculative</t>
+        </is>
+      </c>
+      <c r="S11" s="34" t="n">
         <v>-0.1063652</v>
       </c>
-      <c r="S11" s="34" t="n">
+      <c r="T11" s="34" t="n">
         <v>-0.2061012</v>
       </c>
-      <c r="T11" s="34" t="n">
+      <c r="U11" s="34" t="n">
         <v>-0.0557522</v>
       </c>
-      <c r="U11" s="34" t="n">
+      <c r="V11" s="34" t="n">
         <v>-0.0895904</v>
       </c>
-      <c r="V11" s="34" t="n">
+      <c r="W11" s="34" t="n">
         <v>0.1184486</v>
       </c>
     </row>
@@ -15626,19 +15662,24 @@
       <c r="Q12" s="39" t="n">
         <v>6.1</v>
       </c>
-      <c r="R12" s="41" t="n">
+      <c r="R12" s="27" t="inlineStr">
+        <is>
+          <t>Speculative</t>
+        </is>
+      </c>
+      <c r="S12" s="41" t="n">
         <v>-0.0272109</v>
       </c>
-      <c r="S12" s="41" t="n">
+      <c r="T12" s="41" t="n">
         <v>-0.0793991</v>
       </c>
-      <c r="T12" s="41" t="n">
+      <c r="U12" s="41" t="n">
         <v>-0.3254717</v>
       </c>
-      <c r="U12" s="41" t="n">
+      <c r="V12" s="41" t="n">
         <v>-0.3035714</v>
       </c>
-      <c r="V12" s="41" t="n">
+      <c r="W12" s="41" t="n">
         <v>-0.3035714</v>
       </c>
     </row>
@@ -15700,19 +15741,24 @@
       <c r="Q13" s="39" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="R13" s="34" t="n">
+      <c r="R13" s="27" t="inlineStr">
+        <is>
+          <t>Speculative</t>
+        </is>
+      </c>
+      <c r="S13" s="34" t="n">
         <v>-0.1748072</v>
       </c>
-      <c r="S13" s="34" t="n">
+      <c r="T13" s="34" t="n">
         <v>-0.4729064000000001</v>
       </c>
-      <c r="T13" s="34" t="n">
+      <c r="U13" s="34" t="n">
         <v>0.07718120000000001</v>
       </c>
-      <c r="U13" s="34" t="n">
+      <c r="V13" s="34" t="n">
         <v>-0.3502024</v>
       </c>
-      <c r="V13" s="34" t="n">
+      <c r="W13" s="34" t="n">
         <v>-0.5143722000000001</v>
       </c>
     </row>
@@ -15774,19 +15820,24 @@
       <c r="Q14" s="39" t="n">
         <v>17.6</v>
       </c>
-      <c r="R14" s="41" t="n">
+      <c r="R14" s="27" t="inlineStr">
+        <is>
+          <t>Speculative</t>
+        </is>
+      </c>
+      <c r="S14" s="41" t="n">
         <v>-0.05880080000000001</v>
       </c>
-      <c r="S14" s="41" t="n">
+      <c r="T14" s="41" t="n">
         <v>-0.0897213</v>
       </c>
-      <c r="T14" s="41" t="n">
+      <c r="U14" s="41" t="n">
         <v>-0.1400188</v>
       </c>
-      <c r="U14" s="41" t="n">
+      <c r="V14" s="41" t="n">
         <v>-0.0193055</v>
       </c>
-      <c r="V14" s="41" t="n">
+      <c r="W14" s="41" t="n">
         <v>0.0590705</v>
       </c>
     </row>
@@ -15817,6 +15868,7 @@
       <c r="T17" s="17" t="n"/>
       <c r="U17" s="17" t="n"/>
       <c r="V17" s="17" t="n"/>
+      <c r="W17" s="17" t="n"/>
     </row>
     <row r="18" ht="18" customHeight="1">
       <c r="A18" s="18" t="inlineStr">
@@ -16256,9 +16308,9 @@
   <mergeCells count="3">
     <mergeCell ref="A2:V2"/>
     <mergeCell ref="A1:V1"/>
-    <mergeCell ref="A17:V17"/>
+    <mergeCell ref="A17:W17"/>
   </mergeCells>
-  <conditionalFormatting sqref="K5:K14">
+  <conditionalFormatting sqref="L5:L14">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="num" val="0"/>
@@ -16270,7 +16322,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L5:L14">
+  <conditionalFormatting sqref="M5:M14">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="num" val="0"/>
@@ -16282,7 +16334,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M5:M14">
+  <conditionalFormatting sqref="N5:N14">
     <cfRule type="colorScale" priority="3">
       <colorScale>
         <cfvo type="num" val="0"/>
@@ -16294,7 +16346,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N5:N14">
+  <conditionalFormatting sqref="O5:O14">
     <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="num" val="0"/>
@@ -16306,7 +16358,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P5:P14">
+  <conditionalFormatting sqref="Q5:Q14">
     <cfRule type="colorScale" priority="5">
       <colorScale>
         <cfvo type="min"/>
@@ -16356,15 +16408,15 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R5:R14">
+  <conditionalFormatting sqref="K5:K14">
     <cfRule type="colorScale" priority="10">
       <colorScale>
-        <cfvo type="min"/>
         <cfvo type="num" val="0"/>
-        <cfvo type="max"/>
-        <color rgb="00E76F51"/>
-        <color rgb="00FFFFFF"/>
-        <color rgb="002A9D8F"/>
+        <cfvo type="num" val="50"/>
+        <cfvo type="num" val="100"/>
+        <color rgb="00C1121F"/>
+        <color rgb="00F9C74F"/>
+        <color rgb="001A6B3C"/>
       </colorScale>
     </cfRule>
   </conditionalFormatting>
@@ -16416,8 +16468,20 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="W5:W14">
+    <cfRule type="colorScale" priority="15">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="num" val="0"/>
+        <cfvo type="max"/>
+        <color rgb="00E76F51"/>
+        <color rgb="00FFFFFF"/>
+        <color rgb="002A9D8F"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="B19:B28">
-    <cfRule type="colorScale" priority="15">
+    <cfRule type="colorScale" priority="16">
       <colorScale>
         <cfvo type="num" val="0"/>
         <cfvo type="num" val="50"/>
@@ -16429,7 +16493,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C19:C28">
-    <cfRule type="colorScale" priority="16">
+    <cfRule type="colorScale" priority="17">
       <colorScale>
         <cfvo type="num" val="0"/>
         <cfvo type="num" val="50"/>
@@ -16441,7 +16505,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D19:D28">
-    <cfRule type="colorScale" priority="17">
+    <cfRule type="colorScale" priority="18">
       <colorScale>
         <cfvo type="num" val="0"/>
         <cfvo type="num" val="50"/>
@@ -16453,7 +16517,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E19:E28">
-    <cfRule type="colorScale" priority="18">
+    <cfRule type="colorScale" priority="19">
       <colorScale>
         <cfvo type="num" val="0"/>
         <cfvo type="num" val="50"/>
@@ -16465,7 +16529,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F19:F28">
-    <cfRule type="colorScale" priority="19">
+    <cfRule type="colorScale" priority="20">
       <colorScale>
         <cfvo type="num" val="0"/>
         <cfvo type="num" val="50"/>
@@ -16505,15 +16569,16 @@
     <col width="12" customWidth="1" min="11" max="11"/>
     <col width="12" customWidth="1" min="12" max="12"/>
     <col width="12" customWidth="1" min="13" max="13"/>
-    <col width="10" customWidth="1" min="14" max="14"/>
-    <col width="14" customWidth="1" min="15" max="15"/>
+    <col width="12" customWidth="1" min="14" max="14"/>
+    <col width="10" customWidth="1" min="15" max="15"/>
     <col width="14" customWidth="1" min="16" max="16"/>
-    <col width="12" customWidth="1" min="17" max="17"/>
-    <col width="10" customWidth="1" min="18" max="18"/>
+    <col width="14" customWidth="1" min="17" max="17"/>
+    <col width="12" customWidth="1" min="18" max="18"/>
     <col width="10" customWidth="1" min="19" max="19"/>
     <col width="10" customWidth="1" min="20" max="20"/>
     <col width="10" customWidth="1" min="21" max="21"/>
     <col width="10" customWidth="1" min="22" max="22"/>
+    <col width="10" customWidth="1" min="23" max="23"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -16748,19 +16813,24 @@
       <c r="Q5" s="39" t="n">
         <v>31.8</v>
       </c>
-      <c r="R5" s="34" t="n">
+      <c r="R5" s="23" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="S5" s="34" t="n">
         <v>-0.0764</v>
       </c>
-      <c r="S5" s="34" t="n">
+      <c r="T5" s="34" t="n">
         <v>-0.1028425</v>
       </c>
-      <c r="T5" s="34" t="n">
+      <c r="U5" s="34" t="n">
         <v>-0.0592352</v>
       </c>
-      <c r="U5" s="34" t="n">
+      <c r="V5" s="34" t="n">
         <v>0.333465</v>
       </c>
-      <c r="V5" s="34" t="n">
+      <c r="W5" s="34" t="n">
         <v>0.4888348</v>
       </c>
     </row>
@@ -16822,19 +16892,24 @@
       <c r="Q6" s="45" t="n">
         <v>65.90000000000001</v>
       </c>
-      <c r="R6" s="41" t="n">
+      <c r="R6" s="27" t="inlineStr">
+        <is>
+          <t>Speculative</t>
+        </is>
+      </c>
+      <c r="S6" s="41" t="n">
         <v>-0.1993195</v>
       </c>
-      <c r="S6" s="41" t="n">
+      <c r="T6" s="41" t="n">
         <v>-0.0620936</v>
       </c>
-      <c r="T6" s="41" t="n">
+      <c r="U6" s="41" t="n">
         <v>0.09556480000000001</v>
       </c>
-      <c r="U6" s="41" t="n">
+      <c r="V6" s="41" t="n">
         <v>0.3921843</v>
       </c>
-      <c r="V6" s="41" t="n">
+      <c r="W6" s="41" t="n">
         <v>0.8711027</v>
       </c>
     </row>
@@ -16896,19 +16971,24 @@
       <c r="Q7" s="39" t="n">
         <v>7.5</v>
       </c>
-      <c r="R7" s="34" t="n">
+      <c r="R7" s="27" t="inlineStr">
+        <is>
+          <t>Speculative</t>
+        </is>
+      </c>
+      <c r="S7" s="34" t="n">
         <v>-0.009964050300000001</v>
       </c>
-      <c r="S7" s="34" t="n">
+      <c r="T7" s="34" t="n">
         <v>-0.1380438</v>
       </c>
-      <c r="T7" s="34" t="n">
+      <c r="U7" s="34" t="n">
         <v>-0.0779185</v>
       </c>
-      <c r="U7" s="34" t="n">
+      <c r="V7" s="34" t="n">
         <v>0.0477933</v>
       </c>
-      <c r="V7" s="34" t="n">
+      <c r="W7" s="34" t="n">
         <v>-0.0251504</v>
       </c>
     </row>
@@ -16970,19 +17050,24 @@
       <c r="Q8" s="39" t="n">
         <v>21.9</v>
       </c>
-      <c r="R8" s="41" t="n">
+      <c r="R8" s="27" t="inlineStr">
+        <is>
+          <t>Speculative</t>
+        </is>
+      </c>
+      <c r="S8" s="41" t="n">
         <v>-0.2711404</v>
       </c>
-      <c r="S8" s="41" t="n">
+      <c r="T8" s="41" t="n">
         <v>-0.3827201</v>
       </c>
-      <c r="T8" s="41" t="n">
+      <c r="U8" s="41" t="n">
         <v>0.4733403</v>
       </c>
-      <c r="U8" s="41" t="n">
+      <c r="V8" s="41" t="n">
         <v>0.3097119</v>
       </c>
-      <c r="V8" s="41" t="n">
+      <c r="W8" s="41" t="n">
         <v>0.2127797</v>
       </c>
     </row>
@@ -17044,19 +17129,24 @@
       <c r="Q9" s="45" t="n">
         <v>60.3</v>
       </c>
-      <c r="R9" s="34" t="n">
+      <c r="R9" s="27" t="inlineStr">
+        <is>
+          <t>Speculative</t>
+        </is>
+      </c>
+      <c r="S9" s="34" t="n">
         <v>-0.04738299999999999</v>
       </c>
-      <c r="S9" s="34" t="n">
+      <c r="T9" s="34" t="n">
         <v>-0.4553184</v>
       </c>
-      <c r="T9" s="34" t="n">
+      <c r="U9" s="34" t="n">
         <v>0.5034514</v>
       </c>
-      <c r="U9" s="34" t="n">
+      <c r="V9" s="34" t="n">
         <v>0.6971429</v>
       </c>
-      <c r="V9" s="34" t="n">
+      <c r="W9" s="34" t="n">
         <v>1.1809079</v>
       </c>
     </row>
@@ -17118,19 +17208,24 @@
       <c r="Q10" s="45" t="n">
         <v>41.2</v>
       </c>
-      <c r="R10" s="41" t="n">
+      <c r="R10" s="27" t="inlineStr">
+        <is>
+          <t>Speculative</t>
+        </is>
+      </c>
+      <c r="S10" s="41" t="n">
         <v>0.3156425</v>
       </c>
-      <c r="S10" s="41" t="n">
+      <c r="T10" s="41" t="n">
         <v>0.369186</v>
       </c>
-      <c r="T10" s="41" t="n">
+      <c r="U10" s="41" t="n">
         <v>0.5292208</v>
       </c>
-      <c r="U10" s="41" t="n">
+      <c r="V10" s="41" t="n">
         <v>0.4101796</v>
       </c>
-      <c r="V10" s="41" t="n">
+      <c r="W10" s="41" t="n">
         <v>0.1432039</v>
       </c>
     </row>
@@ -17192,19 +17287,24 @@
       <c r="Q11" s="39" t="n">
         <v>2.3</v>
       </c>
-      <c r="R11" s="34" t="n">
+      <c r="R11" s="27" t="inlineStr">
+        <is>
+          <t>Speculative</t>
+        </is>
+      </c>
+      <c r="S11" s="34" t="n">
         <v>-0.1703263</v>
       </c>
-      <c r="S11" s="34" t="n">
+      <c r="T11" s="34" t="n">
         <v>-0.126134</v>
       </c>
-      <c r="T11" s="34" t="n">
+      <c r="U11" s="34" t="n">
         <v>0.0011614173</v>
       </c>
-      <c r="U11" s="34" t="n">
+      <c r="V11" s="34" t="n">
         <v>-0.2896788</v>
       </c>
-      <c r="V11" s="34" t="n">
+      <c r="W11" s="34" t="n">
         <v>-0.3850181</v>
       </c>
     </row>
@@ -17266,19 +17366,24 @@
       <c r="Q12" s="39" t="n">
         <v>1.9</v>
       </c>
-      <c r="R12" s="41" t="n">
+      <c r="R12" s="27" t="inlineStr">
+        <is>
+          <t>Speculative</t>
+        </is>
+      </c>
+      <c r="S12" s="41" t="n">
         <v>-0.003968254</v>
       </c>
-      <c r="S12" s="41" t="n">
+      <c r="T12" s="41" t="n">
         <v>-0.5299625</v>
       </c>
-      <c r="T12" s="41" t="n">
+      <c r="U12" s="41" t="n">
         <v>-0.2148071</v>
       </c>
-      <c r="U12" s="41" t="n">
+      <c r="V12" s="41" t="n">
         <v>-0.1334868</v>
       </c>
-      <c r="V12" s="41" t="n">
+      <c r="W12" s="41" t="n">
         <v>-0.2617647</v>
       </c>
     </row>
@@ -17340,19 +17445,24 @@
       <c r="Q13" s="39" t="n">
         <v>28</v>
       </c>
-      <c r="R13" s="34" t="n">
+      <c r="R13" s="27" t="inlineStr">
+        <is>
+          <t>Speculative</t>
+        </is>
+      </c>
+      <c r="S13" s="34" t="n">
         <v>-0.07517310000000001</v>
       </c>
-      <c r="S13" s="34" t="n">
+      <c r="T13" s="34" t="n">
         <v>0.5008026</v>
       </c>
-      <c r="T13" s="34" t="n">
+      <c r="U13" s="34" t="n">
         <v>0.1150865</v>
       </c>
-      <c r="U13" s="34" t="n">
+      <c r="V13" s="34" t="n">
         <v>0.08405799999999999</v>
       </c>
-      <c r="V13" s="34" t="n">
+      <c r="W13" s="34" t="n">
         <v>0.2541918</v>
       </c>
     </row>
@@ -17414,19 +17524,24 @@
       <c r="Q14" s="39" t="n">
         <v>20</v>
       </c>
-      <c r="R14" s="41" t="n">
+      <c r="R14" s="27" t="inlineStr">
+        <is>
+          <t>Speculative</t>
+        </is>
+      </c>
+      <c r="S14" s="41" t="n">
         <v>0.0315871</v>
       </c>
-      <c r="S14" s="41" t="n">
+      <c r="T14" s="41" t="n">
         <v>0.1158333</v>
       </c>
-      <c r="T14" s="41" t="n">
+      <c r="U14" s="41" t="n">
         <v>0.1047855</v>
       </c>
-      <c r="U14" s="41" t="n">
+      <c r="V14" s="41" t="n">
         <v>0.2239488</v>
       </c>
-      <c r="V14" s="41" t="n">
+      <c r="W14" s="41" t="n">
         <v>0.0939542</v>
       </c>
     </row>
@@ -17457,6 +17572,7 @@
       <c r="T17" s="17" t="n"/>
       <c r="U17" s="17" t="n"/>
       <c r="V17" s="17" t="n"/>
+      <c r="W17" s="17" t="n"/>
     </row>
     <row r="18" ht="18" customHeight="1">
       <c r="A18" s="18" t="inlineStr">
@@ -17896,9 +18012,9 @@
   <mergeCells count="3">
     <mergeCell ref="A2:V2"/>
     <mergeCell ref="A1:V1"/>
-    <mergeCell ref="A17:V17"/>
+    <mergeCell ref="A17:W17"/>
   </mergeCells>
-  <conditionalFormatting sqref="K5:K14">
+  <conditionalFormatting sqref="L5:L14">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="num" val="0"/>
@@ -17910,7 +18026,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L5:L14">
+  <conditionalFormatting sqref="M5:M14">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="num" val="0"/>
@@ -17922,7 +18038,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M5:M14">
+  <conditionalFormatting sqref="N5:N14">
     <cfRule type="colorScale" priority="3">
       <colorScale>
         <cfvo type="num" val="0"/>
@@ -17934,7 +18050,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N5:N14">
+  <conditionalFormatting sqref="O5:O14">
     <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="num" val="0"/>
@@ -17946,7 +18062,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P5:P14">
+  <conditionalFormatting sqref="Q5:Q14">
     <cfRule type="colorScale" priority="5">
       <colorScale>
         <cfvo type="min"/>
@@ -17996,15 +18112,15 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R5:R14">
+  <conditionalFormatting sqref="K5:K14">
     <cfRule type="colorScale" priority="10">
       <colorScale>
-        <cfvo type="min"/>
         <cfvo type="num" val="0"/>
-        <cfvo type="max"/>
-        <color rgb="00E76F51"/>
-        <color rgb="00FFFFFF"/>
-        <color rgb="002A9D8F"/>
+        <cfvo type="num" val="50"/>
+        <cfvo type="num" val="100"/>
+        <color rgb="00C1121F"/>
+        <color rgb="00F9C74F"/>
+        <color rgb="001A6B3C"/>
       </colorScale>
     </cfRule>
   </conditionalFormatting>
@@ -18056,8 +18172,20 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="W5:W14">
+    <cfRule type="colorScale" priority="15">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="num" val="0"/>
+        <cfvo type="max"/>
+        <color rgb="00E76F51"/>
+        <color rgb="00FFFFFF"/>
+        <color rgb="002A9D8F"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="B19:B28">
-    <cfRule type="colorScale" priority="15">
+    <cfRule type="colorScale" priority="16">
       <colorScale>
         <cfvo type="num" val="0"/>
         <cfvo type="num" val="50"/>
@@ -18069,7 +18197,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C19:C28">
-    <cfRule type="colorScale" priority="16">
+    <cfRule type="colorScale" priority="17">
       <colorScale>
         <cfvo type="num" val="0"/>
         <cfvo type="num" val="50"/>
@@ -18081,7 +18209,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D19:D28">
-    <cfRule type="colorScale" priority="17">
+    <cfRule type="colorScale" priority="18">
       <colorScale>
         <cfvo type="num" val="0"/>
         <cfvo type="num" val="50"/>
@@ -18093,7 +18221,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E19:E28">
-    <cfRule type="colorScale" priority="18">
+    <cfRule type="colorScale" priority="19">
       <colorScale>
         <cfvo type="num" val="0"/>
         <cfvo type="num" val="50"/>
@@ -18105,7 +18233,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F19:F28">
-    <cfRule type="colorScale" priority="19">
+    <cfRule type="colorScale" priority="20">
       <colorScale>
         <cfvo type="num" val="0"/>
         <cfvo type="num" val="50"/>
@@ -18145,15 +18273,16 @@
     <col width="12" customWidth="1" min="11" max="11"/>
     <col width="12" customWidth="1" min="12" max="12"/>
     <col width="12" customWidth="1" min="13" max="13"/>
-    <col width="10" customWidth="1" min="14" max="14"/>
-    <col width="14" customWidth="1" min="15" max="15"/>
+    <col width="12" customWidth="1" min="14" max="14"/>
+    <col width="10" customWidth="1" min="15" max="15"/>
     <col width="14" customWidth="1" min="16" max="16"/>
-    <col width="12" customWidth="1" min="17" max="17"/>
-    <col width="10" customWidth="1" min="18" max="18"/>
+    <col width="14" customWidth="1" min="17" max="17"/>
+    <col width="12" customWidth="1" min="18" max="18"/>
     <col width="10" customWidth="1" min="19" max="19"/>
     <col width="10" customWidth="1" min="20" max="20"/>
     <col width="10" customWidth="1" min="21" max="21"/>
     <col width="10" customWidth="1" min="22" max="22"/>
+    <col width="10" customWidth="1" min="23" max="23"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -18388,19 +18517,24 @@
       <c r="Q5" s="39" t="n">
         <v>12.8</v>
       </c>
-      <c r="R5" s="34" t="n">
+      <c r="R5" s="23" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="S5" s="34" t="n">
         <v>0.0141262</v>
       </c>
-      <c r="S5" s="34" t="n">
+      <c r="T5" s="34" t="n">
         <v>-0.0931133</v>
       </c>
-      <c r="T5" s="34" t="n">
+      <c r="U5" s="34" t="n">
         <v>-0.0975264</v>
       </c>
-      <c r="U5" s="34" t="n">
+      <c r="V5" s="34" t="n">
         <v>0.05274359999999999</v>
       </c>
-      <c r="V5" s="34" t="n">
+      <c r="W5" s="34" t="n">
         <v>-0.04320719999999999</v>
       </c>
     </row>
@@ -18462,19 +18596,24 @@
       <c r="Q6" s="39" t="n">
         <v>1.3</v>
       </c>
-      <c r="R6" s="41" t="n">
+      <c r="R6" s="23" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="S6" s="41" t="n">
         <v>-0.0709584</v>
       </c>
-      <c r="S6" s="41" t="n">
+      <c r="T6" s="41" t="n">
         <v>-0.0535139</v>
       </c>
-      <c r="T6" s="41" t="n">
+      <c r="U6" s="41" t="n">
         <v>-0.3008718</v>
       </c>
-      <c r="U6" s="41" t="n">
+      <c r="V6" s="41" t="n">
         <v>-0.3333648</v>
       </c>
-      <c r="V6" s="41" t="n">
+      <c r="W6" s="41" t="n">
         <v>-0.4225041</v>
       </c>
     </row>
@@ -18536,19 +18675,24 @@
       <c r="Q7" s="45" t="n">
         <v>51.1</v>
       </c>
-      <c r="R7" s="34" t="n">
+      <c r="R7" s="27" t="inlineStr">
+        <is>
+          <t>Speculative</t>
+        </is>
+      </c>
+      <c r="S7" s="34" t="n">
         <v>-0.0364896</v>
       </c>
-      <c r="S7" s="34" t="n">
+      <c r="T7" s="34" t="n">
         <v>-0.1378796</v>
       </c>
-      <c r="T7" s="34" t="n">
+      <c r="U7" s="34" t="n">
         <v>0.3688928</v>
       </c>
-      <c r="U7" s="34" t="n">
+      <c r="V7" s="34" t="n">
         <v>0.5768058</v>
       </c>
-      <c r="V7" s="34" t="n">
+      <c r="W7" s="34" t="n">
         <v>0.7696747</v>
       </c>
     </row>
@@ -18610,19 +18754,24 @@
       <c r="Q8" s="39" t="n">
         <v>20.7</v>
       </c>
-      <c r="R8" s="41" t="n">
+      <c r="R8" s="27" t="inlineStr">
+        <is>
+          <t>Speculative</t>
+        </is>
+      </c>
+      <c r="S8" s="41" t="n">
         <v>-0.0709867</v>
       </c>
-      <c r="S8" s="41" t="n">
+      <c r="T8" s="41" t="n">
         <v>0.09085499999999999</v>
       </c>
-      <c r="T8" s="41" t="n">
+      <c r="U8" s="41" t="n">
         <v>0.032458</v>
       </c>
-      <c r="U8" s="41" t="n">
+      <c r="V8" s="41" t="n">
         <v>0.0332732</v>
       </c>
-      <c r="V8" s="41" t="n">
+      <c r="W8" s="41" t="n">
         <v>0.1276465</v>
       </c>
     </row>
@@ -18684,19 +18833,24 @@
       <c r="Q9" s="39" t="n">
         <v>18.1</v>
       </c>
-      <c r="R9" s="34" t="n">
+      <c r="R9" s="27" t="inlineStr">
+        <is>
+          <t>Speculative</t>
+        </is>
+      </c>
+      <c r="S9" s="34" t="n">
         <v>-0.0535698</v>
       </c>
-      <c r="S9" s="34" t="n">
+      <c r="T9" s="34" t="n">
         <v>0.04776</v>
       </c>
-      <c r="T9" s="34" t="n">
+      <c r="U9" s="34" t="n">
         <v>-0.09756930000000001</v>
       </c>
-      <c r="U9" s="34" t="n">
+      <c r="V9" s="34" t="n">
         <v>-0.0903795</v>
       </c>
-      <c r="V9" s="34" t="n">
+      <c r="W9" s="34" t="n">
         <v>-0.07589209999999999</v>
       </c>
     </row>
@@ -18758,19 +18912,24 @@
       <c r="Q10" s="39" t="n">
         <v>30.8</v>
       </c>
-      <c r="R10" s="41" t="n">
+      <c r="R10" s="27" t="inlineStr">
+        <is>
+          <t>Speculative</t>
+        </is>
+      </c>
+      <c r="S10" s="41" t="n">
         <v>-0.0826219</v>
       </c>
-      <c r="S10" s="41" t="n">
+      <c r="T10" s="41" t="n">
         <v>-0.08009289999999999</v>
       </c>
-      <c r="T10" s="41" t="n">
+      <c r="U10" s="41" t="n">
         <v>0.0872921</v>
       </c>
-      <c r="U10" s="41" t="n">
+      <c r="V10" s="41" t="n">
         <v>0.1531466</v>
       </c>
-      <c r="V10" s="41" t="n">
+      <c r="W10" s="41" t="n">
         <v>0.3180873</v>
       </c>
     </row>
@@ -18832,19 +18991,24 @@
       <c r="Q11" s="45" t="n">
         <v>46.9</v>
       </c>
-      <c r="R11" s="34" t="n">
+      <c r="R11" s="27" t="inlineStr">
+        <is>
+          <t>Speculative</t>
+        </is>
+      </c>
+      <c r="S11" s="34" t="n">
         <v>-0.0427199</v>
       </c>
-      <c r="S11" s="34" t="n">
+      <c r="T11" s="34" t="n">
         <v>0.1883114</v>
       </c>
-      <c r="T11" s="34" t="n">
+      <c r="U11" s="34" t="n">
         <v>0.001461039</v>
       </c>
-      <c r="U11" s="34" t="n">
+      <c r="V11" s="34" t="n">
         <v>0.1578236</v>
       </c>
-      <c r="V11" s="34" t="n">
+      <c r="W11" s="34" t="n">
         <v>0.301367</v>
       </c>
     </row>
@@ -18906,19 +19070,24 @@
       <c r="Q12" s="45" t="n">
         <v>48.8</v>
       </c>
-      <c r="R12" s="41" t="n">
+      <c r="R12" s="27" t="inlineStr">
+        <is>
+          <t>Speculative</t>
+        </is>
+      </c>
+      <c r="S12" s="41" t="n">
         <v>-0.0492216</v>
       </c>
-      <c r="S12" s="41" t="n">
+      <c r="T12" s="41" t="n">
         <v>0.0507947</v>
       </c>
-      <c r="T12" s="41" t="n">
+      <c r="U12" s="41" t="n">
         <v>0.4366039</v>
       </c>
-      <c r="U12" s="41" t="n">
+      <c r="V12" s="41" t="n">
         <v>0.2596739</v>
       </c>
-      <c r="V12" s="41" t="n">
+      <c r="W12" s="41" t="n">
         <v>0.5150012</v>
       </c>
     </row>
@@ -18980,19 +19149,24 @@
       <c r="Q13" s="39" t="n">
         <v>23.5</v>
       </c>
-      <c r="R13" s="34" t="n">
+      <c r="R13" s="27" t="inlineStr">
+        <is>
+          <t>Speculative</t>
+        </is>
+      </c>
+      <c r="S13" s="34" t="n">
         <v>-0.0783015</v>
       </c>
-      <c r="S13" s="34" t="n">
+      <c r="T13" s="34" t="n">
         <v>0.1319464</v>
       </c>
-      <c r="T13" s="34" t="n">
+      <c r="U13" s="34" t="n">
         <v>0.0026208026</v>
       </c>
-      <c r="U13" s="34" t="n">
+      <c r="V13" s="34" t="n">
         <v>0.0503647</v>
       </c>
-      <c r="V13" s="34" t="n">
+      <c r="W13" s="34" t="n">
         <v>-0.06054789999999999</v>
       </c>
     </row>
@@ -19054,19 +19228,24 @@
       <c r="Q14" s="39" t="n">
         <v>5.9</v>
       </c>
-      <c r="R14" s="41" t="n">
+      <c r="R14" s="27" t="inlineStr">
+        <is>
+          <t>Speculative</t>
+        </is>
+      </c>
+      <c r="S14" s="41" t="n">
         <v>-0.09878740000000001</v>
       </c>
-      <c r="S14" s="41" t="n">
+      <c r="T14" s="41" t="n">
         <v>0.0929931</v>
       </c>
-      <c r="T14" s="41" t="n">
+      <c r="U14" s="41" t="n">
         <v>-0.0420773</v>
       </c>
-      <c r="U14" s="41" t="n">
+      <c r="V14" s="41" t="n">
         <v>-0.5242846</v>
       </c>
-      <c r="V14" s="41" t="n">
+      <c r="W14" s="41" t="n">
         <v>-0.6187387</v>
       </c>
     </row>
@@ -19097,6 +19276,7 @@
       <c r="T17" s="17" t="n"/>
       <c r="U17" s="17" t="n"/>
       <c r="V17" s="17" t="n"/>
+      <c r="W17" s="17" t="n"/>
     </row>
     <row r="18" ht="18" customHeight="1">
       <c r="A18" s="18" t="inlineStr">
@@ -19536,9 +19716,9 @@
   <mergeCells count="3">
     <mergeCell ref="A2:V2"/>
     <mergeCell ref="A1:V1"/>
-    <mergeCell ref="A17:V17"/>
+    <mergeCell ref="A17:W17"/>
   </mergeCells>
-  <conditionalFormatting sqref="K5:K14">
+  <conditionalFormatting sqref="L5:L14">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="num" val="0"/>
@@ -19550,7 +19730,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L5:L14">
+  <conditionalFormatting sqref="M5:M14">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="num" val="0"/>
@@ -19562,7 +19742,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M5:M14">
+  <conditionalFormatting sqref="N5:N14">
     <cfRule type="colorScale" priority="3">
       <colorScale>
         <cfvo type="num" val="0"/>
@@ -19574,7 +19754,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N5:N14">
+  <conditionalFormatting sqref="O5:O14">
     <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="num" val="0"/>
@@ -19586,7 +19766,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P5:P14">
+  <conditionalFormatting sqref="Q5:Q14">
     <cfRule type="colorScale" priority="5">
       <colorScale>
         <cfvo type="min"/>
@@ -19636,15 +19816,15 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R5:R14">
+  <conditionalFormatting sqref="K5:K14">
     <cfRule type="colorScale" priority="10">
       <colorScale>
-        <cfvo type="min"/>
         <cfvo type="num" val="0"/>
-        <cfvo type="max"/>
-        <color rgb="00E76F51"/>
-        <color rgb="00FFFFFF"/>
-        <color rgb="002A9D8F"/>
+        <cfvo type="num" val="50"/>
+        <cfvo type="num" val="100"/>
+        <color rgb="00C1121F"/>
+        <color rgb="00F9C74F"/>
+        <color rgb="001A6B3C"/>
       </colorScale>
     </cfRule>
   </conditionalFormatting>
@@ -19696,8 +19876,20 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="W5:W14">
+    <cfRule type="colorScale" priority="15">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="num" val="0"/>
+        <cfvo type="max"/>
+        <color rgb="00E76F51"/>
+        <color rgb="00FFFFFF"/>
+        <color rgb="002A9D8F"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="B19:B28">
-    <cfRule type="colorScale" priority="15">
+    <cfRule type="colorScale" priority="16">
       <colorScale>
         <cfvo type="num" val="0"/>
         <cfvo type="num" val="50"/>
@@ -19709,7 +19901,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C19:C28">
-    <cfRule type="colorScale" priority="16">
+    <cfRule type="colorScale" priority="17">
       <colorScale>
         <cfvo type="num" val="0"/>
         <cfvo type="num" val="50"/>
@@ -19721,7 +19913,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D19:D28">
-    <cfRule type="colorScale" priority="17">
+    <cfRule type="colorScale" priority="18">
       <colorScale>
         <cfvo type="num" val="0"/>
         <cfvo type="num" val="50"/>
@@ -19733,7 +19925,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E19:E28">
-    <cfRule type="colorScale" priority="18">
+    <cfRule type="colorScale" priority="19">
       <colorScale>
         <cfvo type="num" val="0"/>
         <cfvo type="num" val="50"/>
@@ -19745,7 +19937,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F19:F28">
-    <cfRule type="colorScale" priority="19">
+    <cfRule type="colorScale" priority="20">
       <colorScale>
         <cfvo type="num" val="0"/>
         <cfvo type="num" val="50"/>
@@ -19785,15 +19977,16 @@
     <col width="12" customWidth="1" min="11" max="11"/>
     <col width="12" customWidth="1" min="12" max="12"/>
     <col width="12" customWidth="1" min="13" max="13"/>
-    <col width="10" customWidth="1" min="14" max="14"/>
-    <col width="14" customWidth="1" min="15" max="15"/>
+    <col width="12" customWidth="1" min="14" max="14"/>
+    <col width="10" customWidth="1" min="15" max="15"/>
     <col width="14" customWidth="1" min="16" max="16"/>
-    <col width="12" customWidth="1" min="17" max="17"/>
-    <col width="10" customWidth="1" min="18" max="18"/>
+    <col width="14" customWidth="1" min="17" max="17"/>
+    <col width="12" customWidth="1" min="18" max="18"/>
     <col width="10" customWidth="1" min="19" max="19"/>
     <col width="10" customWidth="1" min="20" max="20"/>
     <col width="10" customWidth="1" min="21" max="21"/>
     <col width="10" customWidth="1" min="22" max="22"/>
+    <col width="10" customWidth="1" min="23" max="23"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
